--- a/public/templates/template_target.xlsx
+++ b/public/templates/template_target.xlsx
@@ -7,15 +7,21 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Lists" sheetId="2" state="hidden" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="YearList">'Lists'!$A$1:$A$5</definedName>
+    <definedName name="MonthList">'Lists'!$B$1:$B$12</definedName>
+    <definedName name="AmList">'Lists'!$C$1:$C$9</definedName>
+    <definedName name="EntityList">'Lists'!$D$1:$D$6</definedName>
+  </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
   <si>
     <t>tahun</t>
   </si>
@@ -32,10 +38,82 @@
     <t>target</t>
   </si>
   <si>
-    <t>Nama Sales Member (Contoh: BREE COFFEE &amp; KITCHEN)</t>
+    <t>Juni</t>
   </si>
   <si>
-    <t>Nama / Kode Entity (Contoh: BAHANA)</t>
+    <t>REZKY ADIBRATA</t>
+  </si>
+  <si>
+    <t>BUANA</t>
+  </si>
+  <si>
+    <t>Januari</t>
+  </si>
+  <si>
+    <t>Februari</t>
+  </si>
+  <si>
+    <t>Maret</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Mei</t>
+  </si>
+  <si>
+    <t>Juli</t>
+  </si>
+  <si>
+    <t>Agustus</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>Oktober</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>Desember</t>
+  </si>
+  <si>
+    <t>YUDHIE SISWAHYUDIE</t>
+  </si>
+  <si>
+    <t>SUYATMAN</t>
+  </si>
+  <si>
+    <t>KARPIANTO ARIBOWO</t>
+  </si>
+  <si>
+    <t>RIO ANGGRIAWAN</t>
+  </si>
+  <si>
+    <t>BREE COFFEE &amp; KITCHEN</t>
+  </si>
+  <si>
+    <t>TANABAMBU</t>
+  </si>
+  <si>
+    <t>SUWUNG STUDIO</t>
+  </si>
+  <si>
+    <t>INSTAFACTORY</t>
+  </si>
+  <si>
+    <t>BENTALA</t>
+  </si>
+  <si>
+    <t>TRITUNAS</t>
+  </si>
+  <si>
+    <t>BAHANA</t>
+  </si>
+  <si>
+    <t>SUWUNG</t>
   </si>
 </sst>
 </file>
@@ -375,13 +453,13 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="58.843" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="42.418" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -406,17 +484,6163 @@
       <c r="A2">
         <v>2026</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>10000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32"/>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78"/>
+      <c r="D78"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+      <c r="D128"/>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+      <c r="D133"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+      <c r="D134"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+      <c r="D135"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+      <c r="D136"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+      <c r="D137"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+      <c r="D140"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+      <c r="D141"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+      <c r="D142"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+      <c r="D143"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+      <c r="D146"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+      <c r="D147"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+      <c r="D148"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+      <c r="D149"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+      <c r="D150"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151"/>
+      <c r="B151"/>
+      <c r="C151"/>
+      <c r="D151"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152"/>
+      <c r="B152"/>
+      <c r="C152"/>
+      <c r="D152"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+      <c r="D153"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154"/>
+      <c r="B154"/>
+      <c r="C154"/>
+      <c r="D154"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155"/>
+      <c r="B155"/>
+      <c r="C155"/>
+      <c r="D155"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156"/>
+      <c r="B156"/>
+      <c r="C156"/>
+      <c r="D156"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157"/>
+      <c r="B157"/>
+      <c r="C157"/>
+      <c r="D157"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158"/>
+      <c r="B158"/>
+      <c r="C158"/>
+      <c r="D158"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159"/>
+      <c r="B159"/>
+      <c r="C159"/>
+      <c r="D159"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160"/>
+      <c r="B160"/>
+      <c r="C160"/>
+      <c r="D160"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161"/>
+      <c r="B161"/>
+      <c r="C161"/>
+      <c r="D161"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162"/>
+      <c r="B162"/>
+      <c r="C162"/>
+      <c r="D162"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163"/>
+      <c r="B163"/>
+      <c r="C163"/>
+      <c r="D163"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164"/>
+      <c r="B164"/>
+      <c r="C164"/>
+      <c r="D164"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165"/>
+      <c r="B165"/>
+      <c r="C165"/>
+      <c r="D165"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166"/>
+      <c r="B166"/>
+      <c r="C166"/>
+      <c r="D166"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167"/>
+      <c r="B167"/>
+      <c r="C167"/>
+      <c r="D167"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168"/>
+      <c r="B168"/>
+      <c r="C168"/>
+      <c r="D168"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169"/>
+      <c r="B169"/>
+      <c r="C169"/>
+      <c r="D169"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170"/>
+      <c r="B170"/>
+      <c r="C170"/>
+      <c r="D170"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171"/>
+      <c r="B171"/>
+      <c r="C171"/>
+      <c r="D171"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172"/>
+      <c r="B172"/>
+      <c r="C172"/>
+      <c r="D172"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173"/>
+      <c r="B173"/>
+      <c r="C173"/>
+      <c r="D173"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174"/>
+      <c r="B174"/>
+      <c r="C174"/>
+      <c r="D174"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175"/>
+      <c r="B175"/>
+      <c r="C175"/>
+      <c r="D175"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176"/>
+      <c r="B176"/>
+      <c r="C176"/>
+      <c r="D176"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177"/>
+      <c r="B177"/>
+      <c r="C177"/>
+      <c r="D177"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178"/>
+      <c r="B178"/>
+      <c r="C178"/>
+      <c r="D178"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179"/>
+      <c r="B179"/>
+      <c r="C179"/>
+      <c r="D179"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180"/>
+      <c r="B180"/>
+      <c r="C180"/>
+      <c r="D180"/>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181"/>
+      <c r="B181"/>
+      <c r="C181"/>
+      <c r="D181"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182"/>
+      <c r="B182"/>
+      <c r="C182"/>
+      <c r="D182"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183"/>
+      <c r="B183"/>
+      <c r="C183"/>
+      <c r="D183"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184"/>
+      <c r="B184"/>
+      <c r="C184"/>
+      <c r="D184"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185"/>
+      <c r="B185"/>
+      <c r="C185"/>
+      <c r="D185"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186"/>
+      <c r="B186"/>
+      <c r="C186"/>
+      <c r="D186"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187"/>
+      <c r="B187"/>
+      <c r="C187"/>
+      <c r="D187"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188"/>
+      <c r="B188"/>
+      <c r="C188"/>
+      <c r="D188"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189"/>
+      <c r="B189"/>
+      <c r="C189"/>
+      <c r="D189"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190"/>
+      <c r="B190"/>
+      <c r="C190"/>
+      <c r="D190"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191"/>
+      <c r="B191"/>
+      <c r="C191"/>
+      <c r="D191"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192"/>
+      <c r="B192"/>
+      <c r="C192"/>
+      <c r="D192"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193"/>
+      <c r="B193"/>
+      <c r="C193"/>
+      <c r="D193"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194"/>
+      <c r="B194"/>
+      <c r="C194"/>
+      <c r="D194"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195"/>
+      <c r="B195"/>
+      <c r="C195"/>
+      <c r="D195"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196"/>
+      <c r="B196"/>
+      <c r="C196"/>
+      <c r="D196"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197"/>
+      <c r="B197"/>
+      <c r="C197"/>
+      <c r="D197"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198"/>
+      <c r="B198"/>
+      <c r="C198"/>
+      <c r="D198"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199"/>
+      <c r="B199"/>
+      <c r="C199"/>
+      <c r="D199"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200"/>
+      <c r="B200"/>
+      <c r="C200"/>
+      <c r="D200"/>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201"/>
+      <c r="B201"/>
+      <c r="C201"/>
+      <c r="D201"/>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202"/>
+      <c r="B202"/>
+      <c r="C202"/>
+      <c r="D202"/>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203"/>
+      <c r="B203"/>
+      <c r="C203"/>
+      <c r="D203"/>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204"/>
+      <c r="B204"/>
+      <c r="C204"/>
+      <c r="D204"/>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205"/>
+      <c r="B205"/>
+      <c r="C205"/>
+      <c r="D205"/>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206"/>
+      <c r="B206"/>
+      <c r="C206"/>
+      <c r="D206"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207"/>
+      <c r="B207"/>
+      <c r="C207"/>
+      <c r="D207"/>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208"/>
+      <c r="B208"/>
+      <c r="C208"/>
+      <c r="D208"/>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209"/>
+      <c r="B209"/>
+      <c r="C209"/>
+      <c r="D209"/>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210"/>
+      <c r="B210"/>
+      <c r="C210"/>
+      <c r="D210"/>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211"/>
+      <c r="B211"/>
+      <c r="C211"/>
+      <c r="D211"/>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212"/>
+      <c r="B212"/>
+      <c r="C212"/>
+      <c r="D212"/>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213"/>
+      <c r="B213"/>
+      <c r="C213"/>
+      <c r="D213"/>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214"/>
+      <c r="B214"/>
+      <c r="C214"/>
+      <c r="D214"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215"/>
+      <c r="B215"/>
+      <c r="C215"/>
+      <c r="D215"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216"/>
+      <c r="B216"/>
+      <c r="C216"/>
+      <c r="D216"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217"/>
+      <c r="B217"/>
+      <c r="C217"/>
+      <c r="D217"/>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218"/>
+      <c r="B218"/>
+      <c r="C218"/>
+      <c r="D218"/>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219"/>
+      <c r="B219"/>
+      <c r="C219"/>
+      <c r="D219"/>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220"/>
+      <c r="B220"/>
+      <c r="C220"/>
+      <c r="D220"/>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221"/>
+      <c r="B221"/>
+      <c r="C221"/>
+      <c r="D221"/>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222"/>
+      <c r="B222"/>
+      <c r="C222"/>
+      <c r="D222"/>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223"/>
+      <c r="B223"/>
+      <c r="C223"/>
+      <c r="D223"/>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224"/>
+      <c r="B224"/>
+      <c r="C224"/>
+      <c r="D224"/>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225"/>
+      <c r="B225"/>
+      <c r="C225"/>
+      <c r="D225"/>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226"/>
+      <c r="B226"/>
+      <c r="C226"/>
+      <c r="D226"/>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227"/>
+      <c r="B227"/>
+      <c r="C227"/>
+      <c r="D227"/>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228"/>
+      <c r="B228"/>
+      <c r="C228"/>
+      <c r="D228"/>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229"/>
+      <c r="B229"/>
+      <c r="C229"/>
+      <c r="D229"/>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230"/>
+      <c r="B230"/>
+      <c r="C230"/>
+      <c r="D230"/>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231"/>
+      <c r="B231"/>
+      <c r="C231"/>
+      <c r="D231"/>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232"/>
+      <c r="B232"/>
+      <c r="C232"/>
+      <c r="D232"/>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233"/>
+      <c r="B233"/>
+      <c r="C233"/>
+      <c r="D233"/>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234"/>
+      <c r="B234"/>
+      <c r="C234"/>
+      <c r="D234"/>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235"/>
+      <c r="B235"/>
+      <c r="C235"/>
+      <c r="D235"/>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236"/>
+      <c r="B236"/>
+      <c r="C236"/>
+      <c r="D236"/>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237"/>
+      <c r="B237"/>
+      <c r="C237"/>
+      <c r="D237"/>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238"/>
+      <c r="B238"/>
+      <c r="C238"/>
+      <c r="D238"/>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239"/>
+      <c r="B239"/>
+      <c r="C239"/>
+      <c r="D239"/>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240"/>
+      <c r="B240"/>
+      <c r="C240"/>
+      <c r="D240"/>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241"/>
+      <c r="B241"/>
+      <c r="C241"/>
+      <c r="D241"/>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242"/>
+      <c r="B242"/>
+      <c r="C242"/>
+      <c r="D242"/>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243"/>
+      <c r="B243"/>
+      <c r="C243"/>
+      <c r="D243"/>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244"/>
+      <c r="B244"/>
+      <c r="C244"/>
+      <c r="D244"/>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245"/>
+      <c r="B245"/>
+      <c r="C245"/>
+      <c r="D245"/>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246"/>
+      <c r="B246"/>
+      <c r="C246"/>
+      <c r="D246"/>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247"/>
+      <c r="B247"/>
+      <c r="C247"/>
+      <c r="D247"/>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248"/>
+      <c r="B248"/>
+      <c r="C248"/>
+      <c r="D248"/>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249"/>
+      <c r="B249"/>
+      <c r="C249"/>
+      <c r="D249"/>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250"/>
+      <c r="B250"/>
+      <c r="C250"/>
+      <c r="D250"/>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251"/>
+      <c r="B251"/>
+      <c r="C251"/>
+      <c r="D251"/>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252"/>
+      <c r="B252"/>
+      <c r="C252"/>
+      <c r="D252"/>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253"/>
+      <c r="B253"/>
+      <c r="C253"/>
+      <c r="D253"/>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254"/>
+      <c r="B254"/>
+      <c r="C254"/>
+      <c r="D254"/>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255"/>
+      <c r="B255"/>
+      <c r="C255"/>
+      <c r="D255"/>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256"/>
+      <c r="B256"/>
+      <c r="C256"/>
+      <c r="D256"/>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257"/>
+      <c r="B257"/>
+      <c r="C257"/>
+      <c r="D257"/>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258"/>
+      <c r="B258"/>
+      <c r="C258"/>
+      <c r="D258"/>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259"/>
+      <c r="B259"/>
+      <c r="C259"/>
+      <c r="D259"/>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260"/>
+      <c r="B260"/>
+      <c r="C260"/>
+      <c r="D260"/>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261"/>
+      <c r="B261"/>
+      <c r="C261"/>
+      <c r="D261"/>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262"/>
+      <c r="B262"/>
+      <c r="C262"/>
+      <c r="D262"/>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263"/>
+      <c r="B263"/>
+      <c r="C263"/>
+      <c r="D263"/>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264"/>
+      <c r="B264"/>
+      <c r="C264"/>
+      <c r="D264"/>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265"/>
+      <c r="B265"/>
+      <c r="C265"/>
+      <c r="D265"/>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266"/>
+      <c r="B266"/>
+      <c r="C266"/>
+      <c r="D266"/>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267"/>
+      <c r="B267"/>
+      <c r="C267"/>
+      <c r="D267"/>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268"/>
+      <c r="B268"/>
+      <c r="C268"/>
+      <c r="D268"/>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269"/>
+      <c r="B269"/>
+      <c r="C269"/>
+      <c r="D269"/>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270"/>
+      <c r="B270"/>
+      <c r="C270"/>
+      <c r="D270"/>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271"/>
+      <c r="B271"/>
+      <c r="C271"/>
+      <c r="D271"/>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272"/>
+      <c r="B272"/>
+      <c r="C272"/>
+      <c r="D272"/>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273"/>
+      <c r="B273"/>
+      <c r="C273"/>
+      <c r="D273"/>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274"/>
+      <c r="B274"/>
+      <c r="C274"/>
+      <c r="D274"/>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275"/>
+      <c r="B275"/>
+      <c r="C275"/>
+      <c r="D275"/>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276"/>
+      <c r="B276"/>
+      <c r="C276"/>
+      <c r="D276"/>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277"/>
+      <c r="B277"/>
+      <c r="C277"/>
+      <c r="D277"/>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278"/>
+      <c r="B278"/>
+      <c r="C278"/>
+      <c r="D278"/>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279"/>
+      <c r="B279"/>
+      <c r="C279"/>
+      <c r="D279"/>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280"/>
+      <c r="B280"/>
+      <c r="C280"/>
+      <c r="D280"/>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281"/>
+      <c r="B281"/>
+      <c r="C281"/>
+      <c r="D281"/>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282"/>
+      <c r="B282"/>
+      <c r="C282"/>
+      <c r="D282"/>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283"/>
+      <c r="B283"/>
+      <c r="C283"/>
+      <c r="D283"/>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284"/>
+      <c r="B284"/>
+      <c r="C284"/>
+      <c r="D284"/>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285"/>
+      <c r="B285"/>
+      <c r="C285"/>
+      <c r="D285"/>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286"/>
+      <c r="B286"/>
+      <c r="C286"/>
+      <c r="D286"/>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287"/>
+      <c r="B287"/>
+      <c r="C287"/>
+      <c r="D287"/>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288"/>
+      <c r="B288"/>
+      <c r="C288"/>
+      <c r="D288"/>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289"/>
+      <c r="B289"/>
+      <c r="C289"/>
+      <c r="D289"/>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290"/>
+      <c r="B290"/>
+      <c r="C290"/>
+      <c r="D290"/>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291"/>
+      <c r="B291"/>
+      <c r="C291"/>
+      <c r="D291"/>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292"/>
+      <c r="B292"/>
+      <c r="C292"/>
+      <c r="D292"/>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293"/>
+      <c r="B293"/>
+      <c r="C293"/>
+      <c r="D293"/>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294"/>
+      <c r="B294"/>
+      <c r="C294"/>
+      <c r="D294"/>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295"/>
+      <c r="B295"/>
+      <c r="C295"/>
+      <c r="D295"/>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296"/>
+      <c r="B296"/>
+      <c r="C296"/>
+      <c r="D296"/>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297"/>
+      <c r="B297"/>
+      <c r="C297"/>
+      <c r="D297"/>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298"/>
+      <c r="B298"/>
+      <c r="C298"/>
+      <c r="D298"/>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299"/>
+      <c r="B299"/>
+      <c r="C299"/>
+      <c r="D299"/>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300"/>
+      <c r="B300"/>
+      <c r="C300"/>
+      <c r="D300"/>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301"/>
+      <c r="B301"/>
+      <c r="C301"/>
+      <c r="D301"/>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302"/>
+      <c r="B302"/>
+      <c r="C302"/>
+      <c r="D302"/>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303"/>
+      <c r="B303"/>
+      <c r="C303"/>
+      <c r="D303"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304"/>
+      <c r="B304"/>
+      <c r="C304"/>
+      <c r="D304"/>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305"/>
+      <c r="B305"/>
+      <c r="C305"/>
+      <c r="D305"/>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306"/>
+      <c r="B306"/>
+      <c r="C306"/>
+      <c r="D306"/>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307"/>
+      <c r="B307"/>
+      <c r="C307"/>
+      <c r="D307"/>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308"/>
+      <c r="B308"/>
+      <c r="C308"/>
+      <c r="D308"/>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309"/>
+      <c r="B309"/>
+      <c r="C309"/>
+      <c r="D309"/>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310"/>
+      <c r="B310"/>
+      <c r="C310"/>
+      <c r="D310"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311"/>
+      <c r="B311"/>
+      <c r="C311"/>
+      <c r="D311"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312"/>
+      <c r="B312"/>
+      <c r="C312"/>
+      <c r="D312"/>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313"/>
+      <c r="B313"/>
+      <c r="C313"/>
+      <c r="D313"/>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314"/>
+      <c r="B314"/>
+      <c r="C314"/>
+      <c r="D314"/>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315"/>
+      <c r="B315"/>
+      <c r="C315"/>
+      <c r="D315"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316"/>
+      <c r="B316"/>
+      <c r="C316"/>
+      <c r="D316"/>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317"/>
+      <c r="B317"/>
+      <c r="C317"/>
+      <c r="D317"/>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318"/>
+      <c r="B318"/>
+      <c r="C318"/>
+      <c r="D318"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319"/>
+      <c r="B319"/>
+      <c r="C319"/>
+      <c r="D319"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320"/>
+      <c r="B320"/>
+      <c r="C320"/>
+      <c r="D320"/>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321"/>
+      <c r="B321"/>
+      <c r="C321"/>
+      <c r="D321"/>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322"/>
+      <c r="B322"/>
+      <c r="C322"/>
+      <c r="D322"/>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323"/>
+      <c r="B323"/>
+      <c r="C323"/>
+      <c r="D323"/>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324"/>
+      <c r="B324"/>
+      <c r="C324"/>
+      <c r="D324"/>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325"/>
+      <c r="B325"/>
+      <c r="C325"/>
+      <c r="D325"/>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326"/>
+      <c r="B326"/>
+      <c r="C326"/>
+      <c r="D326"/>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327"/>
+      <c r="B327"/>
+      <c r="C327"/>
+      <c r="D327"/>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328"/>
+      <c r="B328"/>
+      <c r="C328"/>
+      <c r="D328"/>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329"/>
+      <c r="B329"/>
+      <c r="C329"/>
+      <c r="D329"/>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330"/>
+      <c r="B330"/>
+      <c r="C330"/>
+      <c r="D330"/>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331"/>
+      <c r="B331"/>
+      <c r="C331"/>
+      <c r="D331"/>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332"/>
+      <c r="B332"/>
+      <c r="C332"/>
+      <c r="D332"/>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333"/>
+      <c r="B333"/>
+      <c r="C333"/>
+      <c r="D333"/>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334"/>
+      <c r="B334"/>
+      <c r="C334"/>
+      <c r="D334"/>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335"/>
+      <c r="B335"/>
+      <c r="C335"/>
+      <c r="D335"/>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336"/>
+      <c r="B336"/>
+      <c r="C336"/>
+      <c r="D336"/>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337"/>
+      <c r="B337"/>
+      <c r="C337"/>
+      <c r="D337"/>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338"/>
+      <c r="B338"/>
+      <c r="C338"/>
+      <c r="D338"/>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339"/>
+      <c r="B339"/>
+      <c r="C339"/>
+      <c r="D339"/>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340"/>
+      <c r="B340"/>
+      <c r="C340"/>
+      <c r="D340"/>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341"/>
+      <c r="B341"/>
+      <c r="C341"/>
+      <c r="D341"/>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342"/>
+      <c r="B342"/>
+      <c r="C342"/>
+      <c r="D342"/>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343"/>
+      <c r="B343"/>
+      <c r="C343"/>
+      <c r="D343"/>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344"/>
+      <c r="B344"/>
+      <c r="C344"/>
+      <c r="D344"/>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345"/>
+      <c r="B345"/>
+      <c r="C345"/>
+      <c r="D345"/>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346"/>
+      <c r="B346"/>
+      <c r="C346"/>
+      <c r="D346"/>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347"/>
+      <c r="B347"/>
+      <c r="C347"/>
+      <c r="D347"/>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348"/>
+      <c r="B348"/>
+      <c r="C348"/>
+      <c r="D348"/>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349"/>
+      <c r="B349"/>
+      <c r="C349"/>
+      <c r="D349"/>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350"/>
+      <c r="B350"/>
+      <c r="C350"/>
+      <c r="D350"/>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351"/>
+      <c r="B351"/>
+      <c r="C351"/>
+      <c r="D351"/>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352"/>
+      <c r="B352"/>
+      <c r="C352"/>
+      <c r="D352"/>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353"/>
+      <c r="B353"/>
+      <c r="C353"/>
+      <c r="D353"/>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354"/>
+      <c r="B354"/>
+      <c r="C354"/>
+      <c r="D354"/>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355"/>
+      <c r="B355"/>
+      <c r="C355"/>
+      <c r="D355"/>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356"/>
+      <c r="B356"/>
+      <c r="C356"/>
+      <c r="D356"/>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357"/>
+      <c r="B357"/>
+      <c r="C357"/>
+      <c r="D357"/>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358"/>
+      <c r="B358"/>
+      <c r="C358"/>
+      <c r="D358"/>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359"/>
+      <c r="B359"/>
+      <c r="C359"/>
+      <c r="D359"/>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360"/>
+      <c r="B360"/>
+      <c r="C360"/>
+      <c r="D360"/>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361"/>
+      <c r="B361"/>
+      <c r="C361"/>
+      <c r="D361"/>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362"/>
+      <c r="B362"/>
+      <c r="C362"/>
+      <c r="D362"/>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363"/>
+      <c r="B363"/>
+      <c r="C363"/>
+      <c r="D363"/>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364"/>
+      <c r="B364"/>
+      <c r="C364"/>
+      <c r="D364"/>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365"/>
+      <c r="B365"/>
+      <c r="C365"/>
+      <c r="D365"/>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366"/>
+      <c r="B366"/>
+      <c r="C366"/>
+      <c r="D366"/>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367"/>
+      <c r="B367"/>
+      <c r="C367"/>
+      <c r="D367"/>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368"/>
+      <c r="B368"/>
+      <c r="C368"/>
+      <c r="D368"/>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369"/>
+      <c r="B369"/>
+      <c r="C369"/>
+      <c r="D369"/>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370"/>
+      <c r="B370"/>
+      <c r="C370"/>
+      <c r="D370"/>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371"/>
+      <c r="B371"/>
+      <c r="C371"/>
+      <c r="D371"/>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372"/>
+      <c r="B372"/>
+      <c r="C372"/>
+      <c r="D372"/>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373"/>
+      <c r="B373"/>
+      <c r="C373"/>
+      <c r="D373"/>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374"/>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375"/>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376"/>
+      <c r="B376"/>
+      <c r="C376"/>
+      <c r="D376"/>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377"/>
+      <c r="B377"/>
+      <c r="C377"/>
+      <c r="D377"/>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378"/>
+      <c r="B378"/>
+      <c r="C378"/>
+      <c r="D378"/>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379"/>
+      <c r="B379"/>
+      <c r="C379"/>
+      <c r="D379"/>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380"/>
+      <c r="B380"/>
+      <c r="C380"/>
+      <c r="D380"/>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381"/>
+      <c r="B381"/>
+      <c r="C381"/>
+      <c r="D381"/>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382"/>
+      <c r="B382"/>
+      <c r="C382"/>
+      <c r="D382"/>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383"/>
+      <c r="B383"/>
+      <c r="C383"/>
+      <c r="D383"/>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384"/>
+      <c r="B384"/>
+      <c r="C384"/>
+      <c r="D384"/>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385"/>
+      <c r="B385"/>
+      <c r="C385"/>
+      <c r="D385"/>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386"/>
+      <c r="B386"/>
+      <c r="C386"/>
+      <c r="D386"/>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387"/>
+      <c r="B387"/>
+      <c r="C387"/>
+      <c r="D387"/>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388"/>
+      <c r="B388"/>
+      <c r="C388"/>
+      <c r="D388"/>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389"/>
+      <c r="B389"/>
+      <c r="C389"/>
+      <c r="D389"/>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390"/>
+      <c r="B390"/>
+      <c r="C390"/>
+      <c r="D390"/>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391"/>
+      <c r="B391"/>
+      <c r="C391"/>
+      <c r="D391"/>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392"/>
+      <c r="B392"/>
+      <c r="C392"/>
+      <c r="D392"/>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393"/>
+      <c r="B393"/>
+      <c r="C393"/>
+      <c r="D393"/>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394"/>
+      <c r="B394"/>
+      <c r="C394"/>
+      <c r="D394"/>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395"/>
+      <c r="B395"/>
+      <c r="C395"/>
+      <c r="D395"/>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396"/>
+      <c r="B396"/>
+      <c r="C396"/>
+      <c r="D396"/>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397"/>
+      <c r="B397"/>
+      <c r="C397"/>
+      <c r="D397"/>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398"/>
+      <c r="B398"/>
+      <c r="C398"/>
+      <c r="D398"/>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399"/>
+      <c r="B399"/>
+      <c r="C399"/>
+      <c r="D399"/>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400"/>
+      <c r="B400"/>
+      <c r="C400"/>
+      <c r="D400"/>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401"/>
+      <c r="B401"/>
+      <c r="C401"/>
+      <c r="D401"/>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402"/>
+      <c r="B402"/>
+      <c r="C402"/>
+      <c r="D402"/>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403"/>
+      <c r="B403"/>
+      <c r="C403"/>
+      <c r="D403"/>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404"/>
+      <c r="B404"/>
+      <c r="C404"/>
+      <c r="D404"/>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405"/>
+      <c r="B405"/>
+      <c r="C405"/>
+      <c r="D405"/>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406"/>
+      <c r="B406"/>
+      <c r="C406"/>
+      <c r="D406"/>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407"/>
+      <c r="B407"/>
+      <c r="C407"/>
+      <c r="D407"/>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408"/>
+      <c r="B408"/>
+      <c r="C408"/>
+      <c r="D408"/>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409"/>
+      <c r="B409"/>
+      <c r="C409"/>
+      <c r="D409"/>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410"/>
+      <c r="B410"/>
+      <c r="C410"/>
+      <c r="D410"/>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411"/>
+      <c r="B411"/>
+      <c r="C411"/>
+      <c r="D411"/>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412"/>
+      <c r="B412"/>
+      <c r="C412"/>
+      <c r="D412"/>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413"/>
+      <c r="B413"/>
+      <c r="C413"/>
+      <c r="D413"/>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414"/>
+      <c r="B414"/>
+      <c r="C414"/>
+      <c r="D414"/>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415"/>
+      <c r="B415"/>
+      <c r="C415"/>
+      <c r="D415"/>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416"/>
+      <c r="B416"/>
+      <c r="C416"/>
+      <c r="D416"/>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417"/>
+      <c r="B417"/>
+      <c r="C417"/>
+      <c r="D417"/>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418"/>
+      <c r="B418"/>
+      <c r="C418"/>
+      <c r="D418"/>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419"/>
+      <c r="B419"/>
+      <c r="C419"/>
+      <c r="D419"/>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420"/>
+      <c r="B420"/>
+      <c r="C420"/>
+      <c r="D420"/>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421"/>
+      <c r="B421"/>
+      <c r="C421"/>
+      <c r="D421"/>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422"/>
+      <c r="B422"/>
+      <c r="C422"/>
+      <c r="D422"/>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423"/>
+      <c r="B423"/>
+      <c r="C423"/>
+      <c r="D423"/>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424"/>
+      <c r="B424"/>
+      <c r="C424"/>
+      <c r="D424"/>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425"/>
+      <c r="B425"/>
+      <c r="C425"/>
+      <c r="D425"/>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426"/>
+      <c r="B426"/>
+      <c r="C426"/>
+      <c r="D426"/>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427"/>
+      <c r="B427"/>
+      <c r="C427"/>
+      <c r="D427"/>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428"/>
+      <c r="B428"/>
+      <c r="C428"/>
+      <c r="D428"/>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429"/>
+      <c r="B429"/>
+      <c r="C429"/>
+      <c r="D429"/>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430"/>
+      <c r="B430"/>
+      <c r="C430"/>
+      <c r="D430"/>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431"/>
+      <c r="B431"/>
+      <c r="C431"/>
+      <c r="D431"/>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432"/>
+      <c r="B432"/>
+      <c r="C432"/>
+      <c r="D432"/>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433"/>
+      <c r="B433"/>
+      <c r="C433"/>
+      <c r="D433"/>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434"/>
+      <c r="B434"/>
+      <c r="C434"/>
+      <c r="D434"/>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435"/>
+      <c r="B435"/>
+      <c r="C435"/>
+      <c r="D435"/>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436"/>
+      <c r="B436"/>
+      <c r="C436"/>
+      <c r="D436"/>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437"/>
+      <c r="B437"/>
+      <c r="C437"/>
+      <c r="D437"/>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438"/>
+      <c r="B438"/>
+      <c r="C438"/>
+      <c r="D438"/>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439"/>
+      <c r="B439"/>
+      <c r="C439"/>
+      <c r="D439"/>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440"/>
+      <c r="B440"/>
+      <c r="C440"/>
+      <c r="D440"/>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441"/>
+      <c r="B441"/>
+      <c r="C441"/>
+      <c r="D441"/>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442"/>
+      <c r="B442"/>
+      <c r="C442"/>
+      <c r="D442"/>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443"/>
+      <c r="B443"/>
+      <c r="C443"/>
+      <c r="D443"/>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444"/>
+      <c r="B444"/>
+      <c r="C444"/>
+      <c r="D444"/>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445"/>
+      <c r="B445"/>
+      <c r="C445"/>
+      <c r="D445"/>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446"/>
+      <c r="B446"/>
+      <c r="C446"/>
+      <c r="D446"/>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447"/>
+      <c r="B447"/>
+      <c r="C447"/>
+      <c r="D447"/>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448"/>
+      <c r="B448"/>
+      <c r="C448"/>
+      <c r="D448"/>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449"/>
+      <c r="B449"/>
+      <c r="C449"/>
+      <c r="D449"/>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450"/>
+      <c r="B450"/>
+      <c r="C450"/>
+      <c r="D450"/>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451"/>
+      <c r="B451"/>
+      <c r="C451"/>
+      <c r="D451"/>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452"/>
+      <c r="B452"/>
+      <c r="C452"/>
+      <c r="D452"/>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453"/>
+      <c r="B453"/>
+      <c r="C453"/>
+      <c r="D453"/>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454"/>
+      <c r="B454"/>
+      <c r="C454"/>
+      <c r="D454"/>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455"/>
+      <c r="B455"/>
+      <c r="C455"/>
+      <c r="D455"/>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456"/>
+      <c r="B456"/>
+      <c r="C456"/>
+      <c r="D456"/>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457"/>
+      <c r="B457"/>
+      <c r="C457"/>
+      <c r="D457"/>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458"/>
+      <c r="B458"/>
+      <c r="C458"/>
+      <c r="D458"/>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459"/>
+      <c r="B459"/>
+      <c r="C459"/>
+      <c r="D459"/>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460"/>
+      <c r="B460"/>
+      <c r="C460"/>
+      <c r="D460"/>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461"/>
+      <c r="B461"/>
+      <c r="C461"/>
+      <c r="D461"/>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462"/>
+      <c r="B462"/>
+      <c r="C462"/>
+      <c r="D462"/>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463"/>
+      <c r="B463"/>
+      <c r="C463"/>
+      <c r="D463"/>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464"/>
+      <c r="B464"/>
+      <c r="C464"/>
+      <c r="D464"/>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465"/>
+      <c r="B465"/>
+      <c r="C465"/>
+      <c r="D465"/>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466"/>
+      <c r="B466"/>
+      <c r="C466"/>
+      <c r="D466"/>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467"/>
+      <c r="B467"/>
+      <c r="C467"/>
+      <c r="D467"/>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468"/>
+      <c r="B468"/>
+      <c r="C468"/>
+      <c r="D468"/>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469"/>
+      <c r="B469"/>
+      <c r="C469"/>
+      <c r="D469"/>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470"/>
+      <c r="B470"/>
+      <c r="C470"/>
+      <c r="D470"/>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471"/>
+      <c r="B471"/>
+      <c r="C471"/>
+      <c r="D471"/>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472"/>
+      <c r="B472"/>
+      <c r="C472"/>
+      <c r="D472"/>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473"/>
+      <c r="B473"/>
+      <c r="C473"/>
+      <c r="D473"/>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474"/>
+      <c r="B474"/>
+      <c r="C474"/>
+      <c r="D474"/>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475"/>
+      <c r="B475"/>
+      <c r="C475"/>
+      <c r="D475"/>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476"/>
+      <c r="B476"/>
+      <c r="C476"/>
+      <c r="D476"/>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477"/>
+      <c r="B477"/>
+      <c r="C477"/>
+      <c r="D477"/>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478"/>
+      <c r="B478"/>
+      <c r="C478"/>
+      <c r="D478"/>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479"/>
+      <c r="B479"/>
+      <c r="C479"/>
+      <c r="D479"/>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480"/>
+      <c r="B480"/>
+      <c r="C480"/>
+      <c r="D480"/>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481"/>
+      <c r="B481"/>
+      <c r="C481"/>
+      <c r="D481"/>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482"/>
+      <c r="B482"/>
+      <c r="C482"/>
+      <c r="D482"/>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483"/>
+      <c r="B483"/>
+      <c r="C483"/>
+      <c r="D483"/>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484"/>
+      <c r="B484"/>
+      <c r="C484"/>
+      <c r="D484"/>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485"/>
+      <c r="B485"/>
+      <c r="C485"/>
+      <c r="D485"/>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486"/>
+      <c r="B486"/>
+      <c r="C486"/>
+      <c r="D486"/>
+    </row>
+    <row r="487" spans="1:5">
+      <c r="A487"/>
+      <c r="B487"/>
+      <c r="C487"/>
+      <c r="D487"/>
+    </row>
+    <row r="488" spans="1:5">
+      <c r="A488"/>
+      <c r="B488"/>
+      <c r="C488"/>
+      <c r="D488"/>
+    </row>
+    <row r="489" spans="1:5">
+      <c r="A489"/>
+      <c r="B489"/>
+      <c r="C489"/>
+      <c r="D489"/>
+    </row>
+    <row r="490" spans="1:5">
+      <c r="A490"/>
+      <c r="B490"/>
+      <c r="C490"/>
+      <c r="D490"/>
+    </row>
+    <row r="491" spans="1:5">
+      <c r="A491"/>
+      <c r="B491"/>
+      <c r="C491"/>
+      <c r="D491"/>
+    </row>
+    <row r="492" spans="1:5">
+      <c r="A492"/>
+      <c r="B492"/>
+      <c r="C492"/>
+      <c r="D492"/>
+    </row>
+    <row r="493" spans="1:5">
+      <c r="A493"/>
+      <c r="B493"/>
+      <c r="C493"/>
+      <c r="D493"/>
+    </row>
+    <row r="494" spans="1:5">
+      <c r="A494"/>
+      <c r="B494"/>
+      <c r="C494"/>
+      <c r="D494"/>
+    </row>
+    <row r="495" spans="1:5">
+      <c r="A495"/>
+      <c r="B495"/>
+      <c r="C495"/>
+      <c r="D495"/>
+    </row>
+    <row r="496" spans="1:5">
+      <c r="A496"/>
+      <c r="B496"/>
+      <c r="C496"/>
+      <c r="D496"/>
+    </row>
+    <row r="497" spans="1:5">
+      <c r="A497"/>
+      <c r="B497"/>
+      <c r="C497"/>
+      <c r="D497"/>
+    </row>
+    <row r="498" spans="1:5">
+      <c r="A498"/>
+      <c r="B498"/>
+      <c r="C498"/>
+      <c r="D498"/>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499"/>
+      <c r="B499"/>
+      <c r="C499"/>
+      <c r="D499"/>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500"/>
+      <c r="B500"/>
+      <c r="C500"/>
+      <c r="D500"/>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501"/>
+      <c r="B501"/>
+      <c r="C501"/>
+      <c r="D501"/>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502"/>
+      <c r="B502"/>
+      <c r="C502"/>
+      <c r="D502"/>
+    </row>
+    <row r="503" spans="1:5">
+      <c r="A503"/>
+      <c r="B503"/>
+      <c r="C503"/>
+      <c r="D503"/>
+    </row>
+    <row r="504" spans="1:5">
+      <c r="A504"/>
+      <c r="B504"/>
+      <c r="C504"/>
+      <c r="D504"/>
+    </row>
+    <row r="505" spans="1:5">
+      <c r="A505"/>
+      <c r="B505"/>
+      <c r="C505"/>
+      <c r="D505"/>
+    </row>
+    <row r="506" spans="1:5">
+      <c r="A506"/>
+      <c r="B506"/>
+      <c r="C506"/>
+      <c r="D506"/>
+    </row>
+    <row r="507" spans="1:5">
+      <c r="A507"/>
+      <c r="B507"/>
+      <c r="C507"/>
+      <c r="D507"/>
+    </row>
+    <row r="508" spans="1:5">
+      <c r="A508"/>
+      <c r="B508"/>
+      <c r="C508"/>
+      <c r="D508"/>
+    </row>
+    <row r="509" spans="1:5">
+      <c r="A509"/>
+      <c r="B509"/>
+      <c r="C509"/>
+      <c r="D509"/>
+    </row>
+    <row r="510" spans="1:5">
+      <c r="A510"/>
+      <c r="B510"/>
+      <c r="C510"/>
+      <c r="D510"/>
+    </row>
+    <row r="511" spans="1:5">
+      <c r="A511"/>
+      <c r="B511"/>
+      <c r="C511"/>
+      <c r="D511"/>
+    </row>
+    <row r="512" spans="1:5">
+      <c r="A512"/>
+      <c r="B512"/>
+      <c r="C512"/>
+      <c r="D512"/>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513"/>
+      <c r="B513"/>
+      <c r="C513"/>
+      <c r="D513"/>
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514"/>
+      <c r="B514"/>
+      <c r="C514"/>
+      <c r="D514"/>
+    </row>
+    <row r="515" spans="1:5">
+      <c r="A515"/>
+      <c r="B515"/>
+      <c r="C515"/>
+      <c r="D515"/>
+    </row>
+    <row r="516" spans="1:5">
+      <c r="A516"/>
+      <c r="B516"/>
+      <c r="C516"/>
+      <c r="D516"/>
+    </row>
+    <row r="517" spans="1:5">
+      <c r="A517"/>
+      <c r="B517"/>
+      <c r="C517"/>
+      <c r="D517"/>
+    </row>
+    <row r="518" spans="1:5">
+      <c r="A518"/>
+      <c r="B518"/>
+      <c r="C518"/>
+      <c r="D518"/>
+    </row>
+    <row r="519" spans="1:5">
+      <c r="A519"/>
+      <c r="B519"/>
+      <c r="C519"/>
+      <c r="D519"/>
+    </row>
+    <row r="520" spans="1:5">
+      <c r="A520"/>
+      <c r="B520"/>
+      <c r="C520"/>
+      <c r="D520"/>
+    </row>
+    <row r="521" spans="1:5">
+      <c r="A521"/>
+      <c r="B521"/>
+      <c r="C521"/>
+      <c r="D521"/>
+    </row>
+    <row r="522" spans="1:5">
+      <c r="A522"/>
+      <c r="B522"/>
+      <c r="C522"/>
+      <c r="D522"/>
+    </row>
+    <row r="523" spans="1:5">
+      <c r="A523"/>
+      <c r="B523"/>
+      <c r="C523"/>
+      <c r="D523"/>
+    </row>
+    <row r="524" spans="1:5">
+      <c r="A524"/>
+      <c r="B524"/>
+      <c r="C524"/>
+      <c r="D524"/>
+    </row>
+    <row r="525" spans="1:5">
+      <c r="A525"/>
+      <c r="B525"/>
+      <c r="C525"/>
+      <c r="D525"/>
+    </row>
+    <row r="526" spans="1:5">
+      <c r="A526"/>
+      <c r="B526"/>
+      <c r="C526"/>
+      <c r="D526"/>
+    </row>
+    <row r="527" spans="1:5">
+      <c r="A527"/>
+      <c r="B527"/>
+      <c r="C527"/>
+      <c r="D527"/>
+    </row>
+    <row r="528" spans="1:5">
+      <c r="A528"/>
+      <c r="B528"/>
+      <c r="C528"/>
+      <c r="D528"/>
+    </row>
+    <row r="529" spans="1:5">
+      <c r="A529"/>
+      <c r="B529"/>
+      <c r="C529"/>
+      <c r="D529"/>
+    </row>
+    <row r="530" spans="1:5">
+      <c r="A530"/>
+      <c r="B530"/>
+      <c r="C530"/>
+      <c r="D530"/>
+    </row>
+    <row r="531" spans="1:5">
+      <c r="A531"/>
+      <c r="B531"/>
+      <c r="C531"/>
+      <c r="D531"/>
+    </row>
+    <row r="532" spans="1:5">
+      <c r="A532"/>
+      <c r="B532"/>
+      <c r="C532"/>
+      <c r="D532"/>
+    </row>
+    <row r="533" spans="1:5">
+      <c r="A533"/>
+      <c r="B533"/>
+      <c r="C533"/>
+      <c r="D533"/>
+    </row>
+    <row r="534" spans="1:5">
+      <c r="A534"/>
+      <c r="B534"/>
+      <c r="C534"/>
+      <c r="D534"/>
+    </row>
+    <row r="535" spans="1:5">
+      <c r="A535"/>
+      <c r="B535"/>
+      <c r="C535"/>
+      <c r="D535"/>
+    </row>
+    <row r="536" spans="1:5">
+      <c r="A536"/>
+      <c r="B536"/>
+      <c r="C536"/>
+      <c r="D536"/>
+    </row>
+    <row r="537" spans="1:5">
+      <c r="A537"/>
+      <c r="B537"/>
+      <c r="C537"/>
+      <c r="D537"/>
+    </row>
+    <row r="538" spans="1:5">
+      <c r="A538"/>
+      <c r="B538"/>
+      <c r="C538"/>
+      <c r="D538"/>
+    </row>
+    <row r="539" spans="1:5">
+      <c r="A539"/>
+      <c r="B539"/>
+      <c r="C539"/>
+      <c r="D539"/>
+    </row>
+    <row r="540" spans="1:5">
+      <c r="A540"/>
+      <c r="B540"/>
+      <c r="C540"/>
+      <c r="D540"/>
+    </row>
+    <row r="541" spans="1:5">
+      <c r="A541"/>
+      <c r="B541"/>
+      <c r="C541"/>
+      <c r="D541"/>
+    </row>
+    <row r="542" spans="1:5">
+      <c r="A542"/>
+      <c r="B542"/>
+      <c r="C542"/>
+      <c r="D542"/>
+    </row>
+    <row r="543" spans="1:5">
+      <c r="A543"/>
+      <c r="B543"/>
+      <c r="C543"/>
+      <c r="D543"/>
+    </row>
+    <row r="544" spans="1:5">
+      <c r="A544"/>
+      <c r="B544"/>
+      <c r="C544"/>
+      <c r="D544"/>
+    </row>
+    <row r="545" spans="1:5">
+      <c r="A545"/>
+      <c r="B545"/>
+      <c r="C545"/>
+      <c r="D545"/>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546"/>
+      <c r="B546"/>
+      <c r="C546"/>
+      <c r="D546"/>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547"/>
+      <c r="B547"/>
+      <c r="C547"/>
+      <c r="D547"/>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548"/>
+      <c r="B548"/>
+      <c r="C548"/>
+      <c r="D548"/>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549"/>
+      <c r="B549"/>
+      <c r="C549"/>
+      <c r="D549"/>
+    </row>
+    <row r="550" spans="1:5">
+      <c r="A550"/>
+      <c r="B550"/>
+      <c r="C550"/>
+      <c r="D550"/>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551"/>
+      <c r="B551"/>
+      <c r="C551"/>
+      <c r="D551"/>
+    </row>
+    <row r="552" spans="1:5">
+      <c r="A552"/>
+      <c r="B552"/>
+      <c r="C552"/>
+      <c r="D552"/>
+    </row>
+    <row r="553" spans="1:5">
+      <c r="A553"/>
+      <c r="B553"/>
+      <c r="C553"/>
+      <c r="D553"/>
+    </row>
+    <row r="554" spans="1:5">
+      <c r="A554"/>
+      <c r="B554"/>
+      <c r="C554"/>
+      <c r="D554"/>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555"/>
+      <c r="B555"/>
+      <c r="C555"/>
+      <c r="D555"/>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556"/>
+      <c r="B556"/>
+      <c r="C556"/>
+      <c r="D556"/>
+    </row>
+    <row r="557" spans="1:5">
+      <c r="A557"/>
+      <c r="B557"/>
+      <c r="C557"/>
+      <c r="D557"/>
+    </row>
+    <row r="558" spans="1:5">
+      <c r="A558"/>
+      <c r="B558"/>
+      <c r="C558"/>
+      <c r="D558"/>
+    </row>
+    <row r="559" spans="1:5">
+      <c r="A559"/>
+      <c r="B559"/>
+      <c r="C559"/>
+      <c r="D559"/>
+    </row>
+    <row r="560" spans="1:5">
+      <c r="A560"/>
+      <c r="B560"/>
+      <c r="C560"/>
+      <c r="D560"/>
+    </row>
+    <row r="561" spans="1:5">
+      <c r="A561"/>
+      <c r="B561"/>
+      <c r="C561"/>
+      <c r="D561"/>
+    </row>
+    <row r="562" spans="1:5">
+      <c r="A562"/>
+      <c r="B562"/>
+      <c r="C562"/>
+      <c r="D562"/>
+    </row>
+    <row r="563" spans="1:5">
+      <c r="A563"/>
+      <c r="B563"/>
+      <c r="C563"/>
+      <c r="D563"/>
+    </row>
+    <row r="564" spans="1:5">
+      <c r="A564"/>
+      <c r="B564"/>
+      <c r="C564"/>
+      <c r="D564"/>
+    </row>
+    <row r="565" spans="1:5">
+      <c r="A565"/>
+      <c r="B565"/>
+      <c r="C565"/>
+      <c r="D565"/>
+    </row>
+    <row r="566" spans="1:5">
+      <c r="A566"/>
+      <c r="B566"/>
+      <c r="C566"/>
+      <c r="D566"/>
+    </row>
+    <row r="567" spans="1:5">
+      <c r="A567"/>
+      <c r="B567"/>
+      <c r="C567"/>
+      <c r="D567"/>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568"/>
+      <c r="B568"/>
+      <c r="C568"/>
+      <c r="D568"/>
+    </row>
+    <row r="569" spans="1:5">
+      <c r="A569"/>
+      <c r="B569"/>
+      <c r="C569"/>
+      <c r="D569"/>
+    </row>
+    <row r="570" spans="1:5">
+      <c r="A570"/>
+      <c r="B570"/>
+      <c r="C570"/>
+      <c r="D570"/>
+    </row>
+    <row r="571" spans="1:5">
+      <c r="A571"/>
+      <c r="B571"/>
+      <c r="C571"/>
+      <c r="D571"/>
+    </row>
+    <row r="572" spans="1:5">
+      <c r="A572"/>
+      <c r="B572"/>
+      <c r="C572"/>
+      <c r="D572"/>
+    </row>
+    <row r="573" spans="1:5">
+      <c r="A573"/>
+      <c r="B573"/>
+      <c r="C573"/>
+      <c r="D573"/>
+    </row>
+    <row r="574" spans="1:5">
+      <c r="A574"/>
+      <c r="B574"/>
+      <c r="C574"/>
+      <c r="D574"/>
+    </row>
+    <row r="575" spans="1:5">
+      <c r="A575"/>
+      <c r="B575"/>
+      <c r="C575"/>
+      <c r="D575"/>
+    </row>
+    <row r="576" spans="1:5">
+      <c r="A576"/>
+      <c r="B576"/>
+      <c r="C576"/>
+      <c r="D576"/>
+    </row>
+    <row r="577" spans="1:5">
+      <c r="A577"/>
+      <c r="B577"/>
+      <c r="C577"/>
+      <c r="D577"/>
+    </row>
+    <row r="578" spans="1:5">
+      <c r="A578"/>
+      <c r="B578"/>
+      <c r="C578"/>
+      <c r="D578"/>
+    </row>
+    <row r="579" spans="1:5">
+      <c r="A579"/>
+      <c r="B579"/>
+      <c r="C579"/>
+      <c r="D579"/>
+    </row>
+    <row r="580" spans="1:5">
+      <c r="A580"/>
+      <c r="B580"/>
+      <c r="C580"/>
+      <c r="D580"/>
+    </row>
+    <row r="581" spans="1:5">
+      <c r="A581"/>
+      <c r="B581"/>
+      <c r="C581"/>
+      <c r="D581"/>
+    </row>
+    <row r="582" spans="1:5">
+      <c r="A582"/>
+      <c r="B582"/>
+      <c r="C582"/>
+      <c r="D582"/>
+    </row>
+    <row r="583" spans="1:5">
+      <c r="A583"/>
+      <c r="B583"/>
+      <c r="C583"/>
+      <c r="D583"/>
+    </row>
+    <row r="584" spans="1:5">
+      <c r="A584"/>
+      <c r="B584"/>
+      <c r="C584"/>
+      <c r="D584"/>
+    </row>
+    <row r="585" spans="1:5">
+      <c r="A585"/>
+      <c r="B585"/>
+      <c r="C585"/>
+      <c r="D585"/>
+    </row>
+    <row r="586" spans="1:5">
+      <c r="A586"/>
+      <c r="B586"/>
+      <c r="C586"/>
+      <c r="D586"/>
+    </row>
+    <row r="587" spans="1:5">
+      <c r="A587"/>
+      <c r="B587"/>
+      <c r="C587"/>
+      <c r="D587"/>
+    </row>
+    <row r="588" spans="1:5">
+      <c r="A588"/>
+      <c r="B588"/>
+      <c r="C588"/>
+      <c r="D588"/>
+    </row>
+    <row r="589" spans="1:5">
+      <c r="A589"/>
+      <c r="B589"/>
+      <c r="C589"/>
+      <c r="D589"/>
+    </row>
+    <row r="590" spans="1:5">
+      <c r="A590"/>
+      <c r="B590"/>
+      <c r="C590"/>
+      <c r="D590"/>
+    </row>
+    <row r="591" spans="1:5">
+      <c r="A591"/>
+      <c r="B591"/>
+      <c r="C591"/>
+      <c r="D591"/>
+    </row>
+    <row r="592" spans="1:5">
+      <c r="A592"/>
+      <c r="B592"/>
+      <c r="C592"/>
+      <c r="D592"/>
+    </row>
+    <row r="593" spans="1:5">
+      <c r="A593"/>
+      <c r="B593"/>
+      <c r="C593"/>
+      <c r="D593"/>
+    </row>
+    <row r="594" spans="1:5">
+      <c r="A594"/>
+      <c r="B594"/>
+      <c r="C594"/>
+      <c r="D594"/>
+    </row>
+    <row r="595" spans="1:5">
+      <c r="A595"/>
+      <c r="B595"/>
+      <c r="C595"/>
+      <c r="D595"/>
+    </row>
+    <row r="596" spans="1:5">
+      <c r="A596"/>
+      <c r="B596"/>
+      <c r="C596"/>
+      <c r="D596"/>
+    </row>
+    <row r="597" spans="1:5">
+      <c r="A597"/>
+      <c r="B597"/>
+      <c r="C597"/>
+      <c r="D597"/>
+    </row>
+    <row r="598" spans="1:5">
+      <c r="A598"/>
+      <c r="B598"/>
+      <c r="C598"/>
+      <c r="D598"/>
+    </row>
+    <row r="599" spans="1:5">
+      <c r="A599"/>
+      <c r="B599"/>
+      <c r="C599"/>
+      <c r="D599"/>
+    </row>
+    <row r="600" spans="1:5">
+      <c r="A600"/>
+      <c r="B600"/>
+      <c r="C600"/>
+      <c r="D600"/>
+    </row>
+    <row r="601" spans="1:5">
+      <c r="A601"/>
+      <c r="B601"/>
+      <c r="C601"/>
+      <c r="D601"/>
+    </row>
+    <row r="602" spans="1:5">
+      <c r="A602"/>
+      <c r="B602"/>
+      <c r="C602"/>
+      <c r="D602"/>
+    </row>
+    <row r="603" spans="1:5">
+      <c r="A603"/>
+      <c r="B603"/>
+      <c r="C603"/>
+      <c r="D603"/>
+    </row>
+    <row r="604" spans="1:5">
+      <c r="A604"/>
+      <c r="B604"/>
+      <c r="C604"/>
+      <c r="D604"/>
+    </row>
+    <row r="605" spans="1:5">
+      <c r="A605"/>
+      <c r="B605"/>
+      <c r="C605"/>
+      <c r="D605"/>
+    </row>
+    <row r="606" spans="1:5">
+      <c r="A606"/>
+      <c r="B606"/>
+      <c r="C606"/>
+      <c r="D606"/>
+    </row>
+    <row r="607" spans="1:5">
+      <c r="A607"/>
+      <c r="B607"/>
+      <c r="C607"/>
+      <c r="D607"/>
+    </row>
+    <row r="608" spans="1:5">
+      <c r="A608"/>
+      <c r="B608"/>
+      <c r="C608"/>
+      <c r="D608"/>
+    </row>
+    <row r="609" spans="1:5">
+      <c r="A609"/>
+      <c r="B609"/>
+      <c r="C609"/>
+      <c r="D609"/>
+    </row>
+    <row r="610" spans="1:5">
+      <c r="A610"/>
+      <c r="B610"/>
+      <c r="C610"/>
+      <c r="D610"/>
+    </row>
+    <row r="611" spans="1:5">
+      <c r="A611"/>
+      <c r="B611"/>
+      <c r="C611"/>
+      <c r="D611"/>
+    </row>
+    <row r="612" spans="1:5">
+      <c r="A612"/>
+      <c r="B612"/>
+      <c r="C612"/>
+      <c r="D612"/>
+    </row>
+    <row r="613" spans="1:5">
+      <c r="A613"/>
+      <c r="B613"/>
+      <c r="C613"/>
+      <c r="D613"/>
+    </row>
+    <row r="614" spans="1:5">
+      <c r="A614"/>
+      <c r="B614"/>
+      <c r="C614"/>
+      <c r="D614"/>
+    </row>
+    <row r="615" spans="1:5">
+      <c r="A615"/>
+      <c r="B615"/>
+      <c r="C615"/>
+      <c r="D615"/>
+    </row>
+    <row r="616" spans="1:5">
+      <c r="A616"/>
+      <c r="B616"/>
+      <c r="C616"/>
+      <c r="D616"/>
+    </row>
+    <row r="617" spans="1:5">
+      <c r="A617"/>
+      <c r="B617"/>
+      <c r="C617"/>
+      <c r="D617"/>
+    </row>
+    <row r="618" spans="1:5">
+      <c r="A618"/>
+      <c r="B618"/>
+      <c r="C618"/>
+      <c r="D618"/>
+    </row>
+    <row r="619" spans="1:5">
+      <c r="A619"/>
+      <c r="B619"/>
+      <c r="C619"/>
+      <c r="D619"/>
+    </row>
+    <row r="620" spans="1:5">
+      <c r="A620"/>
+      <c r="B620"/>
+      <c r="C620"/>
+      <c r="D620"/>
+    </row>
+    <row r="621" spans="1:5">
+      <c r="A621"/>
+      <c r="B621"/>
+      <c r="C621"/>
+      <c r="D621"/>
+    </row>
+    <row r="622" spans="1:5">
+      <c r="A622"/>
+      <c r="B622"/>
+      <c r="C622"/>
+      <c r="D622"/>
+    </row>
+    <row r="623" spans="1:5">
+      <c r="A623"/>
+      <c r="B623"/>
+      <c r="C623"/>
+      <c r="D623"/>
+    </row>
+    <row r="624" spans="1:5">
+      <c r="A624"/>
+      <c r="B624"/>
+      <c r="C624"/>
+      <c r="D624"/>
+    </row>
+    <row r="625" spans="1:5">
+      <c r="A625"/>
+      <c r="B625"/>
+      <c r="C625"/>
+      <c r="D625"/>
+    </row>
+    <row r="626" spans="1:5">
+      <c r="A626"/>
+      <c r="B626"/>
+      <c r="C626"/>
+      <c r="D626"/>
+    </row>
+    <row r="627" spans="1:5">
+      <c r="A627"/>
+      <c r="B627"/>
+      <c r="C627"/>
+      <c r="D627"/>
+    </row>
+    <row r="628" spans="1:5">
+      <c r="A628"/>
+      <c r="B628"/>
+      <c r="C628"/>
+      <c r="D628"/>
+    </row>
+    <row r="629" spans="1:5">
+      <c r="A629"/>
+      <c r="B629"/>
+      <c r="C629"/>
+      <c r="D629"/>
+    </row>
+    <row r="630" spans="1:5">
+      <c r="A630"/>
+      <c r="B630"/>
+      <c r="C630"/>
+      <c r="D630"/>
+    </row>
+    <row r="631" spans="1:5">
+      <c r="A631"/>
+      <c r="B631"/>
+      <c r="C631"/>
+      <c r="D631"/>
+    </row>
+    <row r="632" spans="1:5">
+      <c r="A632"/>
+      <c r="B632"/>
+      <c r="C632"/>
+      <c r="D632"/>
+    </row>
+    <row r="633" spans="1:5">
+      <c r="A633"/>
+      <c r="B633"/>
+      <c r="C633"/>
+      <c r="D633"/>
+    </row>
+    <row r="634" spans="1:5">
+      <c r="A634"/>
+      <c r="B634"/>
+      <c r="C634"/>
+      <c r="D634"/>
+    </row>
+    <row r="635" spans="1:5">
+      <c r="A635"/>
+      <c r="B635"/>
+      <c r="C635"/>
+      <c r="D635"/>
+    </row>
+    <row r="636" spans="1:5">
+      <c r="A636"/>
+      <c r="B636"/>
+      <c r="C636"/>
+      <c r="D636"/>
+    </row>
+    <row r="637" spans="1:5">
+      <c r="A637"/>
+      <c r="B637"/>
+      <c r="C637"/>
+      <c r="D637"/>
+    </row>
+    <row r="638" spans="1:5">
+      <c r="A638"/>
+      <c r="B638"/>
+      <c r="C638"/>
+      <c r="D638"/>
+    </row>
+    <row r="639" spans="1:5">
+      <c r="A639"/>
+      <c r="B639"/>
+      <c r="C639"/>
+      <c r="D639"/>
+    </row>
+    <row r="640" spans="1:5">
+      <c r="A640"/>
+      <c r="B640"/>
+      <c r="C640"/>
+      <c r="D640"/>
+    </row>
+    <row r="641" spans="1:5">
+      <c r="A641"/>
+      <c r="B641"/>
+      <c r="C641"/>
+      <c r="D641"/>
+    </row>
+    <row r="642" spans="1:5">
+      <c r="A642"/>
+      <c r="B642"/>
+      <c r="C642"/>
+      <c r="D642"/>
+    </row>
+    <row r="643" spans="1:5">
+      <c r="A643"/>
+      <c r="B643"/>
+      <c r="C643"/>
+      <c r="D643"/>
+    </row>
+    <row r="644" spans="1:5">
+      <c r="A644"/>
+      <c r="B644"/>
+      <c r="C644"/>
+      <c r="D644"/>
+    </row>
+    <row r="645" spans="1:5">
+      <c r="A645"/>
+      <c r="B645"/>
+      <c r="C645"/>
+      <c r="D645"/>
+    </row>
+    <row r="646" spans="1:5">
+      <c r="A646"/>
+      <c r="B646"/>
+      <c r="C646"/>
+      <c r="D646"/>
+    </row>
+    <row r="647" spans="1:5">
+      <c r="A647"/>
+      <c r="B647"/>
+      <c r="C647"/>
+      <c r="D647"/>
+    </row>
+    <row r="648" spans="1:5">
+      <c r="A648"/>
+      <c r="B648"/>
+      <c r="C648"/>
+      <c r="D648"/>
+    </row>
+    <row r="649" spans="1:5">
+      <c r="A649"/>
+      <c r="B649"/>
+      <c r="C649"/>
+      <c r="D649"/>
+    </row>
+    <row r="650" spans="1:5">
+      <c r="A650"/>
+      <c r="B650"/>
+      <c r="C650"/>
+      <c r="D650"/>
+    </row>
+    <row r="651" spans="1:5">
+      <c r="A651"/>
+      <c r="B651"/>
+      <c r="C651"/>
+      <c r="D651"/>
+    </row>
+    <row r="652" spans="1:5">
+      <c r="A652"/>
+      <c r="B652"/>
+      <c r="C652"/>
+      <c r="D652"/>
+    </row>
+    <row r="653" spans="1:5">
+      <c r="A653"/>
+      <c r="B653"/>
+      <c r="C653"/>
+      <c r="D653"/>
+    </row>
+    <row r="654" spans="1:5">
+      <c r="A654"/>
+      <c r="B654"/>
+      <c r="C654"/>
+      <c r="D654"/>
+    </row>
+    <row r="655" spans="1:5">
+      <c r="A655"/>
+      <c r="B655"/>
+      <c r="C655"/>
+      <c r="D655"/>
+    </row>
+    <row r="656" spans="1:5">
+      <c r="A656"/>
+      <c r="B656"/>
+      <c r="C656"/>
+      <c r="D656"/>
+    </row>
+    <row r="657" spans="1:5">
+      <c r="A657"/>
+      <c r="B657"/>
+      <c r="C657"/>
+      <c r="D657"/>
+    </row>
+    <row r="658" spans="1:5">
+      <c r="A658"/>
+      <c r="B658"/>
+      <c r="C658"/>
+      <c r="D658"/>
+    </row>
+    <row r="659" spans="1:5">
+      <c r="A659"/>
+      <c r="B659"/>
+      <c r="C659"/>
+      <c r="D659"/>
+    </row>
+    <row r="660" spans="1:5">
+      <c r="A660"/>
+      <c r="B660"/>
+      <c r="C660"/>
+      <c r="D660"/>
+    </row>
+    <row r="661" spans="1:5">
+      <c r="A661"/>
+      <c r="B661"/>
+      <c r="C661"/>
+      <c r="D661"/>
+    </row>
+    <row r="662" spans="1:5">
+      <c r="A662"/>
+      <c r="B662"/>
+      <c r="C662"/>
+      <c r="D662"/>
+    </row>
+    <row r="663" spans="1:5">
+      <c r="A663"/>
+      <c r="B663"/>
+      <c r="C663"/>
+      <c r="D663"/>
+    </row>
+    <row r="664" spans="1:5">
+      <c r="A664"/>
+      <c r="B664"/>
+      <c r="C664"/>
+      <c r="D664"/>
+    </row>
+    <row r="665" spans="1:5">
+      <c r="A665"/>
+      <c r="B665"/>
+      <c r="C665"/>
+      <c r="D665"/>
+    </row>
+    <row r="666" spans="1:5">
+      <c r="A666"/>
+      <c r="B666"/>
+      <c r="C666"/>
+      <c r="D666"/>
+    </row>
+    <row r="667" spans="1:5">
+      <c r="A667"/>
+      <c r="B667"/>
+      <c r="C667"/>
+      <c r="D667"/>
+    </row>
+    <row r="668" spans="1:5">
+      <c r="A668"/>
+      <c r="B668"/>
+      <c r="C668"/>
+      <c r="D668"/>
+    </row>
+    <row r="669" spans="1:5">
+      <c r="A669"/>
+      <c r="B669"/>
+      <c r="C669"/>
+      <c r="D669"/>
+    </row>
+    <row r="670" spans="1:5">
+      <c r="A670"/>
+      <c r="B670"/>
+      <c r="C670"/>
+      <c r="D670"/>
+    </row>
+    <row r="671" spans="1:5">
+      <c r="A671"/>
+      <c r="B671"/>
+      <c r="C671"/>
+      <c r="D671"/>
+    </row>
+    <row r="672" spans="1:5">
+      <c r="A672"/>
+      <c r="B672"/>
+      <c r="C672"/>
+      <c r="D672"/>
+    </row>
+    <row r="673" spans="1:5">
+      <c r="A673"/>
+      <c r="B673"/>
+      <c r="C673"/>
+      <c r="D673"/>
+    </row>
+    <row r="674" spans="1:5">
+      <c r="A674"/>
+      <c r="B674"/>
+      <c r="C674"/>
+      <c r="D674"/>
+    </row>
+    <row r="675" spans="1:5">
+      <c r="A675"/>
+      <c r="B675"/>
+      <c r="C675"/>
+      <c r="D675"/>
+    </row>
+    <row r="676" spans="1:5">
+      <c r="A676"/>
+      <c r="B676"/>
+      <c r="C676"/>
+      <c r="D676"/>
+    </row>
+    <row r="677" spans="1:5">
+      <c r="A677"/>
+      <c r="B677"/>
+      <c r="C677"/>
+      <c r="D677"/>
+    </row>
+    <row r="678" spans="1:5">
+      <c r="A678"/>
+      <c r="B678"/>
+      <c r="C678"/>
+      <c r="D678"/>
+    </row>
+    <row r="679" spans="1:5">
+      <c r="A679"/>
+      <c r="B679"/>
+      <c r="C679"/>
+      <c r="D679"/>
+    </row>
+    <row r="680" spans="1:5">
+      <c r="A680"/>
+      <c r="B680"/>
+      <c r="C680"/>
+      <c r="D680"/>
+    </row>
+    <row r="681" spans="1:5">
+      <c r="A681"/>
+      <c r="B681"/>
+      <c r="C681"/>
+      <c r="D681"/>
+    </row>
+    <row r="682" spans="1:5">
+      <c r="A682"/>
+      <c r="B682"/>
+      <c r="C682"/>
+      <c r="D682"/>
+    </row>
+    <row r="683" spans="1:5">
+      <c r="A683"/>
+      <c r="B683"/>
+      <c r="C683"/>
+      <c r="D683"/>
+    </row>
+    <row r="684" spans="1:5">
+      <c r="A684"/>
+      <c r="B684"/>
+      <c r="C684"/>
+      <c r="D684"/>
+    </row>
+    <row r="685" spans="1:5">
+      <c r="A685"/>
+      <c r="B685"/>
+      <c r="C685"/>
+      <c r="D685"/>
+    </row>
+    <row r="686" spans="1:5">
+      <c r="A686"/>
+      <c r="B686"/>
+      <c r="C686"/>
+      <c r="D686"/>
+    </row>
+    <row r="687" spans="1:5">
+      <c r="A687"/>
+      <c r="B687"/>
+      <c r="C687"/>
+      <c r="D687"/>
+    </row>
+    <row r="688" spans="1:5">
+      <c r="A688"/>
+      <c r="B688"/>
+      <c r="C688"/>
+      <c r="D688"/>
+    </row>
+    <row r="689" spans="1:5">
+      <c r="A689"/>
+      <c r="B689"/>
+      <c r="C689"/>
+      <c r="D689"/>
+    </row>
+    <row r="690" spans="1:5">
+      <c r="A690"/>
+      <c r="B690"/>
+      <c r="C690"/>
+      <c r="D690"/>
+    </row>
+    <row r="691" spans="1:5">
+      <c r="A691"/>
+      <c r="B691"/>
+      <c r="C691"/>
+      <c r="D691"/>
+    </row>
+    <row r="692" spans="1:5">
+      <c r="A692"/>
+      <c r="B692"/>
+      <c r="C692"/>
+      <c r="D692"/>
+    </row>
+    <row r="693" spans="1:5">
+      <c r="A693"/>
+      <c r="B693"/>
+      <c r="C693"/>
+      <c r="D693"/>
+    </row>
+    <row r="694" spans="1:5">
+      <c r="A694"/>
+      <c r="B694"/>
+      <c r="C694"/>
+      <c r="D694"/>
+    </row>
+    <row r="695" spans="1:5">
+      <c r="A695"/>
+      <c r="B695"/>
+      <c r="C695"/>
+      <c r="D695"/>
+    </row>
+    <row r="696" spans="1:5">
+      <c r="A696"/>
+      <c r="B696"/>
+      <c r="C696"/>
+      <c r="D696"/>
+    </row>
+    <row r="697" spans="1:5">
+      <c r="A697"/>
+      <c r="B697"/>
+      <c r="C697"/>
+      <c r="D697"/>
+    </row>
+    <row r="698" spans="1:5">
+      <c r="A698"/>
+      <c r="B698"/>
+      <c r="C698"/>
+      <c r="D698"/>
+    </row>
+    <row r="699" spans="1:5">
+      <c r="A699"/>
+      <c r="B699"/>
+      <c r="C699"/>
+      <c r="D699"/>
+    </row>
+    <row r="700" spans="1:5">
+      <c r="A700"/>
+      <c r="B700"/>
+      <c r="C700"/>
+      <c r="D700"/>
+    </row>
+    <row r="701" spans="1:5">
+      <c r="A701"/>
+      <c r="B701"/>
+      <c r="C701"/>
+      <c r="D701"/>
+    </row>
+    <row r="702" spans="1:5">
+      <c r="A702"/>
+      <c r="B702"/>
+      <c r="C702"/>
+      <c r="D702"/>
+    </row>
+    <row r="703" spans="1:5">
+      <c r="A703"/>
+      <c r="B703"/>
+      <c r="C703"/>
+      <c r="D703"/>
+    </row>
+    <row r="704" spans="1:5">
+      <c r="A704"/>
+      <c r="B704"/>
+      <c r="C704"/>
+      <c r="D704"/>
+    </row>
+    <row r="705" spans="1:5">
+      <c r="A705"/>
+      <c r="B705"/>
+      <c r="C705"/>
+      <c r="D705"/>
+    </row>
+    <row r="706" spans="1:5">
+      <c r="A706"/>
+      <c r="B706"/>
+      <c r="C706"/>
+      <c r="D706"/>
+    </row>
+    <row r="707" spans="1:5">
+      <c r="A707"/>
+      <c r="B707"/>
+      <c r="C707"/>
+      <c r="D707"/>
+    </row>
+    <row r="708" spans="1:5">
+      <c r="A708"/>
+      <c r="B708"/>
+      <c r="C708"/>
+      <c r="D708"/>
+    </row>
+    <row r="709" spans="1:5">
+      <c r="A709"/>
+      <c r="B709"/>
+      <c r="C709"/>
+      <c r="D709"/>
+    </row>
+    <row r="710" spans="1:5">
+      <c r="A710"/>
+      <c r="B710"/>
+      <c r="C710"/>
+      <c r="D710"/>
+    </row>
+    <row r="711" spans="1:5">
+      <c r="A711"/>
+      <c r="B711"/>
+      <c r="C711"/>
+      <c r="D711"/>
+    </row>
+    <row r="712" spans="1:5">
+      <c r="A712"/>
+      <c r="B712"/>
+      <c r="C712"/>
+      <c r="D712"/>
+    </row>
+    <row r="713" spans="1:5">
+      <c r="A713"/>
+      <c r="B713"/>
+      <c r="C713"/>
+      <c r="D713"/>
+    </row>
+    <row r="714" spans="1:5">
+      <c r="A714"/>
+      <c r="B714"/>
+      <c r="C714"/>
+      <c r="D714"/>
+    </row>
+    <row r="715" spans="1:5">
+      <c r="A715"/>
+      <c r="B715"/>
+      <c r="C715"/>
+      <c r="D715"/>
+    </row>
+    <row r="716" spans="1:5">
+      <c r="A716"/>
+      <c r="B716"/>
+      <c r="C716"/>
+      <c r="D716"/>
+    </row>
+    <row r="717" spans="1:5">
+      <c r="A717"/>
+      <c r="B717"/>
+      <c r="C717"/>
+      <c r="D717"/>
+    </row>
+    <row r="718" spans="1:5">
+      <c r="A718"/>
+      <c r="B718"/>
+      <c r="C718"/>
+      <c r="D718"/>
+    </row>
+    <row r="719" spans="1:5">
+      <c r="A719"/>
+      <c r="B719"/>
+      <c r="C719"/>
+      <c r="D719"/>
+    </row>
+    <row r="720" spans="1:5">
+      <c r="A720"/>
+      <c r="B720"/>
+      <c r="C720"/>
+      <c r="D720"/>
+    </row>
+    <row r="721" spans="1:5">
+      <c r="A721"/>
+      <c r="B721"/>
+      <c r="C721"/>
+      <c r="D721"/>
+    </row>
+    <row r="722" spans="1:5">
+      <c r="A722"/>
+      <c r="B722"/>
+      <c r="C722"/>
+      <c r="D722"/>
+    </row>
+    <row r="723" spans="1:5">
+      <c r="A723"/>
+      <c r="B723"/>
+      <c r="C723"/>
+      <c r="D723"/>
+    </row>
+    <row r="724" spans="1:5">
+      <c r="A724"/>
+      <c r="B724"/>
+      <c r="C724"/>
+      <c r="D724"/>
+    </row>
+    <row r="725" spans="1:5">
+      <c r="A725"/>
+      <c r="B725"/>
+      <c r="C725"/>
+      <c r="D725"/>
+    </row>
+    <row r="726" spans="1:5">
+      <c r="A726"/>
+      <c r="B726"/>
+      <c r="C726"/>
+      <c r="D726"/>
+    </row>
+    <row r="727" spans="1:5">
+      <c r="A727"/>
+      <c r="B727"/>
+      <c r="C727"/>
+      <c r="D727"/>
+    </row>
+    <row r="728" spans="1:5">
+      <c r="A728"/>
+      <c r="B728"/>
+      <c r="C728"/>
+      <c r="D728"/>
+    </row>
+    <row r="729" spans="1:5">
+      <c r="A729"/>
+      <c r="B729"/>
+      <c r="C729"/>
+      <c r="D729"/>
+    </row>
+    <row r="730" spans="1:5">
+      <c r="A730"/>
+      <c r="B730"/>
+      <c r="C730"/>
+      <c r="D730"/>
+    </row>
+    <row r="731" spans="1:5">
+      <c r="A731"/>
+      <c r="B731"/>
+      <c r="C731"/>
+      <c r="D731"/>
+    </row>
+    <row r="732" spans="1:5">
+      <c r="A732"/>
+      <c r="B732"/>
+      <c r="C732"/>
+      <c r="D732"/>
+    </row>
+    <row r="733" spans="1:5">
+      <c r="A733"/>
+      <c r="B733"/>
+      <c r="C733"/>
+      <c r="D733"/>
+    </row>
+    <row r="734" spans="1:5">
+      <c r="A734"/>
+      <c r="B734"/>
+      <c r="C734"/>
+      <c r="D734"/>
+    </row>
+    <row r="735" spans="1:5">
+      <c r="A735"/>
+      <c r="B735"/>
+      <c r="C735"/>
+      <c r="D735"/>
+    </row>
+    <row r="736" spans="1:5">
+      <c r="A736"/>
+      <c r="B736"/>
+      <c r="C736"/>
+      <c r="D736"/>
+    </row>
+    <row r="737" spans="1:5">
+      <c r="A737"/>
+      <c r="B737"/>
+      <c r="C737"/>
+      <c r="D737"/>
+    </row>
+    <row r="738" spans="1:5">
+      <c r="A738"/>
+      <c r="B738"/>
+      <c r="C738"/>
+      <c r="D738"/>
+    </row>
+    <row r="739" spans="1:5">
+      <c r="A739"/>
+      <c r="B739"/>
+      <c r="C739"/>
+      <c r="D739"/>
+    </row>
+    <row r="740" spans="1:5">
+      <c r="A740"/>
+      <c r="B740"/>
+      <c r="C740"/>
+      <c r="D740"/>
+    </row>
+    <row r="741" spans="1:5">
+      <c r="A741"/>
+      <c r="B741"/>
+      <c r="C741"/>
+      <c r="D741"/>
+    </row>
+    <row r="742" spans="1:5">
+      <c r="A742"/>
+      <c r="B742"/>
+      <c r="C742"/>
+      <c r="D742"/>
+    </row>
+    <row r="743" spans="1:5">
+      <c r="A743"/>
+      <c r="B743"/>
+      <c r="C743"/>
+      <c r="D743"/>
+    </row>
+    <row r="744" spans="1:5">
+      <c r="A744"/>
+      <c r="B744"/>
+      <c r="C744"/>
+      <c r="D744"/>
+    </row>
+    <row r="745" spans="1:5">
+      <c r="A745"/>
+      <c r="B745"/>
+      <c r="C745"/>
+      <c r="D745"/>
+    </row>
+    <row r="746" spans="1:5">
+      <c r="A746"/>
+      <c r="B746"/>
+      <c r="C746"/>
+      <c r="D746"/>
+    </row>
+    <row r="747" spans="1:5">
+      <c r="A747"/>
+      <c r="B747"/>
+      <c r="C747"/>
+      <c r="D747"/>
+    </row>
+    <row r="748" spans="1:5">
+      <c r="A748"/>
+      <c r="B748"/>
+      <c r="C748"/>
+      <c r="D748"/>
+    </row>
+    <row r="749" spans="1:5">
+      <c r="A749"/>
+      <c r="B749"/>
+      <c r="C749"/>
+      <c r="D749"/>
+    </row>
+    <row r="750" spans="1:5">
+      <c r="A750"/>
+      <c r="B750"/>
+      <c r="C750"/>
+      <c r="D750"/>
+    </row>
+    <row r="751" spans="1:5">
+      <c r="A751"/>
+      <c r="B751"/>
+      <c r="C751"/>
+      <c r="D751"/>
+    </row>
+    <row r="752" spans="1:5">
+      <c r="A752"/>
+      <c r="B752"/>
+      <c r="C752"/>
+      <c r="D752"/>
+    </row>
+    <row r="753" spans="1:5">
+      <c r="A753"/>
+      <c r="B753"/>
+      <c r="C753"/>
+      <c r="D753"/>
+    </row>
+    <row r="754" spans="1:5">
+      <c r="A754"/>
+      <c r="B754"/>
+      <c r="C754"/>
+      <c r="D754"/>
+    </row>
+    <row r="755" spans="1:5">
+      <c r="A755"/>
+      <c r="B755"/>
+      <c r="C755"/>
+      <c r="D755"/>
+    </row>
+    <row r="756" spans="1:5">
+      <c r="A756"/>
+      <c r="B756"/>
+      <c r="C756"/>
+      <c r="D756"/>
+    </row>
+    <row r="757" spans="1:5">
+      <c r="A757"/>
+      <c r="B757"/>
+      <c r="C757"/>
+      <c r="D757"/>
+    </row>
+    <row r="758" spans="1:5">
+      <c r="A758"/>
+      <c r="B758"/>
+      <c r="C758"/>
+      <c r="D758"/>
+    </row>
+    <row r="759" spans="1:5">
+      <c r="A759"/>
+      <c r="B759"/>
+      <c r="C759"/>
+      <c r="D759"/>
+    </row>
+    <row r="760" spans="1:5">
+      <c r="A760"/>
+      <c r="B760"/>
+      <c r="C760"/>
+      <c r="D760"/>
+    </row>
+    <row r="761" spans="1:5">
+      <c r="A761"/>
+      <c r="B761"/>
+      <c r="C761"/>
+      <c r="D761"/>
+    </row>
+    <row r="762" spans="1:5">
+      <c r="A762"/>
+      <c r="B762"/>
+      <c r="C762"/>
+      <c r="D762"/>
+    </row>
+    <row r="763" spans="1:5">
+      <c r="A763"/>
+      <c r="B763"/>
+      <c r="C763"/>
+      <c r="D763"/>
+    </row>
+    <row r="764" spans="1:5">
+      <c r="A764"/>
+      <c r="B764"/>
+      <c r="C764"/>
+      <c r="D764"/>
+    </row>
+    <row r="765" spans="1:5">
+      <c r="A765"/>
+      <c r="B765"/>
+      <c r="C765"/>
+      <c r="D765"/>
+    </row>
+    <row r="766" spans="1:5">
+      <c r="A766"/>
+      <c r="B766"/>
+      <c r="C766"/>
+      <c r="D766"/>
+    </row>
+    <row r="767" spans="1:5">
+      <c r="A767"/>
+      <c r="B767"/>
+      <c r="C767"/>
+      <c r="D767"/>
+    </row>
+    <row r="768" spans="1:5">
+      <c r="A768"/>
+      <c r="B768"/>
+      <c r="C768"/>
+      <c r="D768"/>
+    </row>
+    <row r="769" spans="1:5">
+      <c r="A769"/>
+      <c r="B769"/>
+      <c r="C769"/>
+      <c r="D769"/>
+    </row>
+    <row r="770" spans="1:5">
+      <c r="A770"/>
+      <c r="B770"/>
+      <c r="C770"/>
+      <c r="D770"/>
+    </row>
+    <row r="771" spans="1:5">
+      <c r="A771"/>
+      <c r="B771"/>
+      <c r="C771"/>
+      <c r="D771"/>
+    </row>
+    <row r="772" spans="1:5">
+      <c r="A772"/>
+      <c r="B772"/>
+      <c r="C772"/>
+      <c r="D772"/>
+    </row>
+    <row r="773" spans="1:5">
+      <c r="A773"/>
+      <c r="B773"/>
+      <c r="C773"/>
+      <c r="D773"/>
+    </row>
+    <row r="774" spans="1:5">
+      <c r="A774"/>
+      <c r="B774"/>
+      <c r="C774"/>
+      <c r="D774"/>
+    </row>
+    <row r="775" spans="1:5">
+      <c r="A775"/>
+      <c r="B775"/>
+      <c r="C775"/>
+      <c r="D775"/>
+    </row>
+    <row r="776" spans="1:5">
+      <c r="A776"/>
+      <c r="B776"/>
+      <c r="C776"/>
+      <c r="D776"/>
+    </row>
+    <row r="777" spans="1:5">
+      <c r="A777"/>
+      <c r="B777"/>
+      <c r="C777"/>
+      <c r="D777"/>
+    </row>
+    <row r="778" spans="1:5">
+      <c r="A778"/>
+      <c r="B778"/>
+      <c r="C778"/>
+      <c r="D778"/>
+    </row>
+    <row r="779" spans="1:5">
+      <c r="A779"/>
+      <c r="B779"/>
+      <c r="C779"/>
+      <c r="D779"/>
+    </row>
+    <row r="780" spans="1:5">
+      <c r="A780"/>
+      <c r="B780"/>
+      <c r="C780"/>
+      <c r="D780"/>
+    </row>
+    <row r="781" spans="1:5">
+      <c r="A781"/>
+      <c r="B781"/>
+      <c r="C781"/>
+      <c r="D781"/>
+    </row>
+    <row r="782" spans="1:5">
+      <c r="A782"/>
+      <c r="B782"/>
+      <c r="C782"/>
+      <c r="D782"/>
+    </row>
+    <row r="783" spans="1:5">
+      <c r="A783"/>
+      <c r="B783"/>
+      <c r="C783"/>
+      <c r="D783"/>
+    </row>
+    <row r="784" spans="1:5">
+      <c r="A784"/>
+      <c r="B784"/>
+      <c r="C784"/>
+      <c r="D784"/>
+    </row>
+    <row r="785" spans="1:5">
+      <c r="A785"/>
+      <c r="B785"/>
+      <c r="C785"/>
+      <c r="D785"/>
+    </row>
+    <row r="786" spans="1:5">
+      <c r="A786"/>
+      <c r="B786"/>
+      <c r="C786"/>
+      <c r="D786"/>
+    </row>
+    <row r="787" spans="1:5">
+      <c r="A787"/>
+      <c r="B787"/>
+      <c r="C787"/>
+      <c r="D787"/>
+    </row>
+    <row r="788" spans="1:5">
+      <c r="A788"/>
+      <c r="B788"/>
+      <c r="C788"/>
+      <c r="D788"/>
+    </row>
+    <row r="789" spans="1:5">
+      <c r="A789"/>
+      <c r="B789"/>
+      <c r="C789"/>
+      <c r="D789"/>
+    </row>
+    <row r="790" spans="1:5">
+      <c r="A790"/>
+      <c r="B790"/>
+      <c r="C790"/>
+      <c r="D790"/>
+    </row>
+    <row r="791" spans="1:5">
+      <c r="A791"/>
+      <c r="B791"/>
+      <c r="C791"/>
+      <c r="D791"/>
+    </row>
+    <row r="792" spans="1:5">
+      <c r="A792"/>
+      <c r="B792"/>
+      <c r="C792"/>
+      <c r="D792"/>
+    </row>
+    <row r="793" spans="1:5">
+      <c r="A793"/>
+      <c r="B793"/>
+      <c r="C793"/>
+      <c r="D793"/>
+    </row>
+    <row r="794" spans="1:5">
+      <c r="A794"/>
+      <c r="B794"/>
+      <c r="C794"/>
+      <c r="D794"/>
+    </row>
+    <row r="795" spans="1:5">
+      <c r="A795"/>
+      <c r="B795"/>
+      <c r="C795"/>
+      <c r="D795"/>
+    </row>
+    <row r="796" spans="1:5">
+      <c r="A796"/>
+      <c r="B796"/>
+      <c r="C796"/>
+      <c r="D796"/>
+    </row>
+    <row r="797" spans="1:5">
+      <c r="A797"/>
+      <c r="B797"/>
+      <c r="C797"/>
+      <c r="D797"/>
+    </row>
+    <row r="798" spans="1:5">
+      <c r="A798"/>
+      <c r="B798"/>
+      <c r="C798"/>
+      <c r="D798"/>
+    </row>
+    <row r="799" spans="1:5">
+      <c r="A799"/>
+      <c r="B799"/>
+      <c r="C799"/>
+      <c r="D799"/>
+    </row>
+    <row r="800" spans="1:5">
+      <c r="A800"/>
+      <c r="B800"/>
+      <c r="C800"/>
+      <c r="D800"/>
+    </row>
+    <row r="801" spans="1:5">
+      <c r="A801"/>
+      <c r="B801"/>
+      <c r="C801"/>
+      <c r="D801"/>
+    </row>
+    <row r="802" spans="1:5">
+      <c r="A802"/>
+      <c r="B802"/>
+      <c r="C802"/>
+      <c r="D802"/>
+    </row>
+    <row r="803" spans="1:5">
+      <c r="A803"/>
+      <c r="B803"/>
+      <c r="C803"/>
+      <c r="D803"/>
+    </row>
+    <row r="804" spans="1:5">
+      <c r="A804"/>
+      <c r="B804"/>
+      <c r="C804"/>
+      <c r="D804"/>
+    </row>
+    <row r="805" spans="1:5">
+      <c r="A805"/>
+      <c r="B805"/>
+      <c r="C805"/>
+      <c r="D805"/>
+    </row>
+    <row r="806" spans="1:5">
+      <c r="A806"/>
+      <c r="B806"/>
+      <c r="C806"/>
+      <c r="D806"/>
+    </row>
+    <row r="807" spans="1:5">
+      <c r="A807"/>
+      <c r="B807"/>
+      <c r="C807"/>
+      <c r="D807"/>
+    </row>
+    <row r="808" spans="1:5">
+      <c r="A808"/>
+      <c r="B808"/>
+      <c r="C808"/>
+      <c r="D808"/>
+    </row>
+    <row r="809" spans="1:5">
+      <c r="A809"/>
+      <c r="B809"/>
+      <c r="C809"/>
+      <c r="D809"/>
+    </row>
+    <row r="810" spans="1:5">
+      <c r="A810"/>
+      <c r="B810"/>
+      <c r="C810"/>
+      <c r="D810"/>
+    </row>
+    <row r="811" spans="1:5">
+      <c r="A811"/>
+      <c r="B811"/>
+      <c r="C811"/>
+      <c r="D811"/>
+    </row>
+    <row r="812" spans="1:5">
+      <c r="A812"/>
+      <c r="B812"/>
+      <c r="C812"/>
+      <c r="D812"/>
+    </row>
+    <row r="813" spans="1:5">
+      <c r="A813"/>
+      <c r="B813"/>
+      <c r="C813"/>
+      <c r="D813"/>
+    </row>
+    <row r="814" spans="1:5">
+      <c r="A814"/>
+      <c r="B814"/>
+      <c r="C814"/>
+      <c r="D814"/>
+    </row>
+    <row r="815" spans="1:5">
+      <c r="A815"/>
+      <c r="B815"/>
+      <c r="C815"/>
+      <c r="D815"/>
+    </row>
+    <row r="816" spans="1:5">
+      <c r="A816"/>
+      <c r="B816"/>
+      <c r="C816"/>
+      <c r="D816"/>
+    </row>
+    <row r="817" spans="1:5">
+      <c r="A817"/>
+      <c r="B817"/>
+      <c r="C817"/>
+      <c r="D817"/>
+    </row>
+    <row r="818" spans="1:5">
+      <c r="A818"/>
+      <c r="B818"/>
+      <c r="C818"/>
+      <c r="D818"/>
+    </row>
+    <row r="819" spans="1:5">
+      <c r="A819"/>
+      <c r="B819"/>
+      <c r="C819"/>
+      <c r="D819"/>
+    </row>
+    <row r="820" spans="1:5">
+      <c r="A820"/>
+      <c r="B820"/>
+      <c r="C820"/>
+      <c r="D820"/>
+    </row>
+    <row r="821" spans="1:5">
+      <c r="A821"/>
+      <c r="B821"/>
+      <c r="C821"/>
+      <c r="D821"/>
+    </row>
+    <row r="822" spans="1:5">
+      <c r="A822"/>
+      <c r="B822"/>
+      <c r="C822"/>
+      <c r="D822"/>
+    </row>
+    <row r="823" spans="1:5">
+      <c r="A823"/>
+      <c r="B823"/>
+      <c r="C823"/>
+      <c r="D823"/>
+    </row>
+    <row r="824" spans="1:5">
+      <c r="A824"/>
+      <c r="B824"/>
+      <c r="C824"/>
+      <c r="D824"/>
+    </row>
+    <row r="825" spans="1:5">
+      <c r="A825"/>
+      <c r="B825"/>
+      <c r="C825"/>
+      <c r="D825"/>
+    </row>
+    <row r="826" spans="1:5">
+      <c r="A826"/>
+      <c r="B826"/>
+      <c r="C826"/>
+      <c r="D826"/>
+    </row>
+    <row r="827" spans="1:5">
+      <c r="A827"/>
+      <c r="B827"/>
+      <c r="C827"/>
+      <c r="D827"/>
+    </row>
+    <row r="828" spans="1:5">
+      <c r="A828"/>
+      <c r="B828"/>
+      <c r="C828"/>
+      <c r="D828"/>
+    </row>
+    <row r="829" spans="1:5">
+      <c r="A829"/>
+      <c r="B829"/>
+      <c r="C829"/>
+      <c r="D829"/>
+    </row>
+    <row r="830" spans="1:5">
+      <c r="A830"/>
+      <c r="B830"/>
+      <c r="C830"/>
+      <c r="D830"/>
+    </row>
+    <row r="831" spans="1:5">
+      <c r="A831"/>
+      <c r="B831"/>
+      <c r="C831"/>
+      <c r="D831"/>
+    </row>
+    <row r="832" spans="1:5">
+      <c r="A832"/>
+      <c r="B832"/>
+      <c r="C832"/>
+      <c r="D832"/>
+    </row>
+    <row r="833" spans="1:5">
+      <c r="A833"/>
+      <c r="B833"/>
+      <c r="C833"/>
+      <c r="D833"/>
+    </row>
+    <row r="834" spans="1:5">
+      <c r="A834"/>
+      <c r="B834"/>
+      <c r="C834"/>
+      <c r="D834"/>
+    </row>
+    <row r="835" spans="1:5">
+      <c r="A835"/>
+      <c r="B835"/>
+      <c r="C835"/>
+      <c r="D835"/>
+    </row>
+    <row r="836" spans="1:5">
+      <c r="A836"/>
+      <c r="B836"/>
+      <c r="C836"/>
+      <c r="D836"/>
+    </row>
+    <row r="837" spans="1:5">
+      <c r="A837"/>
+      <c r="B837"/>
+      <c r="C837"/>
+      <c r="D837"/>
+    </row>
+    <row r="838" spans="1:5">
+      <c r="A838"/>
+      <c r="B838"/>
+      <c r="C838"/>
+      <c r="D838"/>
+    </row>
+    <row r="839" spans="1:5">
+      <c r="A839"/>
+      <c r="B839"/>
+      <c r="C839"/>
+      <c r="D839"/>
+    </row>
+    <row r="840" spans="1:5">
+      <c r="A840"/>
+      <c r="B840"/>
+      <c r="C840"/>
+      <c r="D840"/>
+    </row>
+    <row r="841" spans="1:5">
+      <c r="A841"/>
+      <c r="B841"/>
+      <c r="C841"/>
+      <c r="D841"/>
+    </row>
+    <row r="842" spans="1:5">
+      <c r="A842"/>
+      <c r="B842"/>
+      <c r="C842"/>
+      <c r="D842"/>
+    </row>
+    <row r="843" spans="1:5">
+      <c r="A843"/>
+      <c r="B843"/>
+      <c r="C843"/>
+      <c r="D843"/>
+    </row>
+    <row r="844" spans="1:5">
+      <c r="A844"/>
+      <c r="B844"/>
+      <c r="C844"/>
+      <c r="D844"/>
+    </row>
+    <row r="845" spans="1:5">
+      <c r="A845"/>
+      <c r="B845"/>
+      <c r="C845"/>
+      <c r="D845"/>
+    </row>
+    <row r="846" spans="1:5">
+      <c r="A846"/>
+      <c r="B846"/>
+      <c r="C846"/>
+      <c r="D846"/>
+    </row>
+    <row r="847" spans="1:5">
+      <c r="A847"/>
+      <c r="B847"/>
+      <c r="C847"/>
+      <c r="D847"/>
+    </row>
+    <row r="848" spans="1:5">
+      <c r="A848"/>
+      <c r="B848"/>
+      <c r="C848"/>
+      <c r="D848"/>
+    </row>
+    <row r="849" spans="1:5">
+      <c r="A849"/>
+      <c r="B849"/>
+      <c r="C849"/>
+      <c r="D849"/>
+    </row>
+    <row r="850" spans="1:5">
+      <c r="A850"/>
+      <c r="B850"/>
+      <c r="C850"/>
+      <c r="D850"/>
+    </row>
+    <row r="851" spans="1:5">
+      <c r="A851"/>
+      <c r="B851"/>
+      <c r="C851"/>
+      <c r="D851"/>
+    </row>
+    <row r="852" spans="1:5">
+      <c r="A852"/>
+      <c r="B852"/>
+      <c r="C852"/>
+      <c r="D852"/>
+    </row>
+    <row r="853" spans="1:5">
+      <c r="A853"/>
+      <c r="B853"/>
+      <c r="C853"/>
+      <c r="D853"/>
+    </row>
+    <row r="854" spans="1:5">
+      <c r="A854"/>
+      <c r="B854"/>
+      <c r="C854"/>
+      <c r="D854"/>
+    </row>
+    <row r="855" spans="1:5">
+      <c r="A855"/>
+      <c r="B855"/>
+      <c r="C855"/>
+      <c r="D855"/>
+    </row>
+    <row r="856" spans="1:5">
+      <c r="A856"/>
+      <c r="B856"/>
+      <c r="C856"/>
+      <c r="D856"/>
+    </row>
+    <row r="857" spans="1:5">
+      <c r="A857"/>
+      <c r="B857"/>
+      <c r="C857"/>
+      <c r="D857"/>
+    </row>
+    <row r="858" spans="1:5">
+      <c r="A858"/>
+      <c r="B858"/>
+      <c r="C858"/>
+      <c r="D858"/>
+    </row>
+    <row r="859" spans="1:5">
+      <c r="A859"/>
+      <c r="B859"/>
+      <c r="C859"/>
+      <c r="D859"/>
+    </row>
+    <row r="860" spans="1:5">
+      <c r="A860"/>
+      <c r="B860"/>
+      <c r="C860"/>
+      <c r="D860"/>
+    </row>
+    <row r="861" spans="1:5">
+      <c r="A861"/>
+      <c r="B861"/>
+      <c r="C861"/>
+      <c r="D861"/>
+    </row>
+    <row r="862" spans="1:5">
+      <c r="A862"/>
+      <c r="B862"/>
+      <c r="C862"/>
+      <c r="D862"/>
+    </row>
+    <row r="863" spans="1:5">
+      <c r="A863"/>
+      <c r="B863"/>
+      <c r="C863"/>
+      <c r="D863"/>
+    </row>
+    <row r="864" spans="1:5">
+      <c r="A864"/>
+      <c r="B864"/>
+      <c r="C864"/>
+      <c r="D864"/>
+    </row>
+    <row r="865" spans="1:5">
+      <c r="A865"/>
+      <c r="B865"/>
+      <c r="C865"/>
+      <c r="D865"/>
+    </row>
+    <row r="866" spans="1:5">
+      <c r="A866"/>
+      <c r="B866"/>
+      <c r="C866"/>
+      <c r="D866"/>
+    </row>
+    <row r="867" spans="1:5">
+      <c r="A867"/>
+      <c r="B867"/>
+      <c r="C867"/>
+      <c r="D867"/>
+    </row>
+    <row r="868" spans="1:5">
+      <c r="A868"/>
+      <c r="B868"/>
+      <c r="C868"/>
+      <c r="D868"/>
+    </row>
+    <row r="869" spans="1:5">
+      <c r="A869"/>
+      <c r="B869"/>
+      <c r="C869"/>
+      <c r="D869"/>
+    </row>
+    <row r="870" spans="1:5">
+      <c r="A870"/>
+      <c r="B870"/>
+      <c r="C870"/>
+      <c r="D870"/>
+    </row>
+    <row r="871" spans="1:5">
+      <c r="A871"/>
+      <c r="B871"/>
+      <c r="C871"/>
+      <c r="D871"/>
+    </row>
+    <row r="872" spans="1:5">
+      <c r="A872"/>
+      <c r="B872"/>
+      <c r="C872"/>
+      <c r="D872"/>
+    </row>
+    <row r="873" spans="1:5">
+      <c r="A873"/>
+      <c r="B873"/>
+      <c r="C873"/>
+      <c r="D873"/>
+    </row>
+    <row r="874" spans="1:5">
+      <c r="A874"/>
+      <c r="B874"/>
+      <c r="C874"/>
+      <c r="D874"/>
+    </row>
+    <row r="875" spans="1:5">
+      <c r="A875"/>
+      <c r="B875"/>
+      <c r="C875"/>
+      <c r="D875"/>
+    </row>
+    <row r="876" spans="1:5">
+      <c r="A876"/>
+      <c r="B876"/>
+      <c r="C876"/>
+      <c r="D876"/>
+    </row>
+    <row r="877" spans="1:5">
+      <c r="A877"/>
+      <c r="B877"/>
+      <c r="C877"/>
+      <c r="D877"/>
+    </row>
+    <row r="878" spans="1:5">
+      <c r="A878"/>
+      <c r="B878"/>
+      <c r="C878"/>
+      <c r="D878"/>
+    </row>
+    <row r="879" spans="1:5">
+      <c r="A879"/>
+      <c r="B879"/>
+      <c r="C879"/>
+      <c r="D879"/>
+    </row>
+    <row r="880" spans="1:5">
+      <c r="A880"/>
+      <c r="B880"/>
+      <c r="C880"/>
+      <c r="D880"/>
+    </row>
+    <row r="881" spans="1:5">
+      <c r="A881"/>
+      <c r="B881"/>
+      <c r="C881"/>
+      <c r="D881"/>
+    </row>
+    <row r="882" spans="1:5">
+      <c r="A882"/>
+      <c r="B882"/>
+      <c r="C882"/>
+      <c r="D882"/>
+    </row>
+    <row r="883" spans="1:5">
+      <c r="A883"/>
+      <c r="B883"/>
+      <c r="C883"/>
+      <c r="D883"/>
+    </row>
+    <row r="884" spans="1:5">
+      <c r="A884"/>
+      <c r="B884"/>
+      <c r="C884"/>
+      <c r="D884"/>
+    </row>
+    <row r="885" spans="1:5">
+      <c r="A885"/>
+      <c r="B885"/>
+      <c r="C885"/>
+      <c r="D885"/>
+    </row>
+    <row r="886" spans="1:5">
+      <c r="A886"/>
+      <c r="B886"/>
+      <c r="C886"/>
+      <c r="D886"/>
+    </row>
+    <row r="887" spans="1:5">
+      <c r="A887"/>
+      <c r="B887"/>
+      <c r="C887"/>
+      <c r="D887"/>
+    </row>
+    <row r="888" spans="1:5">
+      <c r="A888"/>
+      <c r="B888"/>
+      <c r="C888"/>
+      <c r="D888"/>
+    </row>
+    <row r="889" spans="1:5">
+      <c r="A889"/>
+      <c r="B889"/>
+      <c r="C889"/>
+      <c r="D889"/>
+    </row>
+    <row r="890" spans="1:5">
+      <c r="A890"/>
+      <c r="B890"/>
+      <c r="C890"/>
+      <c r="D890"/>
+    </row>
+    <row r="891" spans="1:5">
+      <c r="A891"/>
+      <c r="B891"/>
+      <c r="C891"/>
+      <c r="D891"/>
+    </row>
+    <row r="892" spans="1:5">
+      <c r="A892"/>
+      <c r="B892"/>
+      <c r="C892"/>
+      <c r="D892"/>
+    </row>
+    <row r="893" spans="1:5">
+      <c r="A893"/>
+      <c r="B893"/>
+      <c r="C893"/>
+      <c r="D893"/>
+    </row>
+    <row r="894" spans="1:5">
+      <c r="A894"/>
+      <c r="B894"/>
+      <c r="C894"/>
+      <c r="D894"/>
+    </row>
+    <row r="895" spans="1:5">
+      <c r="A895"/>
+      <c r="B895"/>
+      <c r="C895"/>
+      <c r="D895"/>
+    </row>
+    <row r="896" spans="1:5">
+      <c r="A896"/>
+      <c r="B896"/>
+      <c r="C896"/>
+      <c r="D896"/>
+    </row>
+    <row r="897" spans="1:5">
+      <c r="A897"/>
+      <c r="B897"/>
+      <c r="C897"/>
+      <c r="D897"/>
+    </row>
+    <row r="898" spans="1:5">
+      <c r="A898"/>
+      <c r="B898"/>
+      <c r="C898"/>
+      <c r="D898"/>
+    </row>
+    <row r="899" spans="1:5">
+      <c r="A899"/>
+      <c r="B899"/>
+      <c r="C899"/>
+      <c r="D899"/>
+    </row>
+    <row r="900" spans="1:5">
+      <c r="A900"/>
+      <c r="B900"/>
+      <c r="C900"/>
+      <c r="D900"/>
+    </row>
+    <row r="901" spans="1:5">
+      <c r="A901"/>
+      <c r="B901"/>
+      <c r="C901"/>
+      <c r="D901"/>
+    </row>
+    <row r="902" spans="1:5">
+      <c r="A902"/>
+      <c r="B902"/>
+      <c r="C902"/>
+      <c r="D902"/>
+    </row>
+    <row r="903" spans="1:5">
+      <c r="A903"/>
+      <c r="B903"/>
+      <c r="C903"/>
+      <c r="D903"/>
+    </row>
+    <row r="904" spans="1:5">
+      <c r="A904"/>
+      <c r="B904"/>
+      <c r="C904"/>
+      <c r="D904"/>
+    </row>
+    <row r="905" spans="1:5">
+      <c r="A905"/>
+      <c r="B905"/>
+      <c r="C905"/>
+      <c r="D905"/>
+    </row>
+    <row r="906" spans="1:5">
+      <c r="A906"/>
+      <c r="B906"/>
+      <c r="C906"/>
+      <c r="D906"/>
+    </row>
+    <row r="907" spans="1:5">
+      <c r="A907"/>
+      <c r="B907"/>
+      <c r="C907"/>
+      <c r="D907"/>
+    </row>
+    <row r="908" spans="1:5">
+      <c r="A908"/>
+      <c r="B908"/>
+      <c r="C908"/>
+      <c r="D908"/>
+    </row>
+    <row r="909" spans="1:5">
+      <c r="A909"/>
+      <c r="B909"/>
+      <c r="C909"/>
+      <c r="D909"/>
+    </row>
+    <row r="910" spans="1:5">
+      <c r="A910"/>
+      <c r="B910"/>
+      <c r="C910"/>
+      <c r="D910"/>
+    </row>
+    <row r="911" spans="1:5">
+      <c r="A911"/>
+      <c r="B911"/>
+      <c r="C911"/>
+      <c r="D911"/>
+    </row>
+    <row r="912" spans="1:5">
+      <c r="A912"/>
+      <c r="B912"/>
+      <c r="C912"/>
+      <c r="D912"/>
+    </row>
+    <row r="913" spans="1:5">
+      <c r="A913"/>
+      <c r="B913"/>
+      <c r="C913"/>
+      <c r="D913"/>
+    </row>
+    <row r="914" spans="1:5">
+      <c r="A914"/>
+      <c r="B914"/>
+      <c r="C914"/>
+      <c r="D914"/>
+    </row>
+    <row r="915" spans="1:5">
+      <c r="A915"/>
+      <c r="B915"/>
+      <c r="C915"/>
+      <c r="D915"/>
+    </row>
+    <row r="916" spans="1:5">
+      <c r="A916"/>
+      <c r="B916"/>
+      <c r="C916"/>
+      <c r="D916"/>
+    </row>
+    <row r="917" spans="1:5">
+      <c r="A917"/>
+      <c r="B917"/>
+      <c r="C917"/>
+      <c r="D917"/>
+    </row>
+    <row r="918" spans="1:5">
+      <c r="A918"/>
+      <c r="B918"/>
+      <c r="C918"/>
+      <c r="D918"/>
+    </row>
+    <row r="919" spans="1:5">
+      <c r="A919"/>
+      <c r="B919"/>
+      <c r="C919"/>
+      <c r="D919"/>
+    </row>
+    <row r="920" spans="1:5">
+      <c r="A920"/>
+      <c r="B920"/>
+      <c r="C920"/>
+      <c r="D920"/>
+    </row>
+    <row r="921" spans="1:5">
+      <c r="A921"/>
+      <c r="B921"/>
+      <c r="C921"/>
+      <c r="D921"/>
+    </row>
+    <row r="922" spans="1:5">
+      <c r="A922"/>
+      <c r="B922"/>
+      <c r="C922"/>
+      <c r="D922"/>
+    </row>
+    <row r="923" spans="1:5">
+      <c r="A923"/>
+      <c r="B923"/>
+      <c r="C923"/>
+      <c r="D923"/>
+    </row>
+    <row r="924" spans="1:5">
+      <c r="A924"/>
+      <c r="B924"/>
+      <c r="C924"/>
+      <c r="D924"/>
+    </row>
+    <row r="925" spans="1:5">
+      <c r="A925"/>
+      <c r="B925"/>
+      <c r="C925"/>
+      <c r="D925"/>
+    </row>
+    <row r="926" spans="1:5">
+      <c r="A926"/>
+      <c r="B926"/>
+      <c r="C926"/>
+      <c r="D926"/>
+    </row>
+    <row r="927" spans="1:5">
+      <c r="A927"/>
+      <c r="B927"/>
+      <c r="C927"/>
+      <c r="D927"/>
+    </row>
+    <row r="928" spans="1:5">
+      <c r="A928"/>
+      <c r="B928"/>
+      <c r="C928"/>
+      <c r="D928"/>
+    </row>
+    <row r="929" spans="1:5">
+      <c r="A929"/>
+      <c r="B929"/>
+      <c r="C929"/>
+      <c r="D929"/>
+    </row>
+    <row r="930" spans="1:5">
+      <c r="A930"/>
+      <c r="B930"/>
+      <c r="C930"/>
+      <c r="D930"/>
+    </row>
+    <row r="931" spans="1:5">
+      <c r="A931"/>
+      <c r="B931"/>
+      <c r="C931"/>
+      <c r="D931"/>
+    </row>
+    <row r="932" spans="1:5">
+      <c r="A932"/>
+      <c r="B932"/>
+      <c r="C932"/>
+      <c r="D932"/>
+    </row>
+    <row r="933" spans="1:5">
+      <c r="A933"/>
+      <c r="B933"/>
+      <c r="C933"/>
+      <c r="D933"/>
+    </row>
+    <row r="934" spans="1:5">
+      <c r="A934"/>
+      <c r="B934"/>
+      <c r="C934"/>
+      <c r="D934"/>
+    </row>
+    <row r="935" spans="1:5">
+      <c r="A935"/>
+      <c r="B935"/>
+      <c r="C935"/>
+      <c r="D935"/>
+    </row>
+    <row r="936" spans="1:5">
+      <c r="A936"/>
+      <c r="B936"/>
+      <c r="C936"/>
+      <c r="D936"/>
+    </row>
+    <row r="937" spans="1:5">
+      <c r="A937"/>
+      <c r="B937"/>
+      <c r="C937"/>
+      <c r="D937"/>
+    </row>
+    <row r="938" spans="1:5">
+      <c r="A938"/>
+      <c r="B938"/>
+      <c r="C938"/>
+      <c r="D938"/>
+    </row>
+    <row r="939" spans="1:5">
+      <c r="A939"/>
+      <c r="B939"/>
+      <c r="C939"/>
+      <c r="D939"/>
+    </row>
+    <row r="940" spans="1:5">
+      <c r="A940"/>
+      <c r="B940"/>
+      <c r="C940"/>
+      <c r="D940"/>
+    </row>
+    <row r="941" spans="1:5">
+      <c r="A941"/>
+      <c r="B941"/>
+      <c r="C941"/>
+      <c r="D941"/>
+    </row>
+    <row r="942" spans="1:5">
+      <c r="A942"/>
+      <c r="B942"/>
+      <c r="C942"/>
+      <c r="D942"/>
+    </row>
+    <row r="943" spans="1:5">
+      <c r="A943"/>
+      <c r="B943"/>
+      <c r="C943"/>
+      <c r="D943"/>
+    </row>
+    <row r="944" spans="1:5">
+      <c r="A944"/>
+      <c r="B944"/>
+      <c r="C944"/>
+      <c r="D944"/>
+    </row>
+    <row r="945" spans="1:5">
+      <c r="A945"/>
+      <c r="B945"/>
+      <c r="C945"/>
+      <c r="D945"/>
+    </row>
+    <row r="946" spans="1:5">
+      <c r="A946"/>
+      <c r="B946"/>
+      <c r="C946"/>
+      <c r="D946"/>
+    </row>
+    <row r="947" spans="1:5">
+      <c r="A947"/>
+      <c r="B947"/>
+      <c r="C947"/>
+      <c r="D947"/>
+    </row>
+    <row r="948" spans="1:5">
+      <c r="A948"/>
+      <c r="B948"/>
+      <c r="C948"/>
+      <c r="D948"/>
+    </row>
+    <row r="949" spans="1:5">
+      <c r="A949"/>
+      <c r="B949"/>
+      <c r="C949"/>
+      <c r="D949"/>
+    </row>
+    <row r="950" spans="1:5">
+      <c r="A950"/>
+      <c r="B950"/>
+      <c r="C950"/>
+      <c r="D950"/>
+    </row>
+    <row r="951" spans="1:5">
+      <c r="A951"/>
+      <c r="B951"/>
+      <c r="C951"/>
+      <c r="D951"/>
+    </row>
+    <row r="952" spans="1:5">
+      <c r="A952"/>
+      <c r="B952"/>
+      <c r="C952"/>
+      <c r="D952"/>
+    </row>
+    <row r="953" spans="1:5">
+      <c r="A953"/>
+      <c r="B953"/>
+      <c r="C953"/>
+      <c r="D953"/>
+    </row>
+    <row r="954" spans="1:5">
+      <c r="A954"/>
+      <c r="B954"/>
+      <c r="C954"/>
+      <c r="D954"/>
+    </row>
+    <row r="955" spans="1:5">
+      <c r="A955"/>
+      <c r="B955"/>
+      <c r="C955"/>
+      <c r="D955"/>
+    </row>
+    <row r="956" spans="1:5">
+      <c r="A956"/>
+      <c r="B956"/>
+      <c r="C956"/>
+      <c r="D956"/>
+    </row>
+    <row r="957" spans="1:5">
+      <c r="A957"/>
+      <c r="B957"/>
+      <c r="C957"/>
+      <c r="D957"/>
+    </row>
+    <row r="958" spans="1:5">
+      <c r="A958"/>
+      <c r="B958"/>
+      <c r="C958"/>
+      <c r="D958"/>
+    </row>
+    <row r="959" spans="1:5">
+      <c r="A959"/>
+      <c r="B959"/>
+      <c r="C959"/>
+      <c r="D959"/>
+    </row>
+    <row r="960" spans="1:5">
+      <c r="A960"/>
+      <c r="B960"/>
+      <c r="C960"/>
+      <c r="D960"/>
+    </row>
+    <row r="961" spans="1:5">
+      <c r="A961"/>
+      <c r="B961"/>
+      <c r="C961"/>
+      <c r="D961"/>
+    </row>
+    <row r="962" spans="1:5">
+      <c r="A962"/>
+      <c r="B962"/>
+      <c r="C962"/>
+      <c r="D962"/>
+    </row>
+    <row r="963" spans="1:5">
+      <c r="A963"/>
+      <c r="B963"/>
+      <c r="C963"/>
+      <c r="D963"/>
+    </row>
+    <row r="964" spans="1:5">
+      <c r="A964"/>
+      <c r="B964"/>
+      <c r="C964"/>
+      <c r="D964"/>
+    </row>
+    <row r="965" spans="1:5">
+      <c r="A965"/>
+      <c r="B965"/>
+      <c r="C965"/>
+      <c r="D965"/>
+    </row>
+    <row r="966" spans="1:5">
+      <c r="A966"/>
+      <c r="B966"/>
+      <c r="C966"/>
+      <c r="D966"/>
+    </row>
+    <row r="967" spans="1:5">
+      <c r="A967"/>
+      <c r="B967"/>
+      <c r="C967"/>
+      <c r="D967"/>
+    </row>
+    <row r="968" spans="1:5">
+      <c r="A968"/>
+      <c r="B968"/>
+      <c r="C968"/>
+      <c r="D968"/>
+    </row>
+    <row r="969" spans="1:5">
+      <c r="A969"/>
+      <c r="B969"/>
+      <c r="C969"/>
+      <c r="D969"/>
+    </row>
+    <row r="970" spans="1:5">
+      <c r="A970"/>
+      <c r="B970"/>
+      <c r="C970"/>
+      <c r="D970"/>
+    </row>
+    <row r="971" spans="1:5">
+      <c r="A971"/>
+      <c r="B971"/>
+      <c r="C971"/>
+      <c r="D971"/>
+    </row>
+    <row r="972" spans="1:5">
+      <c r="A972"/>
+      <c r="B972"/>
+      <c r="C972"/>
+      <c r="D972"/>
+    </row>
+    <row r="973" spans="1:5">
+      <c r="A973"/>
+      <c r="B973"/>
+      <c r="C973"/>
+      <c r="D973"/>
+    </row>
+    <row r="974" spans="1:5">
+      <c r="A974"/>
+      <c r="B974"/>
+      <c r="C974"/>
+      <c r="D974"/>
+    </row>
+    <row r="975" spans="1:5">
+      <c r="A975"/>
+      <c r="B975"/>
+      <c r="C975"/>
+      <c r="D975"/>
+    </row>
+    <row r="976" spans="1:5">
+      <c r="A976"/>
+      <c r="B976"/>
+      <c r="C976"/>
+      <c r="D976"/>
+    </row>
+    <row r="977" spans="1:5">
+      <c r="A977"/>
+      <c r="B977"/>
+      <c r="C977"/>
+      <c r="D977"/>
+    </row>
+    <row r="978" spans="1:5">
+      <c r="A978"/>
+      <c r="B978"/>
+      <c r="C978"/>
+      <c r="D978"/>
+    </row>
+    <row r="979" spans="1:5">
+      <c r="A979"/>
+      <c r="B979"/>
+      <c r="C979"/>
+      <c r="D979"/>
+    </row>
+    <row r="980" spans="1:5">
+      <c r="A980"/>
+      <c r="B980"/>
+      <c r="C980"/>
+      <c r="D980"/>
+    </row>
+    <row r="981" spans="1:5">
+      <c r="A981"/>
+      <c r="B981"/>
+      <c r="C981"/>
+      <c r="D981"/>
+    </row>
+    <row r="982" spans="1:5">
+      <c r="A982"/>
+      <c r="B982"/>
+      <c r="C982"/>
+      <c r="D982"/>
+    </row>
+    <row r="983" spans="1:5">
+      <c r="A983"/>
+      <c r="B983"/>
+      <c r="C983"/>
+      <c r="D983"/>
+    </row>
+    <row r="984" spans="1:5">
+      <c r="A984"/>
+      <c r="B984"/>
+      <c r="C984"/>
+      <c r="D984"/>
+    </row>
+    <row r="985" spans="1:5">
+      <c r="A985"/>
+      <c r="B985"/>
+      <c r="C985"/>
+      <c r="D985"/>
+    </row>
+    <row r="986" spans="1:5">
+      <c r="A986"/>
+      <c r="B986"/>
+      <c r="C986"/>
+      <c r="D986"/>
+    </row>
+    <row r="987" spans="1:5">
+      <c r="A987"/>
+      <c r="B987"/>
+      <c r="C987"/>
+      <c r="D987"/>
+    </row>
+    <row r="988" spans="1:5">
+      <c r="A988"/>
+      <c r="B988"/>
+      <c r="C988"/>
+      <c r="D988"/>
+    </row>
+    <row r="989" spans="1:5">
+      <c r="A989"/>
+      <c r="B989"/>
+      <c r="C989"/>
+      <c r="D989"/>
+    </row>
+    <row r="990" spans="1:5">
+      <c r="A990"/>
+      <c r="B990"/>
+      <c r="C990"/>
+      <c r="D990"/>
+    </row>
+    <row r="991" spans="1:5">
+      <c r="A991"/>
+      <c r="B991"/>
+      <c r="C991"/>
+      <c r="D991"/>
+    </row>
+    <row r="992" spans="1:5">
+      <c r="A992"/>
+      <c r="B992"/>
+      <c r="C992"/>
+      <c r="D992"/>
+    </row>
+    <row r="993" spans="1:5">
+      <c r="A993"/>
+      <c r="B993"/>
+      <c r="C993"/>
+      <c r="D993"/>
+    </row>
+    <row r="994" spans="1:5">
+      <c r="A994"/>
+      <c r="B994"/>
+      <c r="C994"/>
+      <c r="D994"/>
+    </row>
+    <row r="995" spans="1:5">
+      <c r="A995"/>
+      <c r="B995"/>
+      <c r="C995"/>
+      <c r="D995"/>
+    </row>
+    <row r="996" spans="1:5">
+      <c r="A996"/>
+      <c r="B996"/>
+      <c r="C996"/>
+      <c r="D996"/>
+    </row>
+    <row r="997" spans="1:5">
+      <c r="A997"/>
+      <c r="B997"/>
+      <c r="C997"/>
+      <c r="D997"/>
+    </row>
+    <row r="998" spans="1:5">
+      <c r="A998"/>
+      <c r="B998"/>
+      <c r="C998"/>
+      <c r="D998"/>
+    </row>
+    <row r="999" spans="1:5">
+      <c r="A999"/>
+      <c r="B999"/>
+      <c r="C999"/>
+      <c r="D999"/>
+    </row>
+    <row r="1000" spans="1:5">
+      <c r="A1000"/>
+      <c r="B1000"/>
+      <c r="C1000"/>
+      <c r="D1000"/>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="A2:A1000">
+      <formula1>=YearList</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="B2:B1000">
+      <formula1>=MonthList</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="C2:C1000">
+      <formula1>=AmList</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="D2:D1000">
+      <formula1>=EntityList</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1">
+        <v>2024</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2027</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2028</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/template_target.xlsx
+++ b/public/templates/template_target.xlsx
@@ -15,13 +15,14 @@
     <definedName name="MonthList">'Lists'!$B$1:$B$12</definedName>
     <definedName name="AmList">'Lists'!$C$1:$C$9</definedName>
     <definedName name="EntityList">'Lists'!$D$1:$D$6</definedName>
+    <definedName name="EndUserList">'Lists'!$E$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>tahun</t>
   </si>
@@ -35,6 +36,9 @@
     <t>entity</t>
   </si>
   <si>
+    <t>end_user</t>
+  </si>
+  <si>
     <t>target</t>
   </si>
   <si>
@@ -45,6 +49,9 @@
   </si>
   <si>
     <t>BUANA</t>
+  </si>
+  <si>
+    <t>XL</t>
   </si>
   <si>
     <t>Januari</t>
@@ -453,7 +460,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E1000"/>
+  <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
@@ -461,9 +468,10 @@
     <col min="3" max="3" width="17.567" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.569" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,6014 +487,7018 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
         <v>10000000</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10"/>
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11"/>
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11"/>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12"/>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="E13"/>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="E14"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="E15"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="E16"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17"/>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="E18"/>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="E19"/>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="E20"/>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="E21"/>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="E22"/>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25"/>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="E26"/>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="E27"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="E28"/>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="E29"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="E30"/>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="E32"/>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
       <c r="D44"/>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45"/>
       <c r="D45"/>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="E45"/>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46"/>
       <c r="D46"/>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="E46"/>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
       <c r="D47"/>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="E47"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48"/>
       <c r="D48"/>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="E48"/>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
       <c r="D49"/>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50"/>
       <c r="D50"/>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="E50"/>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51"/>
       <c r="D51"/>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="E51"/>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
       <c r="D52"/>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="E52"/>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53"/>
       <c r="D53"/>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54"/>
       <c r="D54"/>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
       <c r="D55"/>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
       <c r="D56"/>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
       <c r="D57"/>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
       <c r="D58"/>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59"/>
       <c r="D59"/>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60"/>
       <c r="D60"/>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
       <c r="D61"/>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="E61"/>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62"/>
       <c r="B62"/>
       <c r="C62"/>
       <c r="D62"/>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="E62"/>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63"/>
       <c r="D63"/>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="E63"/>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
       <c r="D64"/>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="E64"/>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
       <c r="D65"/>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="E65"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
       <c r="D66"/>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="E66"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67"/>
       <c r="B67"/>
       <c r="C67"/>
       <c r="D67"/>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="E67"/>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
       <c r="D68"/>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="E68"/>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69"/>
       <c r="B69"/>
       <c r="C69"/>
       <c r="D69"/>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="E69"/>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70"/>
       <c r="B70"/>
       <c r="C70"/>
       <c r="D70"/>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="E70"/>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71"/>
       <c r="B71"/>
       <c r="C71"/>
       <c r="D71"/>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="E71"/>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72"/>
       <c r="B72"/>
       <c r="C72"/>
       <c r="D72"/>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="E72"/>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73"/>
       <c r="B73"/>
       <c r="C73"/>
       <c r="D73"/>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="E73"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74"/>
       <c r="B74"/>
       <c r="C74"/>
       <c r="D74"/>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="E74"/>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75"/>
       <c r="B75"/>
       <c r="C75"/>
       <c r="D75"/>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="E75"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76"/>
       <c r="B76"/>
       <c r="C76"/>
       <c r="D76"/>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="E76"/>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77"/>
       <c r="B77"/>
       <c r="C77"/>
       <c r="D77"/>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="E77"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78"/>
       <c r="B78"/>
       <c r="C78"/>
       <c r="D78"/>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="E78"/>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79"/>
       <c r="B79"/>
       <c r="C79"/>
       <c r="D79"/>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="E79"/>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
       <c r="D80"/>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="E80"/>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81"/>
       <c r="B81"/>
       <c r="C81"/>
       <c r="D81"/>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="E81"/>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82"/>
       <c r="B82"/>
       <c r="C82"/>
       <c r="D82"/>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="E82"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83"/>
       <c r="B83"/>
       <c r="C83"/>
       <c r="D83"/>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="E83"/>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84"/>
       <c r="B84"/>
       <c r="C84"/>
       <c r="D84"/>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="E84"/>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85"/>
       <c r="B85"/>
       <c r="C85"/>
       <c r="D85"/>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="E85"/>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86"/>
       <c r="B86"/>
       <c r="C86"/>
       <c r="D86"/>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="E86"/>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87"/>
       <c r="B87"/>
       <c r="C87"/>
       <c r="D87"/>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="E87"/>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88"/>
       <c r="B88"/>
       <c r="C88"/>
       <c r="D88"/>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="E88"/>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89"/>
       <c r="B89"/>
       <c r="C89"/>
       <c r="D89"/>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="E89"/>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90"/>
       <c r="B90"/>
       <c r="C90"/>
       <c r="D90"/>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="E90"/>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91"/>
       <c r="B91"/>
       <c r="C91"/>
       <c r="D91"/>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="E91"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
       <c r="D92"/>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="E92"/>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93"/>
       <c r="D93"/>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="E93"/>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
       <c r="D94"/>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="E94"/>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95"/>
       <c r="D95"/>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="E95"/>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96"/>
       <c r="D96"/>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="E96"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
       <c r="D97"/>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="E97"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
       <c r="D98"/>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="E98"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
       <c r="D99"/>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="E99"/>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
       <c r="D100"/>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="E100"/>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
       <c r="D101"/>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="E101"/>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
       <c r="D102"/>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="E102"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
       <c r="D103"/>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="E103"/>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
       <c r="D104"/>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="E104"/>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105"/>
       <c r="B105"/>
       <c r="C105"/>
       <c r="D105"/>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106"/>
       <c r="B106"/>
       <c r="C106"/>
       <c r="D106"/>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="E106"/>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107"/>
       <c r="B107"/>
       <c r="C107"/>
       <c r="D107"/>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="E107"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108"/>
       <c r="B108"/>
       <c r="C108"/>
       <c r="D108"/>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="E108"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109"/>
       <c r="B109"/>
       <c r="C109"/>
       <c r="D109"/>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="E109"/>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110"/>
       <c r="B110"/>
       <c r="C110"/>
       <c r="D110"/>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="E110"/>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111"/>
       <c r="B111"/>
       <c r="C111"/>
       <c r="D111"/>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="E111"/>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112"/>
       <c r="B112"/>
       <c r="C112"/>
       <c r="D112"/>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113"/>
       <c r="B113"/>
       <c r="C113"/>
       <c r="D113"/>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="E113"/>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114"/>
       <c r="B114"/>
       <c r="C114"/>
       <c r="D114"/>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="E114"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115"/>
       <c r="B115"/>
       <c r="C115"/>
       <c r="D115"/>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="E115"/>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116"/>
       <c r="B116"/>
       <c r="C116"/>
       <c r="D116"/>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="E116"/>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117"/>
       <c r="B117"/>
       <c r="C117"/>
       <c r="D117"/>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="E117"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118"/>
       <c r="B118"/>
       <c r="C118"/>
       <c r="D118"/>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="E118"/>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119"/>
       <c r="B119"/>
       <c r="C119"/>
       <c r="D119"/>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="E119"/>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120"/>
       <c r="B120"/>
       <c r="C120"/>
       <c r="D120"/>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="E120"/>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121"/>
       <c r="B121"/>
       <c r="C121"/>
       <c r="D121"/>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="E121"/>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122"/>
       <c r="B122"/>
       <c r="C122"/>
       <c r="D122"/>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="E122"/>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123"/>
       <c r="B123"/>
       <c r="C123"/>
       <c r="D123"/>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="E123"/>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124"/>
       <c r="B124"/>
       <c r="C124"/>
       <c r="D124"/>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="E124"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125"/>
       <c r="B125"/>
       <c r="C125"/>
       <c r="D125"/>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="E125"/>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126"/>
       <c r="B126"/>
       <c r="C126"/>
       <c r="D126"/>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="E126"/>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127"/>
       <c r="B127"/>
       <c r="C127"/>
       <c r="D127"/>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="E127"/>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128"/>
       <c r="B128"/>
       <c r="C128"/>
       <c r="D128"/>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="E128"/>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129"/>
       <c r="B129"/>
       <c r="C129"/>
       <c r="D129"/>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="E129"/>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130"/>
       <c r="B130"/>
       <c r="C130"/>
       <c r="D130"/>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="E130"/>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131"/>
       <c r="B131"/>
       <c r="C131"/>
       <c r="D131"/>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="E131"/>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132"/>
       <c r="B132"/>
       <c r="C132"/>
       <c r="D132"/>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="E132"/>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133"/>
       <c r="B133"/>
       <c r="C133"/>
       <c r="D133"/>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="E133"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134"/>
       <c r="B134"/>
       <c r="C134"/>
       <c r="D134"/>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="E134"/>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135"/>
       <c r="B135"/>
       <c r="C135"/>
       <c r="D135"/>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="E135"/>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136"/>
       <c r="B136"/>
       <c r="C136"/>
       <c r="D136"/>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="E136"/>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137"/>
       <c r="B137"/>
       <c r="C137"/>
       <c r="D137"/>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="E137"/>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138"/>
       <c r="B138"/>
       <c r="C138"/>
       <c r="D138"/>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="E138"/>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139"/>
       <c r="B139"/>
       <c r="C139"/>
       <c r="D139"/>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="E139"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140"/>
       <c r="B140"/>
       <c r="C140"/>
       <c r="D140"/>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="E140"/>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141"/>
       <c r="B141"/>
       <c r="C141"/>
       <c r="D141"/>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="E141"/>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142"/>
       <c r="B142"/>
       <c r="C142"/>
       <c r="D142"/>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="E142"/>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143"/>
       <c r="B143"/>
       <c r="C143"/>
       <c r="D143"/>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="E143"/>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144"/>
       <c r="B144"/>
       <c r="C144"/>
       <c r="D144"/>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="E144"/>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145"/>
       <c r="B145"/>
       <c r="C145"/>
       <c r="D145"/>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="E145"/>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146"/>
       <c r="B146"/>
       <c r="C146"/>
       <c r="D146"/>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="E146"/>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147"/>
       <c r="B147"/>
       <c r="C147"/>
       <c r="D147"/>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="E147"/>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148"/>
       <c r="B148"/>
       <c r="C148"/>
       <c r="D148"/>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="E148"/>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149"/>
       <c r="B149"/>
       <c r="C149"/>
       <c r="D149"/>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="E149"/>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150"/>
       <c r="B150"/>
       <c r="C150"/>
       <c r="D150"/>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="E150"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151"/>
       <c r="B151"/>
       <c r="C151"/>
       <c r="D151"/>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="E151"/>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152"/>
       <c r="B152"/>
       <c r="C152"/>
       <c r="D152"/>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="E152"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153"/>
       <c r="B153"/>
       <c r="C153"/>
       <c r="D153"/>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="E153"/>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154"/>
       <c r="B154"/>
       <c r="C154"/>
       <c r="D154"/>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="E154"/>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155"/>
       <c r="B155"/>
       <c r="C155"/>
       <c r="D155"/>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="E155"/>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156"/>
       <c r="B156"/>
       <c r="C156"/>
       <c r="D156"/>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="E156"/>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157"/>
       <c r="B157"/>
       <c r="C157"/>
       <c r="D157"/>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="E157"/>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158"/>
       <c r="B158"/>
       <c r="C158"/>
       <c r="D158"/>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="E158"/>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159"/>
       <c r="B159"/>
       <c r="C159"/>
       <c r="D159"/>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="E159"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160"/>
       <c r="B160"/>
       <c r="C160"/>
       <c r="D160"/>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="E160"/>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161"/>
       <c r="B161"/>
       <c r="C161"/>
       <c r="D161"/>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="E161"/>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162"/>
       <c r="B162"/>
       <c r="C162"/>
       <c r="D162"/>
-    </row>
-    <row r="163" spans="1:5">
+      <c r="E162"/>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163"/>
       <c r="B163"/>
       <c r="C163"/>
       <c r="D163"/>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="E163"/>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164"/>
       <c r="B164"/>
       <c r="C164"/>
       <c r="D164"/>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="E164"/>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165"/>
       <c r="B165"/>
       <c r="C165"/>
       <c r="D165"/>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="E165"/>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166"/>
       <c r="B166"/>
       <c r="C166"/>
       <c r="D166"/>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="E166"/>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167"/>
       <c r="B167"/>
       <c r="C167"/>
       <c r="D167"/>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="E167"/>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168"/>
       <c r="B168"/>
       <c r="C168"/>
       <c r="D168"/>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="E168"/>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169"/>
       <c r="B169"/>
       <c r="C169"/>
       <c r="D169"/>
-    </row>
-    <row r="170" spans="1:5">
+      <c r="E169"/>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170"/>
       <c r="B170"/>
       <c r="C170"/>
       <c r="D170"/>
-    </row>
-    <row r="171" spans="1:5">
+      <c r="E170"/>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171"/>
       <c r="B171"/>
       <c r="C171"/>
       <c r="D171"/>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="E171"/>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172"/>
       <c r="B172"/>
       <c r="C172"/>
       <c r="D172"/>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="E172"/>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173"/>
       <c r="B173"/>
       <c r="C173"/>
       <c r="D173"/>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="E173"/>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174"/>
       <c r="B174"/>
       <c r="C174"/>
       <c r="D174"/>
-    </row>
-    <row r="175" spans="1:5">
+      <c r="E174"/>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175"/>
       <c r="B175"/>
       <c r="C175"/>
       <c r="D175"/>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="E175"/>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176"/>
       <c r="B176"/>
       <c r="C176"/>
       <c r="D176"/>
-    </row>
-    <row r="177" spans="1:5">
+      <c r="E176"/>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177"/>
       <c r="B177"/>
       <c r="C177"/>
       <c r="D177"/>
-    </row>
-    <row r="178" spans="1:5">
+      <c r="E177"/>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178"/>
       <c r="B178"/>
       <c r="C178"/>
       <c r="D178"/>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="E178"/>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179"/>
       <c r="B179"/>
       <c r="C179"/>
       <c r="D179"/>
-    </row>
-    <row r="180" spans="1:5">
+      <c r="E179"/>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180"/>
       <c r="B180"/>
       <c r="C180"/>
       <c r="D180"/>
-    </row>
-    <row r="181" spans="1:5">
+      <c r="E180"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181"/>
       <c r="B181"/>
       <c r="C181"/>
       <c r="D181"/>
-    </row>
-    <row r="182" spans="1:5">
+      <c r="E181"/>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182"/>
       <c r="B182"/>
       <c r="C182"/>
       <c r="D182"/>
-    </row>
-    <row r="183" spans="1:5">
+      <c r="E182"/>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183"/>
       <c r="B183"/>
       <c r="C183"/>
       <c r="D183"/>
-    </row>
-    <row r="184" spans="1:5">
+      <c r="E183"/>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184"/>
       <c r="B184"/>
       <c r="C184"/>
       <c r="D184"/>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="E184"/>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185"/>
       <c r="B185"/>
       <c r="C185"/>
       <c r="D185"/>
-    </row>
-    <row r="186" spans="1:5">
+      <c r="E185"/>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186"/>
       <c r="B186"/>
       <c r="C186"/>
       <c r="D186"/>
-    </row>
-    <row r="187" spans="1:5">
+      <c r="E186"/>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187"/>
       <c r="B187"/>
       <c r="C187"/>
       <c r="D187"/>
-    </row>
-    <row r="188" spans="1:5">
+      <c r="E187"/>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188"/>
       <c r="B188"/>
       <c r="C188"/>
       <c r="D188"/>
-    </row>
-    <row r="189" spans="1:5">
+      <c r="E188"/>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189"/>
       <c r="B189"/>
       <c r="C189"/>
       <c r="D189"/>
-    </row>
-    <row r="190" spans="1:5">
+      <c r="E189"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190"/>
       <c r="B190"/>
       <c r="C190"/>
       <c r="D190"/>
-    </row>
-    <row r="191" spans="1:5">
+      <c r="E190"/>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191"/>
       <c r="B191"/>
       <c r="C191"/>
       <c r="D191"/>
-    </row>
-    <row r="192" spans="1:5">
+      <c r="E191"/>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192"/>
       <c r="B192"/>
       <c r="C192"/>
       <c r="D192"/>
-    </row>
-    <row r="193" spans="1:5">
+      <c r="E192"/>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193"/>
       <c r="B193"/>
       <c r="C193"/>
       <c r="D193"/>
-    </row>
-    <row r="194" spans="1:5">
+      <c r="E193"/>
+    </row>
+    <row r="194" spans="1:6">
       <c r="A194"/>
       <c r="B194"/>
       <c r="C194"/>
       <c r="D194"/>
-    </row>
-    <row r="195" spans="1:5">
+      <c r="E194"/>
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195"/>
       <c r="B195"/>
       <c r="C195"/>
       <c r="D195"/>
-    </row>
-    <row r="196" spans="1:5">
+      <c r="E195"/>
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196"/>
       <c r="B196"/>
       <c r="C196"/>
       <c r="D196"/>
-    </row>
-    <row r="197" spans="1:5">
+      <c r="E196"/>
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197"/>
       <c r="B197"/>
       <c r="C197"/>
       <c r="D197"/>
-    </row>
-    <row r="198" spans="1:5">
+      <c r="E197"/>
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198"/>
       <c r="B198"/>
       <c r="C198"/>
       <c r="D198"/>
-    </row>
-    <row r="199" spans="1:5">
+      <c r="E198"/>
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199"/>
       <c r="B199"/>
       <c r="C199"/>
       <c r="D199"/>
-    </row>
-    <row r="200" spans="1:5">
+      <c r="E199"/>
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200"/>
       <c r="B200"/>
       <c r="C200"/>
       <c r="D200"/>
-    </row>
-    <row r="201" spans="1:5">
+      <c r="E200"/>
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201"/>
       <c r="B201"/>
       <c r="C201"/>
       <c r="D201"/>
-    </row>
-    <row r="202" spans="1:5">
+      <c r="E201"/>
+    </row>
+    <row r="202" spans="1:6">
       <c r="A202"/>
       <c r="B202"/>
       <c r="C202"/>
       <c r="D202"/>
-    </row>
-    <row r="203" spans="1:5">
+      <c r="E202"/>
+    </row>
+    <row r="203" spans="1:6">
       <c r="A203"/>
       <c r="B203"/>
       <c r="C203"/>
       <c r="D203"/>
-    </row>
-    <row r="204" spans="1:5">
+      <c r="E203"/>
+    </row>
+    <row r="204" spans="1:6">
       <c r="A204"/>
       <c r="B204"/>
       <c r="C204"/>
       <c r="D204"/>
-    </row>
-    <row r="205" spans="1:5">
+      <c r="E204"/>
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205"/>
       <c r="B205"/>
       <c r="C205"/>
       <c r="D205"/>
-    </row>
-    <row r="206" spans="1:5">
+      <c r="E205"/>
+    </row>
+    <row r="206" spans="1:6">
       <c r="A206"/>
       <c r="B206"/>
       <c r="C206"/>
       <c r="D206"/>
-    </row>
-    <row r="207" spans="1:5">
+      <c r="E206"/>
+    </row>
+    <row r="207" spans="1:6">
       <c r="A207"/>
       <c r="B207"/>
       <c r="C207"/>
       <c r="D207"/>
-    </row>
-    <row r="208" spans="1:5">
+      <c r="E207"/>
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208"/>
       <c r="B208"/>
       <c r="C208"/>
       <c r="D208"/>
-    </row>
-    <row r="209" spans="1:5">
+      <c r="E208"/>
+    </row>
+    <row r="209" spans="1:6">
       <c r="A209"/>
       <c r="B209"/>
       <c r="C209"/>
       <c r="D209"/>
-    </row>
-    <row r="210" spans="1:5">
+      <c r="E209"/>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210"/>
       <c r="B210"/>
       <c r="C210"/>
       <c r="D210"/>
-    </row>
-    <row r="211" spans="1:5">
+      <c r="E210"/>
+    </row>
+    <row r="211" spans="1:6">
       <c r="A211"/>
       <c r="B211"/>
       <c r="C211"/>
       <c r="D211"/>
-    </row>
-    <row r="212" spans="1:5">
+      <c r="E211"/>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212"/>
       <c r="B212"/>
       <c r="C212"/>
       <c r="D212"/>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="E212"/>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213"/>
       <c r="B213"/>
       <c r="C213"/>
       <c r="D213"/>
-    </row>
-    <row r="214" spans="1:5">
+      <c r="E213"/>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214"/>
       <c r="B214"/>
       <c r="C214"/>
       <c r="D214"/>
-    </row>
-    <row r="215" spans="1:5">
+      <c r="E214"/>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215"/>
       <c r="B215"/>
       <c r="C215"/>
       <c r="D215"/>
-    </row>
-    <row r="216" spans="1:5">
+      <c r="E215"/>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216"/>
       <c r="B216"/>
       <c r="C216"/>
       <c r="D216"/>
-    </row>
-    <row r="217" spans="1:5">
+      <c r="E216"/>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217"/>
       <c r="B217"/>
       <c r="C217"/>
       <c r="D217"/>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="E217"/>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218"/>
       <c r="B218"/>
       <c r="C218"/>
       <c r="D218"/>
-    </row>
-    <row r="219" spans="1:5">
+      <c r="E218"/>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219"/>
       <c r="B219"/>
       <c r="C219"/>
       <c r="D219"/>
-    </row>
-    <row r="220" spans="1:5">
+      <c r="E219"/>
+    </row>
+    <row r="220" spans="1:6">
       <c r="A220"/>
       <c r="B220"/>
       <c r="C220"/>
       <c r="D220"/>
-    </row>
-    <row r="221" spans="1:5">
+      <c r="E220"/>
+    </row>
+    <row r="221" spans="1:6">
       <c r="A221"/>
       <c r="B221"/>
       <c r="C221"/>
       <c r="D221"/>
-    </row>
-    <row r="222" spans="1:5">
+      <c r="E221"/>
+    </row>
+    <row r="222" spans="1:6">
       <c r="A222"/>
       <c r="B222"/>
       <c r="C222"/>
       <c r="D222"/>
-    </row>
-    <row r="223" spans="1:5">
+      <c r="E222"/>
+    </row>
+    <row r="223" spans="1:6">
       <c r="A223"/>
       <c r="B223"/>
       <c r="C223"/>
       <c r="D223"/>
-    </row>
-    <row r="224" spans="1:5">
+      <c r="E223"/>
+    </row>
+    <row r="224" spans="1:6">
       <c r="A224"/>
       <c r="B224"/>
       <c r="C224"/>
       <c r="D224"/>
-    </row>
-    <row r="225" spans="1:5">
+      <c r="E224"/>
+    </row>
+    <row r="225" spans="1:6">
       <c r="A225"/>
       <c r="B225"/>
       <c r="C225"/>
       <c r="D225"/>
-    </row>
-    <row r="226" spans="1:5">
+      <c r="E225"/>
+    </row>
+    <row r="226" spans="1:6">
       <c r="A226"/>
       <c r="B226"/>
       <c r="C226"/>
       <c r="D226"/>
-    </row>
-    <row r="227" spans="1:5">
+      <c r="E226"/>
+    </row>
+    <row r="227" spans="1:6">
       <c r="A227"/>
       <c r="B227"/>
       <c r="C227"/>
       <c r="D227"/>
-    </row>
-    <row r="228" spans="1:5">
+      <c r="E227"/>
+    </row>
+    <row r="228" spans="1:6">
       <c r="A228"/>
       <c r="B228"/>
       <c r="C228"/>
       <c r="D228"/>
-    </row>
-    <row r="229" spans="1:5">
+      <c r="E228"/>
+    </row>
+    <row r="229" spans="1:6">
       <c r="A229"/>
       <c r="B229"/>
       <c r="C229"/>
       <c r="D229"/>
-    </row>
-    <row r="230" spans="1:5">
+      <c r="E229"/>
+    </row>
+    <row r="230" spans="1:6">
       <c r="A230"/>
       <c r="B230"/>
       <c r="C230"/>
       <c r="D230"/>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="E230"/>
+    </row>
+    <row r="231" spans="1:6">
       <c r="A231"/>
       <c r="B231"/>
       <c r="C231"/>
       <c r="D231"/>
-    </row>
-    <row r="232" spans="1:5">
+      <c r="E231"/>
+    </row>
+    <row r="232" spans="1:6">
       <c r="A232"/>
       <c r="B232"/>
       <c r="C232"/>
       <c r="D232"/>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="E232"/>
+    </row>
+    <row r="233" spans="1:6">
       <c r="A233"/>
       <c r="B233"/>
       <c r="C233"/>
       <c r="D233"/>
-    </row>
-    <row r="234" spans="1:5">
+      <c r="E233"/>
+    </row>
+    <row r="234" spans="1:6">
       <c r="A234"/>
       <c r="B234"/>
       <c r="C234"/>
       <c r="D234"/>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="E234"/>
+    </row>
+    <row r="235" spans="1:6">
       <c r="A235"/>
       <c r="B235"/>
       <c r="C235"/>
       <c r="D235"/>
-    </row>
-    <row r="236" spans="1:5">
+      <c r="E235"/>
+    </row>
+    <row r="236" spans="1:6">
       <c r="A236"/>
       <c r="B236"/>
       <c r="C236"/>
       <c r="D236"/>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="E236"/>
+    </row>
+    <row r="237" spans="1:6">
       <c r="A237"/>
       <c r="B237"/>
       <c r="C237"/>
       <c r="D237"/>
-    </row>
-    <row r="238" spans="1:5">
+      <c r="E237"/>
+    </row>
+    <row r="238" spans="1:6">
       <c r="A238"/>
       <c r="B238"/>
       <c r="C238"/>
       <c r="D238"/>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="E238"/>
+    </row>
+    <row r="239" spans="1:6">
       <c r="A239"/>
       <c r="B239"/>
       <c r="C239"/>
       <c r="D239"/>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="E239"/>
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240"/>
       <c r="B240"/>
       <c r="C240"/>
       <c r="D240"/>
-    </row>
-    <row r="241" spans="1:5">
+      <c r="E240"/>
+    </row>
+    <row r="241" spans="1:6">
       <c r="A241"/>
       <c r="B241"/>
       <c r="C241"/>
       <c r="D241"/>
-    </row>
-    <row r="242" spans="1:5">
+      <c r="E241"/>
+    </row>
+    <row r="242" spans="1:6">
       <c r="A242"/>
       <c r="B242"/>
       <c r="C242"/>
       <c r="D242"/>
-    </row>
-    <row r="243" spans="1:5">
+      <c r="E242"/>
+    </row>
+    <row r="243" spans="1:6">
       <c r="A243"/>
       <c r="B243"/>
       <c r="C243"/>
       <c r="D243"/>
-    </row>
-    <row r="244" spans="1:5">
+      <c r="E243"/>
+    </row>
+    <row r="244" spans="1:6">
       <c r="A244"/>
       <c r="B244"/>
       <c r="C244"/>
       <c r="D244"/>
-    </row>
-    <row r="245" spans="1:5">
+      <c r="E244"/>
+    </row>
+    <row r="245" spans="1:6">
       <c r="A245"/>
       <c r="B245"/>
       <c r="C245"/>
       <c r="D245"/>
-    </row>
-    <row r="246" spans="1:5">
+      <c r="E245"/>
+    </row>
+    <row r="246" spans="1:6">
       <c r="A246"/>
       <c r="B246"/>
       <c r="C246"/>
       <c r="D246"/>
-    </row>
-    <row r="247" spans="1:5">
+      <c r="E246"/>
+    </row>
+    <row r="247" spans="1:6">
       <c r="A247"/>
       <c r="B247"/>
       <c r="C247"/>
       <c r="D247"/>
-    </row>
-    <row r="248" spans="1:5">
+      <c r="E247"/>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248"/>
       <c r="B248"/>
       <c r="C248"/>
       <c r="D248"/>
-    </row>
-    <row r="249" spans="1:5">
+      <c r="E248"/>
+    </row>
+    <row r="249" spans="1:6">
       <c r="A249"/>
       <c r="B249"/>
       <c r="C249"/>
       <c r="D249"/>
-    </row>
-    <row r="250" spans="1:5">
+      <c r="E249"/>
+    </row>
+    <row r="250" spans="1:6">
       <c r="A250"/>
       <c r="B250"/>
       <c r="C250"/>
       <c r="D250"/>
-    </row>
-    <row r="251" spans="1:5">
+      <c r="E250"/>
+    </row>
+    <row r="251" spans="1:6">
       <c r="A251"/>
       <c r="B251"/>
       <c r="C251"/>
       <c r="D251"/>
-    </row>
-    <row r="252" spans="1:5">
+      <c r="E251"/>
+    </row>
+    <row r="252" spans="1:6">
       <c r="A252"/>
       <c r="B252"/>
       <c r="C252"/>
       <c r="D252"/>
-    </row>
-    <row r="253" spans="1:5">
+      <c r="E252"/>
+    </row>
+    <row r="253" spans="1:6">
       <c r="A253"/>
       <c r="B253"/>
       <c r="C253"/>
       <c r="D253"/>
-    </row>
-    <row r="254" spans="1:5">
+      <c r="E253"/>
+    </row>
+    <row r="254" spans="1:6">
       <c r="A254"/>
       <c r="B254"/>
       <c r="C254"/>
       <c r="D254"/>
-    </row>
-    <row r="255" spans="1:5">
+      <c r="E254"/>
+    </row>
+    <row r="255" spans="1:6">
       <c r="A255"/>
       <c r="B255"/>
       <c r="C255"/>
       <c r="D255"/>
-    </row>
-    <row r="256" spans="1:5">
+      <c r="E255"/>
+    </row>
+    <row r="256" spans="1:6">
       <c r="A256"/>
       <c r="B256"/>
       <c r="C256"/>
       <c r="D256"/>
-    </row>
-    <row r="257" spans="1:5">
+      <c r="E256"/>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257"/>
       <c r="B257"/>
       <c r="C257"/>
       <c r="D257"/>
-    </row>
-    <row r="258" spans="1:5">
+      <c r="E257"/>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258"/>
       <c r="B258"/>
       <c r="C258"/>
       <c r="D258"/>
-    </row>
-    <row r="259" spans="1:5">
+      <c r="E258"/>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259"/>
       <c r="B259"/>
       <c r="C259"/>
       <c r="D259"/>
-    </row>
-    <row r="260" spans="1:5">
+      <c r="E259"/>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260"/>
       <c r="B260"/>
       <c r="C260"/>
       <c r="D260"/>
-    </row>
-    <row r="261" spans="1:5">
+      <c r="E260"/>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261"/>
       <c r="B261"/>
       <c r="C261"/>
       <c r="D261"/>
-    </row>
-    <row r="262" spans="1:5">
+      <c r="E261"/>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262"/>
       <c r="B262"/>
       <c r="C262"/>
       <c r="D262"/>
-    </row>
-    <row r="263" spans="1:5">
+      <c r="E262"/>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263"/>
       <c r="B263"/>
       <c r="C263"/>
       <c r="D263"/>
-    </row>
-    <row r="264" spans="1:5">
+      <c r="E263"/>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264"/>
       <c r="B264"/>
       <c r="C264"/>
       <c r="D264"/>
-    </row>
-    <row r="265" spans="1:5">
+      <c r="E264"/>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265"/>
       <c r="B265"/>
       <c r="C265"/>
       <c r="D265"/>
-    </row>
-    <row r="266" spans="1:5">
+      <c r="E265"/>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266"/>
       <c r="B266"/>
       <c r="C266"/>
       <c r="D266"/>
-    </row>
-    <row r="267" spans="1:5">
+      <c r="E266"/>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267"/>
       <c r="B267"/>
       <c r="C267"/>
       <c r="D267"/>
-    </row>
-    <row r="268" spans="1:5">
+      <c r="E267"/>
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268"/>
       <c r="B268"/>
       <c r="C268"/>
       <c r="D268"/>
-    </row>
-    <row r="269" spans="1:5">
+      <c r="E268"/>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269"/>
       <c r="B269"/>
       <c r="C269"/>
       <c r="D269"/>
-    </row>
-    <row r="270" spans="1:5">
+      <c r="E269"/>
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270"/>
       <c r="B270"/>
       <c r="C270"/>
       <c r="D270"/>
-    </row>
-    <row r="271" spans="1:5">
+      <c r="E270"/>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271"/>
       <c r="B271"/>
       <c r="C271"/>
       <c r="D271"/>
-    </row>
-    <row r="272" spans="1:5">
+      <c r="E271"/>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272"/>
       <c r="B272"/>
       <c r="C272"/>
       <c r="D272"/>
-    </row>
-    <row r="273" spans="1:5">
+      <c r="E272"/>
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273"/>
       <c r="B273"/>
       <c r="C273"/>
       <c r="D273"/>
-    </row>
-    <row r="274" spans="1:5">
+      <c r="E273"/>
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274"/>
       <c r="B274"/>
       <c r="C274"/>
       <c r="D274"/>
-    </row>
-    <row r="275" spans="1:5">
+      <c r="E274"/>
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275"/>
       <c r="B275"/>
       <c r="C275"/>
       <c r="D275"/>
-    </row>
-    <row r="276" spans="1:5">
+      <c r="E275"/>
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276"/>
       <c r="B276"/>
       <c r="C276"/>
       <c r="D276"/>
-    </row>
-    <row r="277" spans="1:5">
+      <c r="E276"/>
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277"/>
       <c r="B277"/>
       <c r="C277"/>
       <c r="D277"/>
-    </row>
-    <row r="278" spans="1:5">
+      <c r="E277"/>
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278"/>
       <c r="B278"/>
       <c r="C278"/>
       <c r="D278"/>
-    </row>
-    <row r="279" spans="1:5">
+      <c r="E278"/>
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279"/>
       <c r="B279"/>
       <c r="C279"/>
       <c r="D279"/>
-    </row>
-    <row r="280" spans="1:5">
+      <c r="E279"/>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280"/>
       <c r="B280"/>
       <c r="C280"/>
       <c r="D280"/>
-    </row>
-    <row r="281" spans="1:5">
+      <c r="E280"/>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281"/>
       <c r="B281"/>
       <c r="C281"/>
       <c r="D281"/>
-    </row>
-    <row r="282" spans="1:5">
+      <c r="E281"/>
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282"/>
       <c r="B282"/>
       <c r="C282"/>
       <c r="D282"/>
-    </row>
-    <row r="283" spans="1:5">
+      <c r="E282"/>
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283"/>
       <c r="B283"/>
       <c r="C283"/>
       <c r="D283"/>
-    </row>
-    <row r="284" spans="1:5">
+      <c r="E283"/>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284"/>
       <c r="B284"/>
       <c r="C284"/>
       <c r="D284"/>
-    </row>
-    <row r="285" spans="1:5">
+      <c r="E284"/>
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285"/>
       <c r="B285"/>
       <c r="C285"/>
       <c r="D285"/>
-    </row>
-    <row r="286" spans="1:5">
+      <c r="E285"/>
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286"/>
       <c r="B286"/>
       <c r="C286"/>
       <c r="D286"/>
-    </row>
-    <row r="287" spans="1:5">
+      <c r="E286"/>
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287"/>
       <c r="B287"/>
       <c r="C287"/>
       <c r="D287"/>
-    </row>
-    <row r="288" spans="1:5">
+      <c r="E287"/>
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288"/>
       <c r="B288"/>
       <c r="C288"/>
       <c r="D288"/>
-    </row>
-    <row r="289" spans="1:5">
+      <c r="E288"/>
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289"/>
       <c r="B289"/>
       <c r="C289"/>
       <c r="D289"/>
-    </row>
-    <row r="290" spans="1:5">
+      <c r="E289"/>
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290"/>
       <c r="B290"/>
       <c r="C290"/>
       <c r="D290"/>
-    </row>
-    <row r="291" spans="1:5">
+      <c r="E290"/>
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291"/>
       <c r="B291"/>
       <c r="C291"/>
       <c r="D291"/>
-    </row>
-    <row r="292" spans="1:5">
+      <c r="E291"/>
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292"/>
       <c r="B292"/>
       <c r="C292"/>
       <c r="D292"/>
-    </row>
-    <row r="293" spans="1:5">
+      <c r="E292"/>
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293"/>
       <c r="B293"/>
       <c r="C293"/>
       <c r="D293"/>
-    </row>
-    <row r="294" spans="1:5">
+      <c r="E293"/>
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294"/>
       <c r="B294"/>
       <c r="C294"/>
       <c r="D294"/>
-    </row>
-    <row r="295" spans="1:5">
+      <c r="E294"/>
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295"/>
       <c r="B295"/>
       <c r="C295"/>
       <c r="D295"/>
-    </row>
-    <row r="296" spans="1:5">
+      <c r="E295"/>
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296"/>
       <c r="B296"/>
       <c r="C296"/>
       <c r="D296"/>
-    </row>
-    <row r="297" spans="1:5">
+      <c r="E296"/>
+    </row>
+    <row r="297" spans="1:6">
       <c r="A297"/>
       <c r="B297"/>
       <c r="C297"/>
       <c r="D297"/>
-    </row>
-    <row r="298" spans="1:5">
+      <c r="E297"/>
+    </row>
+    <row r="298" spans="1:6">
       <c r="A298"/>
       <c r="B298"/>
       <c r="C298"/>
       <c r="D298"/>
-    </row>
-    <row r="299" spans="1:5">
+      <c r="E298"/>
+    </row>
+    <row r="299" spans="1:6">
       <c r="A299"/>
       <c r="B299"/>
       <c r="C299"/>
       <c r="D299"/>
-    </row>
-    <row r="300" spans="1:5">
+      <c r="E299"/>
+    </row>
+    <row r="300" spans="1:6">
       <c r="A300"/>
       <c r="B300"/>
       <c r="C300"/>
       <c r="D300"/>
-    </row>
-    <row r="301" spans="1:5">
+      <c r="E300"/>
+    </row>
+    <row r="301" spans="1:6">
       <c r="A301"/>
       <c r="B301"/>
       <c r="C301"/>
       <c r="D301"/>
-    </row>
-    <row r="302" spans="1:5">
+      <c r="E301"/>
+    </row>
+    <row r="302" spans="1:6">
       <c r="A302"/>
       <c r="B302"/>
       <c r="C302"/>
       <c r="D302"/>
-    </row>
-    <row r="303" spans="1:5">
+      <c r="E302"/>
+    </row>
+    <row r="303" spans="1:6">
       <c r="A303"/>
       <c r="B303"/>
       <c r="C303"/>
       <c r="D303"/>
-    </row>
-    <row r="304" spans="1:5">
+      <c r="E303"/>
+    </row>
+    <row r="304" spans="1:6">
       <c r="A304"/>
       <c r="B304"/>
       <c r="C304"/>
       <c r="D304"/>
-    </row>
-    <row r="305" spans="1:5">
+      <c r="E304"/>
+    </row>
+    <row r="305" spans="1:6">
       <c r="A305"/>
       <c r="B305"/>
       <c r="C305"/>
       <c r="D305"/>
-    </row>
-    <row r="306" spans="1:5">
+      <c r="E305"/>
+    </row>
+    <row r="306" spans="1:6">
       <c r="A306"/>
       <c r="B306"/>
       <c r="C306"/>
       <c r="D306"/>
-    </row>
-    <row r="307" spans="1:5">
+      <c r="E306"/>
+    </row>
+    <row r="307" spans="1:6">
       <c r="A307"/>
       <c r="B307"/>
       <c r="C307"/>
       <c r="D307"/>
-    </row>
-    <row r="308" spans="1:5">
+      <c r="E307"/>
+    </row>
+    <row r="308" spans="1:6">
       <c r="A308"/>
       <c r="B308"/>
       <c r="C308"/>
       <c r="D308"/>
-    </row>
-    <row r="309" spans="1:5">
+      <c r="E308"/>
+    </row>
+    <row r="309" spans="1:6">
       <c r="A309"/>
       <c r="B309"/>
       <c r="C309"/>
       <c r="D309"/>
-    </row>
-    <row r="310" spans="1:5">
+      <c r="E309"/>
+    </row>
+    <row r="310" spans="1:6">
       <c r="A310"/>
       <c r="B310"/>
       <c r="C310"/>
       <c r="D310"/>
-    </row>
-    <row r="311" spans="1:5">
+      <c r="E310"/>
+    </row>
+    <row r="311" spans="1:6">
       <c r="A311"/>
       <c r="B311"/>
       <c r="C311"/>
       <c r="D311"/>
-    </row>
-    <row r="312" spans="1:5">
+      <c r="E311"/>
+    </row>
+    <row r="312" spans="1:6">
       <c r="A312"/>
       <c r="B312"/>
       <c r="C312"/>
       <c r="D312"/>
-    </row>
-    <row r="313" spans="1:5">
+      <c r="E312"/>
+    </row>
+    <row r="313" spans="1:6">
       <c r="A313"/>
       <c r="B313"/>
       <c r="C313"/>
       <c r="D313"/>
-    </row>
-    <row r="314" spans="1:5">
+      <c r="E313"/>
+    </row>
+    <row r="314" spans="1:6">
       <c r="A314"/>
       <c r="B314"/>
       <c r="C314"/>
       <c r="D314"/>
-    </row>
-    <row r="315" spans="1:5">
+      <c r="E314"/>
+    </row>
+    <row r="315" spans="1:6">
       <c r="A315"/>
       <c r="B315"/>
       <c r="C315"/>
       <c r="D315"/>
-    </row>
-    <row r="316" spans="1:5">
+      <c r="E315"/>
+    </row>
+    <row r="316" spans="1:6">
       <c r="A316"/>
       <c r="B316"/>
       <c r="C316"/>
       <c r="D316"/>
-    </row>
-    <row r="317" spans="1:5">
+      <c r="E316"/>
+    </row>
+    <row r="317" spans="1:6">
       <c r="A317"/>
       <c r="B317"/>
       <c r="C317"/>
       <c r="D317"/>
-    </row>
-    <row r="318" spans="1:5">
+      <c r="E317"/>
+    </row>
+    <row r="318" spans="1:6">
       <c r="A318"/>
       <c r="B318"/>
       <c r="C318"/>
       <c r="D318"/>
-    </row>
-    <row r="319" spans="1:5">
+      <c r="E318"/>
+    </row>
+    <row r="319" spans="1:6">
       <c r="A319"/>
       <c r="B319"/>
       <c r="C319"/>
       <c r="D319"/>
-    </row>
-    <row r="320" spans="1:5">
+      <c r="E319"/>
+    </row>
+    <row r="320" spans="1:6">
       <c r="A320"/>
       <c r="B320"/>
       <c r="C320"/>
       <c r="D320"/>
-    </row>
-    <row r="321" spans="1:5">
+      <c r="E320"/>
+    </row>
+    <row r="321" spans="1:6">
       <c r="A321"/>
       <c r="B321"/>
       <c r="C321"/>
       <c r="D321"/>
-    </row>
-    <row r="322" spans="1:5">
+      <c r="E321"/>
+    </row>
+    <row r="322" spans="1:6">
       <c r="A322"/>
       <c r="B322"/>
       <c r="C322"/>
       <c r="D322"/>
-    </row>
-    <row r="323" spans="1:5">
+      <c r="E322"/>
+    </row>
+    <row r="323" spans="1:6">
       <c r="A323"/>
       <c r="B323"/>
       <c r="C323"/>
       <c r="D323"/>
-    </row>
-    <row r="324" spans="1:5">
+      <c r="E323"/>
+    </row>
+    <row r="324" spans="1:6">
       <c r="A324"/>
       <c r="B324"/>
       <c r="C324"/>
       <c r="D324"/>
-    </row>
-    <row r="325" spans="1:5">
+      <c r="E324"/>
+    </row>
+    <row r="325" spans="1:6">
       <c r="A325"/>
       <c r="B325"/>
       <c r="C325"/>
       <c r="D325"/>
-    </row>
-    <row r="326" spans="1:5">
+      <c r="E325"/>
+    </row>
+    <row r="326" spans="1:6">
       <c r="A326"/>
       <c r="B326"/>
       <c r="C326"/>
       <c r="D326"/>
-    </row>
-    <row r="327" spans="1:5">
+      <c r="E326"/>
+    </row>
+    <row r="327" spans="1:6">
       <c r="A327"/>
       <c r="B327"/>
       <c r="C327"/>
       <c r="D327"/>
-    </row>
-    <row r="328" spans="1:5">
+      <c r="E327"/>
+    </row>
+    <row r="328" spans="1:6">
       <c r="A328"/>
       <c r="B328"/>
       <c r="C328"/>
       <c r="D328"/>
-    </row>
-    <row r="329" spans="1:5">
+      <c r="E328"/>
+    </row>
+    <row r="329" spans="1:6">
       <c r="A329"/>
       <c r="B329"/>
       <c r="C329"/>
       <c r="D329"/>
-    </row>
-    <row r="330" spans="1:5">
+      <c r="E329"/>
+    </row>
+    <row r="330" spans="1:6">
       <c r="A330"/>
       <c r="B330"/>
       <c r="C330"/>
       <c r="D330"/>
-    </row>
-    <row r="331" spans="1:5">
+      <c r="E330"/>
+    </row>
+    <row r="331" spans="1:6">
       <c r="A331"/>
       <c r="B331"/>
       <c r="C331"/>
       <c r="D331"/>
-    </row>
-    <row r="332" spans="1:5">
+      <c r="E331"/>
+    </row>
+    <row r="332" spans="1:6">
       <c r="A332"/>
       <c r="B332"/>
       <c r="C332"/>
       <c r="D332"/>
-    </row>
-    <row r="333" spans="1:5">
+      <c r="E332"/>
+    </row>
+    <row r="333" spans="1:6">
       <c r="A333"/>
       <c r="B333"/>
       <c r="C333"/>
       <c r="D333"/>
-    </row>
-    <row r="334" spans="1:5">
+      <c r="E333"/>
+    </row>
+    <row r="334" spans="1:6">
       <c r="A334"/>
       <c r="B334"/>
       <c r="C334"/>
       <c r="D334"/>
-    </row>
-    <row r="335" spans="1:5">
+      <c r="E334"/>
+    </row>
+    <row r="335" spans="1:6">
       <c r="A335"/>
       <c r="B335"/>
       <c r="C335"/>
       <c r="D335"/>
-    </row>
-    <row r="336" spans="1:5">
+      <c r="E335"/>
+    </row>
+    <row r="336" spans="1:6">
       <c r="A336"/>
       <c r="B336"/>
       <c r="C336"/>
       <c r="D336"/>
-    </row>
-    <row r="337" spans="1:5">
+      <c r="E336"/>
+    </row>
+    <row r="337" spans="1:6">
       <c r="A337"/>
       <c r="B337"/>
       <c r="C337"/>
       <c r="D337"/>
-    </row>
-    <row r="338" spans="1:5">
+      <c r="E337"/>
+    </row>
+    <row r="338" spans="1:6">
       <c r="A338"/>
       <c r="B338"/>
       <c r="C338"/>
       <c r="D338"/>
-    </row>
-    <row r="339" spans="1:5">
+      <c r="E338"/>
+    </row>
+    <row r="339" spans="1:6">
       <c r="A339"/>
       <c r="B339"/>
       <c r="C339"/>
       <c r="D339"/>
-    </row>
-    <row r="340" spans="1:5">
+      <c r="E339"/>
+    </row>
+    <row r="340" spans="1:6">
       <c r="A340"/>
       <c r="B340"/>
       <c r="C340"/>
       <c r="D340"/>
-    </row>
-    <row r="341" spans="1:5">
+      <c r="E340"/>
+    </row>
+    <row r="341" spans="1:6">
       <c r="A341"/>
       <c r="B341"/>
       <c r="C341"/>
       <c r="D341"/>
-    </row>
-    <row r="342" spans="1:5">
+      <c r="E341"/>
+    </row>
+    <row r="342" spans="1:6">
       <c r="A342"/>
       <c r="B342"/>
       <c r="C342"/>
       <c r="D342"/>
-    </row>
-    <row r="343" spans="1:5">
+      <c r="E342"/>
+    </row>
+    <row r="343" spans="1:6">
       <c r="A343"/>
       <c r="B343"/>
       <c r="C343"/>
       <c r="D343"/>
-    </row>
-    <row r="344" spans="1:5">
+      <c r="E343"/>
+    </row>
+    <row r="344" spans="1:6">
       <c r="A344"/>
       <c r="B344"/>
       <c r="C344"/>
       <c r="D344"/>
-    </row>
-    <row r="345" spans="1:5">
+      <c r="E344"/>
+    </row>
+    <row r="345" spans="1:6">
       <c r="A345"/>
       <c r="B345"/>
       <c r="C345"/>
       <c r="D345"/>
-    </row>
-    <row r="346" spans="1:5">
+      <c r="E345"/>
+    </row>
+    <row r="346" spans="1:6">
       <c r="A346"/>
       <c r="B346"/>
       <c r="C346"/>
       <c r="D346"/>
-    </row>
-    <row r="347" spans="1:5">
+      <c r="E346"/>
+    </row>
+    <row r="347" spans="1:6">
       <c r="A347"/>
       <c r="B347"/>
       <c r="C347"/>
       <c r="D347"/>
-    </row>
-    <row r="348" spans="1:5">
+      <c r="E347"/>
+    </row>
+    <row r="348" spans="1:6">
       <c r="A348"/>
       <c r="B348"/>
       <c r="C348"/>
       <c r="D348"/>
-    </row>
-    <row r="349" spans="1:5">
+      <c r="E348"/>
+    </row>
+    <row r="349" spans="1:6">
       <c r="A349"/>
       <c r="B349"/>
       <c r="C349"/>
       <c r="D349"/>
-    </row>
-    <row r="350" spans="1:5">
+      <c r="E349"/>
+    </row>
+    <row r="350" spans="1:6">
       <c r="A350"/>
       <c r="B350"/>
       <c r="C350"/>
       <c r="D350"/>
-    </row>
-    <row r="351" spans="1:5">
+      <c r="E350"/>
+    </row>
+    <row r="351" spans="1:6">
       <c r="A351"/>
       <c r="B351"/>
       <c r="C351"/>
       <c r="D351"/>
-    </row>
-    <row r="352" spans="1:5">
+      <c r="E351"/>
+    </row>
+    <row r="352" spans="1:6">
       <c r="A352"/>
       <c r="B352"/>
       <c r="C352"/>
       <c r="D352"/>
-    </row>
-    <row r="353" spans="1:5">
+      <c r="E352"/>
+    </row>
+    <row r="353" spans="1:6">
       <c r="A353"/>
       <c r="B353"/>
       <c r="C353"/>
       <c r="D353"/>
-    </row>
-    <row r="354" spans="1:5">
+      <c r="E353"/>
+    </row>
+    <row r="354" spans="1:6">
       <c r="A354"/>
       <c r="B354"/>
       <c r="C354"/>
       <c r="D354"/>
-    </row>
-    <row r="355" spans="1:5">
+      <c r="E354"/>
+    </row>
+    <row r="355" spans="1:6">
       <c r="A355"/>
       <c r="B355"/>
       <c r="C355"/>
       <c r="D355"/>
-    </row>
-    <row r="356" spans="1:5">
+      <c r="E355"/>
+    </row>
+    <row r="356" spans="1:6">
       <c r="A356"/>
       <c r="B356"/>
       <c r="C356"/>
       <c r="D356"/>
-    </row>
-    <row r="357" spans="1:5">
+      <c r="E356"/>
+    </row>
+    <row r="357" spans="1:6">
       <c r="A357"/>
       <c r="B357"/>
       <c r="C357"/>
       <c r="D357"/>
-    </row>
-    <row r="358" spans="1:5">
+      <c r="E357"/>
+    </row>
+    <row r="358" spans="1:6">
       <c r="A358"/>
       <c r="B358"/>
       <c r="C358"/>
       <c r="D358"/>
-    </row>
-    <row r="359" spans="1:5">
+      <c r="E358"/>
+    </row>
+    <row r="359" spans="1:6">
       <c r="A359"/>
       <c r="B359"/>
       <c r="C359"/>
       <c r="D359"/>
-    </row>
-    <row r="360" spans="1:5">
+      <c r="E359"/>
+    </row>
+    <row r="360" spans="1:6">
       <c r="A360"/>
       <c r="B360"/>
       <c r="C360"/>
       <c r="D360"/>
-    </row>
-    <row r="361" spans="1:5">
+      <c r="E360"/>
+    </row>
+    <row r="361" spans="1:6">
       <c r="A361"/>
       <c r="B361"/>
       <c r="C361"/>
       <c r="D361"/>
-    </row>
-    <row r="362" spans="1:5">
+      <c r="E361"/>
+    </row>
+    <row r="362" spans="1:6">
       <c r="A362"/>
       <c r="B362"/>
       <c r="C362"/>
       <c r="D362"/>
-    </row>
-    <row r="363" spans="1:5">
+      <c r="E362"/>
+    </row>
+    <row r="363" spans="1:6">
       <c r="A363"/>
       <c r="B363"/>
       <c r="C363"/>
       <c r="D363"/>
-    </row>
-    <row r="364" spans="1:5">
+      <c r="E363"/>
+    </row>
+    <row r="364" spans="1:6">
       <c r="A364"/>
       <c r="B364"/>
       <c r="C364"/>
       <c r="D364"/>
-    </row>
-    <row r="365" spans="1:5">
+      <c r="E364"/>
+    </row>
+    <row r="365" spans="1:6">
       <c r="A365"/>
       <c r="B365"/>
       <c r="C365"/>
       <c r="D365"/>
-    </row>
-    <row r="366" spans="1:5">
+      <c r="E365"/>
+    </row>
+    <row r="366" spans="1:6">
       <c r="A366"/>
       <c r="B366"/>
       <c r="C366"/>
       <c r="D366"/>
-    </row>
-    <row r="367" spans="1:5">
+      <c r="E366"/>
+    </row>
+    <row r="367" spans="1:6">
       <c r="A367"/>
       <c r="B367"/>
       <c r="C367"/>
       <c r="D367"/>
-    </row>
-    <row r="368" spans="1:5">
+      <c r="E367"/>
+    </row>
+    <row r="368" spans="1:6">
       <c r="A368"/>
       <c r="B368"/>
       <c r="C368"/>
       <c r="D368"/>
-    </row>
-    <row r="369" spans="1:5">
+      <c r="E368"/>
+    </row>
+    <row r="369" spans="1:6">
       <c r="A369"/>
       <c r="B369"/>
       <c r="C369"/>
       <c r="D369"/>
-    </row>
-    <row r="370" spans="1:5">
+      <c r="E369"/>
+    </row>
+    <row r="370" spans="1:6">
       <c r="A370"/>
       <c r="B370"/>
       <c r="C370"/>
       <c r="D370"/>
-    </row>
-    <row r="371" spans="1:5">
+      <c r="E370"/>
+    </row>
+    <row r="371" spans="1:6">
       <c r="A371"/>
       <c r="B371"/>
       <c r="C371"/>
       <c r="D371"/>
-    </row>
-    <row r="372" spans="1:5">
+      <c r="E371"/>
+    </row>
+    <row r="372" spans="1:6">
       <c r="A372"/>
       <c r="B372"/>
       <c r="C372"/>
       <c r="D372"/>
-    </row>
-    <row r="373" spans="1:5">
+      <c r="E372"/>
+    </row>
+    <row r="373" spans="1:6">
       <c r="A373"/>
       <c r="B373"/>
       <c r="C373"/>
       <c r="D373"/>
-    </row>
-    <row r="374" spans="1:5">
+      <c r="E373"/>
+    </row>
+    <row r="374" spans="1:6">
       <c r="A374"/>
       <c r="B374"/>
       <c r="C374"/>
       <c r="D374"/>
-    </row>
-    <row r="375" spans="1:5">
+      <c r="E374"/>
+    </row>
+    <row r="375" spans="1:6">
       <c r="A375"/>
       <c r="B375"/>
       <c r="C375"/>
       <c r="D375"/>
-    </row>
-    <row r="376" spans="1:5">
+      <c r="E375"/>
+    </row>
+    <row r="376" spans="1:6">
       <c r="A376"/>
       <c r="B376"/>
       <c r="C376"/>
       <c r="D376"/>
-    </row>
-    <row r="377" spans="1:5">
+      <c r="E376"/>
+    </row>
+    <row r="377" spans="1:6">
       <c r="A377"/>
       <c r="B377"/>
       <c r="C377"/>
       <c r="D377"/>
-    </row>
-    <row r="378" spans="1:5">
+      <c r="E377"/>
+    </row>
+    <row r="378" spans="1:6">
       <c r="A378"/>
       <c r="B378"/>
       <c r="C378"/>
       <c r="D378"/>
-    </row>
-    <row r="379" spans="1:5">
+      <c r="E378"/>
+    </row>
+    <row r="379" spans="1:6">
       <c r="A379"/>
       <c r="B379"/>
       <c r="C379"/>
       <c r="D379"/>
-    </row>
-    <row r="380" spans="1:5">
+      <c r="E379"/>
+    </row>
+    <row r="380" spans="1:6">
       <c r="A380"/>
       <c r="B380"/>
       <c r="C380"/>
       <c r="D380"/>
-    </row>
-    <row r="381" spans="1:5">
+      <c r="E380"/>
+    </row>
+    <row r="381" spans="1:6">
       <c r="A381"/>
       <c r="B381"/>
       <c r="C381"/>
       <c r="D381"/>
-    </row>
-    <row r="382" spans="1:5">
+      <c r="E381"/>
+    </row>
+    <row r="382" spans="1:6">
       <c r="A382"/>
       <c r="B382"/>
       <c r="C382"/>
       <c r="D382"/>
-    </row>
-    <row r="383" spans="1:5">
+      <c r="E382"/>
+    </row>
+    <row r="383" spans="1:6">
       <c r="A383"/>
       <c r="B383"/>
       <c r="C383"/>
       <c r="D383"/>
-    </row>
-    <row r="384" spans="1:5">
+      <c r="E383"/>
+    </row>
+    <row r="384" spans="1:6">
       <c r="A384"/>
       <c r="B384"/>
       <c r="C384"/>
       <c r="D384"/>
-    </row>
-    <row r="385" spans="1:5">
+      <c r="E384"/>
+    </row>
+    <row r="385" spans="1:6">
       <c r="A385"/>
       <c r="B385"/>
       <c r="C385"/>
       <c r="D385"/>
-    </row>
-    <row r="386" spans="1:5">
+      <c r="E385"/>
+    </row>
+    <row r="386" spans="1:6">
       <c r="A386"/>
       <c r="B386"/>
       <c r="C386"/>
       <c r="D386"/>
-    </row>
-    <row r="387" spans="1:5">
+      <c r="E386"/>
+    </row>
+    <row r="387" spans="1:6">
       <c r="A387"/>
       <c r="B387"/>
       <c r="C387"/>
       <c r="D387"/>
-    </row>
-    <row r="388" spans="1:5">
+      <c r="E387"/>
+    </row>
+    <row r="388" spans="1:6">
       <c r="A388"/>
       <c r="B388"/>
       <c r="C388"/>
       <c r="D388"/>
-    </row>
-    <row r="389" spans="1:5">
+      <c r="E388"/>
+    </row>
+    <row r="389" spans="1:6">
       <c r="A389"/>
       <c r="B389"/>
       <c r="C389"/>
       <c r="D389"/>
-    </row>
-    <row r="390" spans="1:5">
+      <c r="E389"/>
+    </row>
+    <row r="390" spans="1:6">
       <c r="A390"/>
       <c r="B390"/>
       <c r="C390"/>
       <c r="D390"/>
-    </row>
-    <row r="391" spans="1:5">
+      <c r="E390"/>
+    </row>
+    <row r="391" spans="1:6">
       <c r="A391"/>
       <c r="B391"/>
       <c r="C391"/>
       <c r="D391"/>
-    </row>
-    <row r="392" spans="1:5">
+      <c r="E391"/>
+    </row>
+    <row r="392" spans="1:6">
       <c r="A392"/>
       <c r="B392"/>
       <c r="C392"/>
       <c r="D392"/>
-    </row>
-    <row r="393" spans="1:5">
+      <c r="E392"/>
+    </row>
+    <row r="393" spans="1:6">
       <c r="A393"/>
       <c r="B393"/>
       <c r="C393"/>
       <c r="D393"/>
-    </row>
-    <row r="394" spans="1:5">
+      <c r="E393"/>
+    </row>
+    <row r="394" spans="1:6">
       <c r="A394"/>
       <c r="B394"/>
       <c r="C394"/>
       <c r="D394"/>
-    </row>
-    <row r="395" spans="1:5">
+      <c r="E394"/>
+    </row>
+    <row r="395" spans="1:6">
       <c r="A395"/>
       <c r="B395"/>
       <c r="C395"/>
       <c r="D395"/>
-    </row>
-    <row r="396" spans="1:5">
+      <c r="E395"/>
+    </row>
+    <row r="396" spans="1:6">
       <c r="A396"/>
       <c r="B396"/>
       <c r="C396"/>
       <c r="D396"/>
-    </row>
-    <row r="397" spans="1:5">
+      <c r="E396"/>
+    </row>
+    <row r="397" spans="1:6">
       <c r="A397"/>
       <c r="B397"/>
       <c r="C397"/>
       <c r="D397"/>
-    </row>
-    <row r="398" spans="1:5">
+      <c r="E397"/>
+    </row>
+    <row r="398" spans="1:6">
       <c r="A398"/>
       <c r="B398"/>
       <c r="C398"/>
       <c r="D398"/>
-    </row>
-    <row r="399" spans="1:5">
+      <c r="E398"/>
+    </row>
+    <row r="399" spans="1:6">
       <c r="A399"/>
       <c r="B399"/>
       <c r="C399"/>
       <c r="D399"/>
-    </row>
-    <row r="400" spans="1:5">
+      <c r="E399"/>
+    </row>
+    <row r="400" spans="1:6">
       <c r="A400"/>
       <c r="B400"/>
       <c r="C400"/>
       <c r="D400"/>
-    </row>
-    <row r="401" spans="1:5">
+      <c r="E400"/>
+    </row>
+    <row r="401" spans="1:6">
       <c r="A401"/>
       <c r="B401"/>
       <c r="C401"/>
       <c r="D401"/>
-    </row>
-    <row r="402" spans="1:5">
+      <c r="E401"/>
+    </row>
+    <row r="402" spans="1:6">
       <c r="A402"/>
       <c r="B402"/>
       <c r="C402"/>
       <c r="D402"/>
-    </row>
-    <row r="403" spans="1:5">
+      <c r="E402"/>
+    </row>
+    <row r="403" spans="1:6">
       <c r="A403"/>
       <c r="B403"/>
       <c r="C403"/>
       <c r="D403"/>
-    </row>
-    <row r="404" spans="1:5">
+      <c r="E403"/>
+    </row>
+    <row r="404" spans="1:6">
       <c r="A404"/>
       <c r="B404"/>
       <c r="C404"/>
       <c r="D404"/>
-    </row>
-    <row r="405" spans="1:5">
+      <c r="E404"/>
+    </row>
+    <row r="405" spans="1:6">
       <c r="A405"/>
       <c r="B405"/>
       <c r="C405"/>
       <c r="D405"/>
-    </row>
-    <row r="406" spans="1:5">
+      <c r="E405"/>
+    </row>
+    <row r="406" spans="1:6">
       <c r="A406"/>
       <c r="B406"/>
       <c r="C406"/>
       <c r="D406"/>
-    </row>
-    <row r="407" spans="1:5">
+      <c r="E406"/>
+    </row>
+    <row r="407" spans="1:6">
       <c r="A407"/>
       <c r="B407"/>
       <c r="C407"/>
       <c r="D407"/>
-    </row>
-    <row r="408" spans="1:5">
+      <c r="E407"/>
+    </row>
+    <row r="408" spans="1:6">
       <c r="A408"/>
       <c r="B408"/>
       <c r="C408"/>
       <c r="D408"/>
-    </row>
-    <row r="409" spans="1:5">
+      <c r="E408"/>
+    </row>
+    <row r="409" spans="1:6">
       <c r="A409"/>
       <c r="B409"/>
       <c r="C409"/>
       <c r="D409"/>
-    </row>
-    <row r="410" spans="1:5">
+      <c r="E409"/>
+    </row>
+    <row r="410" spans="1:6">
       <c r="A410"/>
       <c r="B410"/>
       <c r="C410"/>
       <c r="D410"/>
-    </row>
-    <row r="411" spans="1:5">
+      <c r="E410"/>
+    </row>
+    <row r="411" spans="1:6">
       <c r="A411"/>
       <c r="B411"/>
       <c r="C411"/>
       <c r="D411"/>
-    </row>
-    <row r="412" spans="1:5">
+      <c r="E411"/>
+    </row>
+    <row r="412" spans="1:6">
       <c r="A412"/>
       <c r="B412"/>
       <c r="C412"/>
       <c r="D412"/>
-    </row>
-    <row r="413" spans="1:5">
+      <c r="E412"/>
+    </row>
+    <row r="413" spans="1:6">
       <c r="A413"/>
       <c r="B413"/>
       <c r="C413"/>
       <c r="D413"/>
-    </row>
-    <row r="414" spans="1:5">
+      <c r="E413"/>
+    </row>
+    <row r="414" spans="1:6">
       <c r="A414"/>
       <c r="B414"/>
       <c r="C414"/>
       <c r="D414"/>
-    </row>
-    <row r="415" spans="1:5">
+      <c r="E414"/>
+    </row>
+    <row r="415" spans="1:6">
       <c r="A415"/>
       <c r="B415"/>
       <c r="C415"/>
       <c r="D415"/>
-    </row>
-    <row r="416" spans="1:5">
+      <c r="E415"/>
+    </row>
+    <row r="416" spans="1:6">
       <c r="A416"/>
       <c r="B416"/>
       <c r="C416"/>
       <c r="D416"/>
-    </row>
-    <row r="417" spans="1:5">
+      <c r="E416"/>
+    </row>
+    <row r="417" spans="1:6">
       <c r="A417"/>
       <c r="B417"/>
       <c r="C417"/>
       <c r="D417"/>
-    </row>
-    <row r="418" spans="1:5">
+      <c r="E417"/>
+    </row>
+    <row r="418" spans="1:6">
       <c r="A418"/>
       <c r="B418"/>
       <c r="C418"/>
       <c r="D418"/>
-    </row>
-    <row r="419" spans="1:5">
+      <c r="E418"/>
+    </row>
+    <row r="419" spans="1:6">
       <c r="A419"/>
       <c r="B419"/>
       <c r="C419"/>
       <c r="D419"/>
-    </row>
-    <row r="420" spans="1:5">
+      <c r="E419"/>
+    </row>
+    <row r="420" spans="1:6">
       <c r="A420"/>
       <c r="B420"/>
       <c r="C420"/>
       <c r="D420"/>
-    </row>
-    <row r="421" spans="1:5">
+      <c r="E420"/>
+    </row>
+    <row r="421" spans="1:6">
       <c r="A421"/>
       <c r="B421"/>
       <c r="C421"/>
       <c r="D421"/>
-    </row>
-    <row r="422" spans="1:5">
+      <c r="E421"/>
+    </row>
+    <row r="422" spans="1:6">
       <c r="A422"/>
       <c r="B422"/>
       <c r="C422"/>
       <c r="D422"/>
-    </row>
-    <row r="423" spans="1:5">
+      <c r="E422"/>
+    </row>
+    <row r="423" spans="1:6">
       <c r="A423"/>
       <c r="B423"/>
       <c r="C423"/>
       <c r="D423"/>
-    </row>
-    <row r="424" spans="1:5">
+      <c r="E423"/>
+    </row>
+    <row r="424" spans="1:6">
       <c r="A424"/>
       <c r="B424"/>
       <c r="C424"/>
       <c r="D424"/>
-    </row>
-    <row r="425" spans="1:5">
+      <c r="E424"/>
+    </row>
+    <row r="425" spans="1:6">
       <c r="A425"/>
       <c r="B425"/>
       <c r="C425"/>
       <c r="D425"/>
-    </row>
-    <row r="426" spans="1:5">
+      <c r="E425"/>
+    </row>
+    <row r="426" spans="1:6">
       <c r="A426"/>
       <c r="B426"/>
       <c r="C426"/>
       <c r="D426"/>
-    </row>
-    <row r="427" spans="1:5">
+      <c r="E426"/>
+    </row>
+    <row r="427" spans="1:6">
       <c r="A427"/>
       <c r="B427"/>
       <c r="C427"/>
       <c r="D427"/>
-    </row>
-    <row r="428" spans="1:5">
+      <c r="E427"/>
+    </row>
+    <row r="428" spans="1:6">
       <c r="A428"/>
       <c r="B428"/>
       <c r="C428"/>
       <c r="D428"/>
-    </row>
-    <row r="429" spans="1:5">
+      <c r="E428"/>
+    </row>
+    <row r="429" spans="1:6">
       <c r="A429"/>
       <c r="B429"/>
       <c r="C429"/>
       <c r="D429"/>
-    </row>
-    <row r="430" spans="1:5">
+      <c r="E429"/>
+    </row>
+    <row r="430" spans="1:6">
       <c r="A430"/>
       <c r="B430"/>
       <c r="C430"/>
       <c r="D430"/>
-    </row>
-    <row r="431" spans="1:5">
+      <c r="E430"/>
+    </row>
+    <row r="431" spans="1:6">
       <c r="A431"/>
       <c r="B431"/>
       <c r="C431"/>
       <c r="D431"/>
-    </row>
-    <row r="432" spans="1:5">
+      <c r="E431"/>
+    </row>
+    <row r="432" spans="1:6">
       <c r="A432"/>
       <c r="B432"/>
       <c r="C432"/>
       <c r="D432"/>
-    </row>
-    <row r="433" spans="1:5">
+      <c r="E432"/>
+    </row>
+    <row r="433" spans="1:6">
       <c r="A433"/>
       <c r="B433"/>
       <c r="C433"/>
       <c r="D433"/>
-    </row>
-    <row r="434" spans="1:5">
+      <c r="E433"/>
+    </row>
+    <row r="434" spans="1:6">
       <c r="A434"/>
       <c r="B434"/>
       <c r="C434"/>
       <c r="D434"/>
-    </row>
-    <row r="435" spans="1:5">
+      <c r="E434"/>
+    </row>
+    <row r="435" spans="1:6">
       <c r="A435"/>
       <c r="B435"/>
       <c r="C435"/>
       <c r="D435"/>
-    </row>
-    <row r="436" spans="1:5">
+      <c r="E435"/>
+    </row>
+    <row r="436" spans="1:6">
       <c r="A436"/>
       <c r="B436"/>
       <c r="C436"/>
       <c r="D436"/>
-    </row>
-    <row r="437" spans="1:5">
+      <c r="E436"/>
+    </row>
+    <row r="437" spans="1:6">
       <c r="A437"/>
       <c r="B437"/>
       <c r="C437"/>
       <c r="D437"/>
-    </row>
-    <row r="438" spans="1:5">
+      <c r="E437"/>
+    </row>
+    <row r="438" spans="1:6">
       <c r="A438"/>
       <c r="B438"/>
       <c r="C438"/>
       <c r="D438"/>
-    </row>
-    <row r="439" spans="1:5">
+      <c r="E438"/>
+    </row>
+    <row r="439" spans="1:6">
       <c r="A439"/>
       <c r="B439"/>
       <c r="C439"/>
       <c r="D439"/>
-    </row>
-    <row r="440" spans="1:5">
+      <c r="E439"/>
+    </row>
+    <row r="440" spans="1:6">
       <c r="A440"/>
       <c r="B440"/>
       <c r="C440"/>
       <c r="D440"/>
-    </row>
-    <row r="441" spans="1:5">
+      <c r="E440"/>
+    </row>
+    <row r="441" spans="1:6">
       <c r="A441"/>
       <c r="B441"/>
       <c r="C441"/>
       <c r="D441"/>
-    </row>
-    <row r="442" spans="1:5">
+      <c r="E441"/>
+    </row>
+    <row r="442" spans="1:6">
       <c r="A442"/>
       <c r="B442"/>
       <c r="C442"/>
       <c r="D442"/>
-    </row>
-    <row r="443" spans="1:5">
+      <c r="E442"/>
+    </row>
+    <row r="443" spans="1:6">
       <c r="A443"/>
       <c r="B443"/>
       <c r="C443"/>
       <c r="D443"/>
-    </row>
-    <row r="444" spans="1:5">
+      <c r="E443"/>
+    </row>
+    <row r="444" spans="1:6">
       <c r="A444"/>
       <c r="B444"/>
       <c r="C444"/>
       <c r="D444"/>
-    </row>
-    <row r="445" spans="1:5">
+      <c r="E444"/>
+    </row>
+    <row r="445" spans="1:6">
       <c r="A445"/>
       <c r="B445"/>
       <c r="C445"/>
       <c r="D445"/>
-    </row>
-    <row r="446" spans="1:5">
+      <c r="E445"/>
+    </row>
+    <row r="446" spans="1:6">
       <c r="A446"/>
       <c r="B446"/>
       <c r="C446"/>
       <c r="D446"/>
-    </row>
-    <row r="447" spans="1:5">
+      <c r="E446"/>
+    </row>
+    <row r="447" spans="1:6">
       <c r="A447"/>
       <c r="B447"/>
       <c r="C447"/>
       <c r="D447"/>
-    </row>
-    <row r="448" spans="1:5">
+      <c r="E447"/>
+    </row>
+    <row r="448" spans="1:6">
       <c r="A448"/>
       <c r="B448"/>
       <c r="C448"/>
       <c r="D448"/>
-    </row>
-    <row r="449" spans="1:5">
+      <c r="E448"/>
+    </row>
+    <row r="449" spans="1:6">
       <c r="A449"/>
       <c r="B449"/>
       <c r="C449"/>
       <c r="D449"/>
-    </row>
-    <row r="450" spans="1:5">
+      <c r="E449"/>
+    </row>
+    <row r="450" spans="1:6">
       <c r="A450"/>
       <c r="B450"/>
       <c r="C450"/>
       <c r="D450"/>
-    </row>
-    <row r="451" spans="1:5">
+      <c r="E450"/>
+    </row>
+    <row r="451" spans="1:6">
       <c r="A451"/>
       <c r="B451"/>
       <c r="C451"/>
       <c r="D451"/>
-    </row>
-    <row r="452" spans="1:5">
+      <c r="E451"/>
+    </row>
+    <row r="452" spans="1:6">
       <c r="A452"/>
       <c r="B452"/>
       <c r="C452"/>
       <c r="D452"/>
-    </row>
-    <row r="453" spans="1:5">
+      <c r="E452"/>
+    </row>
+    <row r="453" spans="1:6">
       <c r="A453"/>
       <c r="B453"/>
       <c r="C453"/>
       <c r="D453"/>
-    </row>
-    <row r="454" spans="1:5">
+      <c r="E453"/>
+    </row>
+    <row r="454" spans="1:6">
       <c r="A454"/>
       <c r="B454"/>
       <c r="C454"/>
       <c r="D454"/>
-    </row>
-    <row r="455" spans="1:5">
+      <c r="E454"/>
+    </row>
+    <row r="455" spans="1:6">
       <c r="A455"/>
       <c r="B455"/>
       <c r="C455"/>
       <c r="D455"/>
-    </row>
-    <row r="456" spans="1:5">
+      <c r="E455"/>
+    </row>
+    <row r="456" spans="1:6">
       <c r="A456"/>
       <c r="B456"/>
       <c r="C456"/>
       <c r="D456"/>
-    </row>
-    <row r="457" spans="1:5">
+      <c r="E456"/>
+    </row>
+    <row r="457" spans="1:6">
       <c r="A457"/>
       <c r="B457"/>
       <c r="C457"/>
       <c r="D457"/>
-    </row>
-    <row r="458" spans="1:5">
+      <c r="E457"/>
+    </row>
+    <row r="458" spans="1:6">
       <c r="A458"/>
       <c r="B458"/>
       <c r="C458"/>
       <c r="D458"/>
-    </row>
-    <row r="459" spans="1:5">
+      <c r="E458"/>
+    </row>
+    <row r="459" spans="1:6">
       <c r="A459"/>
       <c r="B459"/>
       <c r="C459"/>
       <c r="D459"/>
-    </row>
-    <row r="460" spans="1:5">
+      <c r="E459"/>
+    </row>
+    <row r="460" spans="1:6">
       <c r="A460"/>
       <c r="B460"/>
       <c r="C460"/>
       <c r="D460"/>
-    </row>
-    <row r="461" spans="1:5">
+      <c r="E460"/>
+    </row>
+    <row r="461" spans="1:6">
       <c r="A461"/>
       <c r="B461"/>
       <c r="C461"/>
       <c r="D461"/>
-    </row>
-    <row r="462" spans="1:5">
+      <c r="E461"/>
+    </row>
+    <row r="462" spans="1:6">
       <c r="A462"/>
       <c r="B462"/>
       <c r="C462"/>
       <c r="D462"/>
-    </row>
-    <row r="463" spans="1:5">
+      <c r="E462"/>
+    </row>
+    <row r="463" spans="1:6">
       <c r="A463"/>
       <c r="B463"/>
       <c r="C463"/>
       <c r="D463"/>
-    </row>
-    <row r="464" spans="1:5">
+      <c r="E463"/>
+    </row>
+    <row r="464" spans="1:6">
       <c r="A464"/>
       <c r="B464"/>
       <c r="C464"/>
       <c r="D464"/>
-    </row>
-    <row r="465" spans="1:5">
+      <c r="E464"/>
+    </row>
+    <row r="465" spans="1:6">
       <c r="A465"/>
       <c r="B465"/>
       <c r="C465"/>
       <c r="D465"/>
-    </row>
-    <row r="466" spans="1:5">
+      <c r="E465"/>
+    </row>
+    <row r="466" spans="1:6">
       <c r="A466"/>
       <c r="B466"/>
       <c r="C466"/>
       <c r="D466"/>
-    </row>
-    <row r="467" spans="1:5">
+      <c r="E466"/>
+    </row>
+    <row r="467" spans="1:6">
       <c r="A467"/>
       <c r="B467"/>
       <c r="C467"/>
       <c r="D467"/>
-    </row>
-    <row r="468" spans="1:5">
+      <c r="E467"/>
+    </row>
+    <row r="468" spans="1:6">
       <c r="A468"/>
       <c r="B468"/>
       <c r="C468"/>
       <c r="D468"/>
-    </row>
-    <row r="469" spans="1:5">
+      <c r="E468"/>
+    </row>
+    <row r="469" spans="1:6">
       <c r="A469"/>
       <c r="B469"/>
       <c r="C469"/>
       <c r="D469"/>
-    </row>
-    <row r="470" spans="1:5">
+      <c r="E469"/>
+    </row>
+    <row r="470" spans="1:6">
       <c r="A470"/>
       <c r="B470"/>
       <c r="C470"/>
       <c r="D470"/>
-    </row>
-    <row r="471" spans="1:5">
+      <c r="E470"/>
+    </row>
+    <row r="471" spans="1:6">
       <c r="A471"/>
       <c r="B471"/>
       <c r="C471"/>
       <c r="D471"/>
-    </row>
-    <row r="472" spans="1:5">
+      <c r="E471"/>
+    </row>
+    <row r="472" spans="1:6">
       <c r="A472"/>
       <c r="B472"/>
       <c r="C472"/>
       <c r="D472"/>
-    </row>
-    <row r="473" spans="1:5">
+      <c r="E472"/>
+    </row>
+    <row r="473" spans="1:6">
       <c r="A473"/>
       <c r="B473"/>
       <c r="C473"/>
       <c r="D473"/>
-    </row>
-    <row r="474" spans="1:5">
+      <c r="E473"/>
+    </row>
+    <row r="474" spans="1:6">
       <c r="A474"/>
       <c r="B474"/>
       <c r="C474"/>
       <c r="D474"/>
-    </row>
-    <row r="475" spans="1:5">
+      <c r="E474"/>
+    </row>
+    <row r="475" spans="1:6">
       <c r="A475"/>
       <c r="B475"/>
       <c r="C475"/>
       <c r="D475"/>
-    </row>
-    <row r="476" spans="1:5">
+      <c r="E475"/>
+    </row>
+    <row r="476" spans="1:6">
       <c r="A476"/>
       <c r="B476"/>
       <c r="C476"/>
       <c r="D476"/>
-    </row>
-    <row r="477" spans="1:5">
+      <c r="E476"/>
+    </row>
+    <row r="477" spans="1:6">
       <c r="A477"/>
       <c r="B477"/>
       <c r="C477"/>
       <c r="D477"/>
-    </row>
-    <row r="478" spans="1:5">
+      <c r="E477"/>
+    </row>
+    <row r="478" spans="1:6">
       <c r="A478"/>
       <c r="B478"/>
       <c r="C478"/>
       <c r="D478"/>
-    </row>
-    <row r="479" spans="1:5">
+      <c r="E478"/>
+    </row>
+    <row r="479" spans="1:6">
       <c r="A479"/>
       <c r="B479"/>
       <c r="C479"/>
       <c r="D479"/>
-    </row>
-    <row r="480" spans="1:5">
+      <c r="E479"/>
+    </row>
+    <row r="480" spans="1:6">
       <c r="A480"/>
       <c r="B480"/>
       <c r="C480"/>
       <c r="D480"/>
-    </row>
-    <row r="481" spans="1:5">
+      <c r="E480"/>
+    </row>
+    <row r="481" spans="1:6">
       <c r="A481"/>
       <c r="B481"/>
       <c r="C481"/>
       <c r="D481"/>
-    </row>
-    <row r="482" spans="1:5">
+      <c r="E481"/>
+    </row>
+    <row r="482" spans="1:6">
       <c r="A482"/>
       <c r="B482"/>
       <c r="C482"/>
       <c r="D482"/>
-    </row>
-    <row r="483" spans="1:5">
+      <c r="E482"/>
+    </row>
+    <row r="483" spans="1:6">
       <c r="A483"/>
       <c r="B483"/>
       <c r="C483"/>
       <c r="D483"/>
-    </row>
-    <row r="484" spans="1:5">
+      <c r="E483"/>
+    </row>
+    <row r="484" spans="1:6">
       <c r="A484"/>
       <c r="B484"/>
       <c r="C484"/>
       <c r="D484"/>
-    </row>
-    <row r="485" spans="1:5">
+      <c r="E484"/>
+    </row>
+    <row r="485" spans="1:6">
       <c r="A485"/>
       <c r="B485"/>
       <c r="C485"/>
       <c r="D485"/>
-    </row>
-    <row r="486" spans="1:5">
+      <c r="E485"/>
+    </row>
+    <row r="486" spans="1:6">
       <c r="A486"/>
       <c r="B486"/>
       <c r="C486"/>
       <c r="D486"/>
-    </row>
-    <row r="487" spans="1:5">
+      <c r="E486"/>
+    </row>
+    <row r="487" spans="1:6">
       <c r="A487"/>
       <c r="B487"/>
       <c r="C487"/>
       <c r="D487"/>
-    </row>
-    <row r="488" spans="1:5">
+      <c r="E487"/>
+    </row>
+    <row r="488" spans="1:6">
       <c r="A488"/>
       <c r="B488"/>
       <c r="C488"/>
       <c r="D488"/>
-    </row>
-    <row r="489" spans="1:5">
+      <c r="E488"/>
+    </row>
+    <row r="489" spans="1:6">
       <c r="A489"/>
       <c r="B489"/>
       <c r="C489"/>
       <c r="D489"/>
-    </row>
-    <row r="490" spans="1:5">
+      <c r="E489"/>
+    </row>
+    <row r="490" spans="1:6">
       <c r="A490"/>
       <c r="B490"/>
       <c r="C490"/>
       <c r="D490"/>
-    </row>
-    <row r="491" spans="1:5">
+      <c r="E490"/>
+    </row>
+    <row r="491" spans="1:6">
       <c r="A491"/>
       <c r="B491"/>
       <c r="C491"/>
       <c r="D491"/>
-    </row>
-    <row r="492" spans="1:5">
+      <c r="E491"/>
+    </row>
+    <row r="492" spans="1:6">
       <c r="A492"/>
       <c r="B492"/>
       <c r="C492"/>
       <c r="D492"/>
-    </row>
-    <row r="493" spans="1:5">
+      <c r="E492"/>
+    </row>
+    <row r="493" spans="1:6">
       <c r="A493"/>
       <c r="B493"/>
       <c r="C493"/>
       <c r="D493"/>
-    </row>
-    <row r="494" spans="1:5">
+      <c r="E493"/>
+    </row>
+    <row r="494" spans="1:6">
       <c r="A494"/>
       <c r="B494"/>
       <c r="C494"/>
       <c r="D494"/>
-    </row>
-    <row r="495" spans="1:5">
+      <c r="E494"/>
+    </row>
+    <row r="495" spans="1:6">
       <c r="A495"/>
       <c r="B495"/>
       <c r="C495"/>
       <c r="D495"/>
-    </row>
-    <row r="496" spans="1:5">
+      <c r="E495"/>
+    </row>
+    <row r="496" spans="1:6">
       <c r="A496"/>
       <c r="B496"/>
       <c r="C496"/>
       <c r="D496"/>
-    </row>
-    <row r="497" spans="1:5">
+      <c r="E496"/>
+    </row>
+    <row r="497" spans="1:6">
       <c r="A497"/>
       <c r="B497"/>
       <c r="C497"/>
       <c r="D497"/>
-    </row>
-    <row r="498" spans="1:5">
+      <c r="E497"/>
+    </row>
+    <row r="498" spans="1:6">
       <c r="A498"/>
       <c r="B498"/>
       <c r="C498"/>
       <c r="D498"/>
-    </row>
-    <row r="499" spans="1:5">
+      <c r="E498"/>
+    </row>
+    <row r="499" spans="1:6">
       <c r="A499"/>
       <c r="B499"/>
       <c r="C499"/>
       <c r="D499"/>
-    </row>
-    <row r="500" spans="1:5">
+      <c r="E499"/>
+    </row>
+    <row r="500" spans="1:6">
       <c r="A500"/>
       <c r="B500"/>
       <c r="C500"/>
       <c r="D500"/>
-    </row>
-    <row r="501" spans="1:5">
+      <c r="E500"/>
+    </row>
+    <row r="501" spans="1:6">
       <c r="A501"/>
       <c r="B501"/>
       <c r="C501"/>
       <c r="D501"/>
-    </row>
-    <row r="502" spans="1:5">
+      <c r="E501"/>
+    </row>
+    <row r="502" spans="1:6">
       <c r="A502"/>
       <c r="B502"/>
       <c r="C502"/>
       <c r="D502"/>
-    </row>
-    <row r="503" spans="1:5">
+      <c r="E502"/>
+    </row>
+    <row r="503" spans="1:6">
       <c r="A503"/>
       <c r="B503"/>
       <c r="C503"/>
       <c r="D503"/>
-    </row>
-    <row r="504" spans="1:5">
+      <c r="E503"/>
+    </row>
+    <row r="504" spans="1:6">
       <c r="A504"/>
       <c r="B504"/>
       <c r="C504"/>
       <c r="D504"/>
-    </row>
-    <row r="505" spans="1:5">
+      <c r="E504"/>
+    </row>
+    <row r="505" spans="1:6">
       <c r="A505"/>
       <c r="B505"/>
       <c r="C505"/>
       <c r="D505"/>
-    </row>
-    <row r="506" spans="1:5">
+      <c r="E505"/>
+    </row>
+    <row r="506" spans="1:6">
       <c r="A506"/>
       <c r="B506"/>
       <c r="C506"/>
       <c r="D506"/>
-    </row>
-    <row r="507" spans="1:5">
+      <c r="E506"/>
+    </row>
+    <row r="507" spans="1:6">
       <c r="A507"/>
       <c r="B507"/>
       <c r="C507"/>
       <c r="D507"/>
-    </row>
-    <row r="508" spans="1:5">
+      <c r="E507"/>
+    </row>
+    <row r="508" spans="1:6">
       <c r="A508"/>
       <c r="B508"/>
       <c r="C508"/>
       <c r="D508"/>
-    </row>
-    <row r="509" spans="1:5">
+      <c r="E508"/>
+    </row>
+    <row r="509" spans="1:6">
       <c r="A509"/>
       <c r="B509"/>
       <c r="C509"/>
       <c r="D509"/>
-    </row>
-    <row r="510" spans="1:5">
+      <c r="E509"/>
+    </row>
+    <row r="510" spans="1:6">
       <c r="A510"/>
       <c r="B510"/>
       <c r="C510"/>
       <c r="D510"/>
-    </row>
-    <row r="511" spans="1:5">
+      <c r="E510"/>
+    </row>
+    <row r="511" spans="1:6">
       <c r="A511"/>
       <c r="B511"/>
       <c r="C511"/>
       <c r="D511"/>
-    </row>
-    <row r="512" spans="1:5">
+      <c r="E511"/>
+    </row>
+    <row r="512" spans="1:6">
       <c r="A512"/>
       <c r="B512"/>
       <c r="C512"/>
       <c r="D512"/>
-    </row>
-    <row r="513" spans="1:5">
+      <c r="E512"/>
+    </row>
+    <row r="513" spans="1:6">
       <c r="A513"/>
       <c r="B513"/>
       <c r="C513"/>
       <c r="D513"/>
-    </row>
-    <row r="514" spans="1:5">
+      <c r="E513"/>
+    </row>
+    <row r="514" spans="1:6">
       <c r="A514"/>
       <c r="B514"/>
       <c r="C514"/>
       <c r="D514"/>
-    </row>
-    <row r="515" spans="1:5">
+      <c r="E514"/>
+    </row>
+    <row r="515" spans="1:6">
       <c r="A515"/>
       <c r="B515"/>
       <c r="C515"/>
       <c r="D515"/>
-    </row>
-    <row r="516" spans="1:5">
+      <c r="E515"/>
+    </row>
+    <row r="516" spans="1:6">
       <c r="A516"/>
       <c r="B516"/>
       <c r="C516"/>
       <c r="D516"/>
-    </row>
-    <row r="517" spans="1:5">
+      <c r="E516"/>
+    </row>
+    <row r="517" spans="1:6">
       <c r="A517"/>
       <c r="B517"/>
       <c r="C517"/>
       <c r="D517"/>
-    </row>
-    <row r="518" spans="1:5">
+      <c r="E517"/>
+    </row>
+    <row r="518" spans="1:6">
       <c r="A518"/>
       <c r="B518"/>
       <c r="C518"/>
       <c r="D518"/>
-    </row>
-    <row r="519" spans="1:5">
+      <c r="E518"/>
+    </row>
+    <row r="519" spans="1:6">
       <c r="A519"/>
       <c r="B519"/>
       <c r="C519"/>
       <c r="D519"/>
-    </row>
-    <row r="520" spans="1:5">
+      <c r="E519"/>
+    </row>
+    <row r="520" spans="1:6">
       <c r="A520"/>
       <c r="B520"/>
       <c r="C520"/>
       <c r="D520"/>
-    </row>
-    <row r="521" spans="1:5">
+      <c r="E520"/>
+    </row>
+    <row r="521" spans="1:6">
       <c r="A521"/>
       <c r="B521"/>
       <c r="C521"/>
       <c r="D521"/>
-    </row>
-    <row r="522" spans="1:5">
+      <c r="E521"/>
+    </row>
+    <row r="522" spans="1:6">
       <c r="A522"/>
       <c r="B522"/>
       <c r="C522"/>
       <c r="D522"/>
-    </row>
-    <row r="523" spans="1:5">
+      <c r="E522"/>
+    </row>
+    <row r="523" spans="1:6">
       <c r="A523"/>
       <c r="B523"/>
       <c r="C523"/>
       <c r="D523"/>
-    </row>
-    <row r="524" spans="1:5">
+      <c r="E523"/>
+    </row>
+    <row r="524" spans="1:6">
       <c r="A524"/>
       <c r="B524"/>
       <c r="C524"/>
       <c r="D524"/>
-    </row>
-    <row r="525" spans="1:5">
+      <c r="E524"/>
+    </row>
+    <row r="525" spans="1:6">
       <c r="A525"/>
       <c r="B525"/>
       <c r="C525"/>
       <c r="D525"/>
-    </row>
-    <row r="526" spans="1:5">
+      <c r="E525"/>
+    </row>
+    <row r="526" spans="1:6">
       <c r="A526"/>
       <c r="B526"/>
       <c r="C526"/>
       <c r="D526"/>
-    </row>
-    <row r="527" spans="1:5">
+      <c r="E526"/>
+    </row>
+    <row r="527" spans="1:6">
       <c r="A527"/>
       <c r="B527"/>
       <c r="C527"/>
       <c r="D527"/>
-    </row>
-    <row r="528" spans="1:5">
+      <c r="E527"/>
+    </row>
+    <row r="528" spans="1:6">
       <c r="A528"/>
       <c r="B528"/>
       <c r="C528"/>
       <c r="D528"/>
-    </row>
-    <row r="529" spans="1:5">
+      <c r="E528"/>
+    </row>
+    <row r="529" spans="1:6">
       <c r="A529"/>
       <c r="B529"/>
       <c r="C529"/>
       <c r="D529"/>
-    </row>
-    <row r="530" spans="1:5">
+      <c r="E529"/>
+    </row>
+    <row r="530" spans="1:6">
       <c r="A530"/>
       <c r="B530"/>
       <c r="C530"/>
       <c r="D530"/>
-    </row>
-    <row r="531" spans="1:5">
+      <c r="E530"/>
+    </row>
+    <row r="531" spans="1:6">
       <c r="A531"/>
       <c r="B531"/>
       <c r="C531"/>
       <c r="D531"/>
-    </row>
-    <row r="532" spans="1:5">
+      <c r="E531"/>
+    </row>
+    <row r="532" spans="1:6">
       <c r="A532"/>
       <c r="B532"/>
       <c r="C532"/>
       <c r="D532"/>
-    </row>
-    <row r="533" spans="1:5">
+      <c r="E532"/>
+    </row>
+    <row r="533" spans="1:6">
       <c r="A533"/>
       <c r="B533"/>
       <c r="C533"/>
       <c r="D533"/>
-    </row>
-    <row r="534" spans="1:5">
+      <c r="E533"/>
+    </row>
+    <row r="534" spans="1:6">
       <c r="A534"/>
       <c r="B534"/>
       <c r="C534"/>
       <c r="D534"/>
-    </row>
-    <row r="535" spans="1:5">
+      <c r="E534"/>
+    </row>
+    <row r="535" spans="1:6">
       <c r="A535"/>
       <c r="B535"/>
       <c r="C535"/>
       <c r="D535"/>
-    </row>
-    <row r="536" spans="1:5">
+      <c r="E535"/>
+    </row>
+    <row r="536" spans="1:6">
       <c r="A536"/>
       <c r="B536"/>
       <c r="C536"/>
       <c r="D536"/>
-    </row>
-    <row r="537" spans="1:5">
+      <c r="E536"/>
+    </row>
+    <row r="537" spans="1:6">
       <c r="A537"/>
       <c r="B537"/>
       <c r="C537"/>
       <c r="D537"/>
-    </row>
-    <row r="538" spans="1:5">
+      <c r="E537"/>
+    </row>
+    <row r="538" spans="1:6">
       <c r="A538"/>
       <c r="B538"/>
       <c r="C538"/>
       <c r="D538"/>
-    </row>
-    <row r="539" spans="1:5">
+      <c r="E538"/>
+    </row>
+    <row r="539" spans="1:6">
       <c r="A539"/>
       <c r="B539"/>
       <c r="C539"/>
       <c r="D539"/>
-    </row>
-    <row r="540" spans="1:5">
+      <c r="E539"/>
+    </row>
+    <row r="540" spans="1:6">
       <c r="A540"/>
       <c r="B540"/>
       <c r="C540"/>
       <c r="D540"/>
-    </row>
-    <row r="541" spans="1:5">
+      <c r="E540"/>
+    </row>
+    <row r="541" spans="1:6">
       <c r="A541"/>
       <c r="B541"/>
       <c r="C541"/>
       <c r="D541"/>
-    </row>
-    <row r="542" spans="1:5">
+      <c r="E541"/>
+    </row>
+    <row r="542" spans="1:6">
       <c r="A542"/>
       <c r="B542"/>
       <c r="C542"/>
       <c r="D542"/>
-    </row>
-    <row r="543" spans="1:5">
+      <c r="E542"/>
+    </row>
+    <row r="543" spans="1:6">
       <c r="A543"/>
       <c r="B543"/>
       <c r="C543"/>
       <c r="D543"/>
-    </row>
-    <row r="544" spans="1:5">
+      <c r="E543"/>
+    </row>
+    <row r="544" spans="1:6">
       <c r="A544"/>
       <c r="B544"/>
       <c r="C544"/>
       <c r="D544"/>
-    </row>
-    <row r="545" spans="1:5">
+      <c r="E544"/>
+    </row>
+    <row r="545" spans="1:6">
       <c r="A545"/>
       <c r="B545"/>
       <c r="C545"/>
       <c r="D545"/>
-    </row>
-    <row r="546" spans="1:5">
+      <c r="E545"/>
+    </row>
+    <row r="546" spans="1:6">
       <c r="A546"/>
       <c r="B546"/>
       <c r="C546"/>
       <c r="D546"/>
-    </row>
-    <row r="547" spans="1:5">
+      <c r="E546"/>
+    </row>
+    <row r="547" spans="1:6">
       <c r="A547"/>
       <c r="B547"/>
       <c r="C547"/>
       <c r="D547"/>
-    </row>
-    <row r="548" spans="1:5">
+      <c r="E547"/>
+    </row>
+    <row r="548" spans="1:6">
       <c r="A548"/>
       <c r="B548"/>
       <c r="C548"/>
       <c r="D548"/>
-    </row>
-    <row r="549" spans="1:5">
+      <c r="E548"/>
+    </row>
+    <row r="549" spans="1:6">
       <c r="A549"/>
       <c r="B549"/>
       <c r="C549"/>
       <c r="D549"/>
-    </row>
-    <row r="550" spans="1:5">
+      <c r="E549"/>
+    </row>
+    <row r="550" spans="1:6">
       <c r="A550"/>
       <c r="B550"/>
       <c r="C550"/>
       <c r="D550"/>
-    </row>
-    <row r="551" spans="1:5">
+      <c r="E550"/>
+    </row>
+    <row r="551" spans="1:6">
       <c r="A551"/>
       <c r="B551"/>
       <c r="C551"/>
       <c r="D551"/>
-    </row>
-    <row r="552" spans="1:5">
+      <c r="E551"/>
+    </row>
+    <row r="552" spans="1:6">
       <c r="A552"/>
       <c r="B552"/>
       <c r="C552"/>
       <c r="D552"/>
-    </row>
-    <row r="553" spans="1:5">
+      <c r="E552"/>
+    </row>
+    <row r="553" spans="1:6">
       <c r="A553"/>
       <c r="B553"/>
       <c r="C553"/>
       <c r="D553"/>
-    </row>
-    <row r="554" spans="1:5">
+      <c r="E553"/>
+    </row>
+    <row r="554" spans="1:6">
       <c r="A554"/>
       <c r="B554"/>
       <c r="C554"/>
       <c r="D554"/>
-    </row>
-    <row r="555" spans="1:5">
+      <c r="E554"/>
+    </row>
+    <row r="555" spans="1:6">
       <c r="A555"/>
       <c r="B555"/>
       <c r="C555"/>
       <c r="D555"/>
-    </row>
-    <row r="556" spans="1:5">
+      <c r="E555"/>
+    </row>
+    <row r="556" spans="1:6">
       <c r="A556"/>
       <c r="B556"/>
       <c r="C556"/>
       <c r="D556"/>
-    </row>
-    <row r="557" spans="1:5">
+      <c r="E556"/>
+    </row>
+    <row r="557" spans="1:6">
       <c r="A557"/>
       <c r="B557"/>
       <c r="C557"/>
       <c r="D557"/>
-    </row>
-    <row r="558" spans="1:5">
+      <c r="E557"/>
+    </row>
+    <row r="558" spans="1:6">
       <c r="A558"/>
       <c r="B558"/>
       <c r="C558"/>
       <c r="D558"/>
-    </row>
-    <row r="559" spans="1:5">
+      <c r="E558"/>
+    </row>
+    <row r="559" spans="1:6">
       <c r="A559"/>
       <c r="B559"/>
       <c r="C559"/>
       <c r="D559"/>
-    </row>
-    <row r="560" spans="1:5">
+      <c r="E559"/>
+    </row>
+    <row r="560" spans="1:6">
       <c r="A560"/>
       <c r="B560"/>
       <c r="C560"/>
       <c r="D560"/>
-    </row>
-    <row r="561" spans="1:5">
+      <c r="E560"/>
+    </row>
+    <row r="561" spans="1:6">
       <c r="A561"/>
       <c r="B561"/>
       <c r="C561"/>
       <c r="D561"/>
-    </row>
-    <row r="562" spans="1:5">
+      <c r="E561"/>
+    </row>
+    <row r="562" spans="1:6">
       <c r="A562"/>
       <c r="B562"/>
       <c r="C562"/>
       <c r="D562"/>
-    </row>
-    <row r="563" spans="1:5">
+      <c r="E562"/>
+    </row>
+    <row r="563" spans="1:6">
       <c r="A563"/>
       <c r="B563"/>
       <c r="C563"/>
       <c r="D563"/>
-    </row>
-    <row r="564" spans="1:5">
+      <c r="E563"/>
+    </row>
+    <row r="564" spans="1:6">
       <c r="A564"/>
       <c r="B564"/>
       <c r="C564"/>
       <c r="D564"/>
-    </row>
-    <row r="565" spans="1:5">
+      <c r="E564"/>
+    </row>
+    <row r="565" spans="1:6">
       <c r="A565"/>
       <c r="B565"/>
       <c r="C565"/>
       <c r="D565"/>
-    </row>
-    <row r="566" spans="1:5">
+      <c r="E565"/>
+    </row>
+    <row r="566" spans="1:6">
       <c r="A566"/>
       <c r="B566"/>
       <c r="C566"/>
       <c r="D566"/>
-    </row>
-    <row r="567" spans="1:5">
+      <c r="E566"/>
+    </row>
+    <row r="567" spans="1:6">
       <c r="A567"/>
       <c r="B567"/>
       <c r="C567"/>
       <c r="D567"/>
-    </row>
-    <row r="568" spans="1:5">
+      <c r="E567"/>
+    </row>
+    <row r="568" spans="1:6">
       <c r="A568"/>
       <c r="B568"/>
       <c r="C568"/>
       <c r="D568"/>
-    </row>
-    <row r="569" spans="1:5">
+      <c r="E568"/>
+    </row>
+    <row r="569" spans="1:6">
       <c r="A569"/>
       <c r="B569"/>
       <c r="C569"/>
       <c r="D569"/>
-    </row>
-    <row r="570" spans="1:5">
+      <c r="E569"/>
+    </row>
+    <row r="570" spans="1:6">
       <c r="A570"/>
       <c r="B570"/>
       <c r="C570"/>
       <c r="D570"/>
-    </row>
-    <row r="571" spans="1:5">
+      <c r="E570"/>
+    </row>
+    <row r="571" spans="1:6">
       <c r="A571"/>
       <c r="B571"/>
       <c r="C571"/>
       <c r="D571"/>
-    </row>
-    <row r="572" spans="1:5">
+      <c r="E571"/>
+    </row>
+    <row r="572" spans="1:6">
       <c r="A572"/>
       <c r="B572"/>
       <c r="C572"/>
       <c r="D572"/>
-    </row>
-    <row r="573" spans="1:5">
+      <c r="E572"/>
+    </row>
+    <row r="573" spans="1:6">
       <c r="A573"/>
       <c r="B573"/>
       <c r="C573"/>
       <c r="D573"/>
-    </row>
-    <row r="574" spans="1:5">
+      <c r="E573"/>
+    </row>
+    <row r="574" spans="1:6">
       <c r="A574"/>
       <c r="B574"/>
       <c r="C574"/>
       <c r="D574"/>
-    </row>
-    <row r="575" spans="1:5">
+      <c r="E574"/>
+    </row>
+    <row r="575" spans="1:6">
       <c r="A575"/>
       <c r="B575"/>
       <c r="C575"/>
       <c r="D575"/>
-    </row>
-    <row r="576" spans="1:5">
+      <c r="E575"/>
+    </row>
+    <row r="576" spans="1:6">
       <c r="A576"/>
       <c r="B576"/>
       <c r="C576"/>
       <c r="D576"/>
-    </row>
-    <row r="577" spans="1:5">
+      <c r="E576"/>
+    </row>
+    <row r="577" spans="1:6">
       <c r="A577"/>
       <c r="B577"/>
       <c r="C577"/>
       <c r="D577"/>
-    </row>
-    <row r="578" spans="1:5">
+      <c r="E577"/>
+    </row>
+    <row r="578" spans="1:6">
       <c r="A578"/>
       <c r="B578"/>
       <c r="C578"/>
       <c r="D578"/>
-    </row>
-    <row r="579" spans="1:5">
+      <c r="E578"/>
+    </row>
+    <row r="579" spans="1:6">
       <c r="A579"/>
       <c r="B579"/>
       <c r="C579"/>
       <c r="D579"/>
-    </row>
-    <row r="580" spans="1:5">
+      <c r="E579"/>
+    </row>
+    <row r="580" spans="1:6">
       <c r="A580"/>
       <c r="B580"/>
       <c r="C580"/>
       <c r="D580"/>
-    </row>
-    <row r="581" spans="1:5">
+      <c r="E580"/>
+    </row>
+    <row r="581" spans="1:6">
       <c r="A581"/>
       <c r="B581"/>
       <c r="C581"/>
       <c r="D581"/>
-    </row>
-    <row r="582" spans="1:5">
+      <c r="E581"/>
+    </row>
+    <row r="582" spans="1:6">
       <c r="A582"/>
       <c r="B582"/>
       <c r="C582"/>
       <c r="D582"/>
-    </row>
-    <row r="583" spans="1:5">
+      <c r="E582"/>
+    </row>
+    <row r="583" spans="1:6">
       <c r="A583"/>
       <c r="B583"/>
       <c r="C583"/>
       <c r="D583"/>
-    </row>
-    <row r="584" spans="1:5">
+      <c r="E583"/>
+    </row>
+    <row r="584" spans="1:6">
       <c r="A584"/>
       <c r="B584"/>
       <c r="C584"/>
       <c r="D584"/>
-    </row>
-    <row r="585" spans="1:5">
+      <c r="E584"/>
+    </row>
+    <row r="585" spans="1:6">
       <c r="A585"/>
       <c r="B585"/>
       <c r="C585"/>
       <c r="D585"/>
-    </row>
-    <row r="586" spans="1:5">
+      <c r="E585"/>
+    </row>
+    <row r="586" spans="1:6">
       <c r="A586"/>
       <c r="B586"/>
       <c r="C586"/>
       <c r="D586"/>
-    </row>
-    <row r="587" spans="1:5">
+      <c r="E586"/>
+    </row>
+    <row r="587" spans="1:6">
       <c r="A587"/>
       <c r="B587"/>
       <c r="C587"/>
       <c r="D587"/>
-    </row>
-    <row r="588" spans="1:5">
+      <c r="E587"/>
+    </row>
+    <row r="588" spans="1:6">
       <c r="A588"/>
       <c r="B588"/>
       <c r="C588"/>
       <c r="D588"/>
-    </row>
-    <row r="589" spans="1:5">
+      <c r="E588"/>
+    </row>
+    <row r="589" spans="1:6">
       <c r="A589"/>
       <c r="B589"/>
       <c r="C589"/>
       <c r="D589"/>
-    </row>
-    <row r="590" spans="1:5">
+      <c r="E589"/>
+    </row>
+    <row r="590" spans="1:6">
       <c r="A590"/>
       <c r="B590"/>
       <c r="C590"/>
       <c r="D590"/>
-    </row>
-    <row r="591" spans="1:5">
+      <c r="E590"/>
+    </row>
+    <row r="591" spans="1:6">
       <c r="A591"/>
       <c r="B591"/>
       <c r="C591"/>
       <c r="D591"/>
-    </row>
-    <row r="592" spans="1:5">
+      <c r="E591"/>
+    </row>
+    <row r="592" spans="1:6">
       <c r="A592"/>
       <c r="B592"/>
       <c r="C592"/>
       <c r="D592"/>
-    </row>
-    <row r="593" spans="1:5">
+      <c r="E592"/>
+    </row>
+    <row r="593" spans="1:6">
       <c r="A593"/>
       <c r="B593"/>
       <c r="C593"/>
       <c r="D593"/>
-    </row>
-    <row r="594" spans="1:5">
+      <c r="E593"/>
+    </row>
+    <row r="594" spans="1:6">
       <c r="A594"/>
       <c r="B594"/>
       <c r="C594"/>
       <c r="D594"/>
-    </row>
-    <row r="595" spans="1:5">
+      <c r="E594"/>
+    </row>
+    <row r="595" spans="1:6">
       <c r="A595"/>
       <c r="B595"/>
       <c r="C595"/>
       <c r="D595"/>
-    </row>
-    <row r="596" spans="1:5">
+      <c r="E595"/>
+    </row>
+    <row r="596" spans="1:6">
       <c r="A596"/>
       <c r="B596"/>
       <c r="C596"/>
       <c r="D596"/>
-    </row>
-    <row r="597" spans="1:5">
+      <c r="E596"/>
+    </row>
+    <row r="597" spans="1:6">
       <c r="A597"/>
       <c r="B597"/>
       <c r="C597"/>
       <c r="D597"/>
-    </row>
-    <row r="598" spans="1:5">
+      <c r="E597"/>
+    </row>
+    <row r="598" spans="1:6">
       <c r="A598"/>
       <c r="B598"/>
       <c r="C598"/>
       <c r="D598"/>
-    </row>
-    <row r="599" spans="1:5">
+      <c r="E598"/>
+    </row>
+    <row r="599" spans="1:6">
       <c r="A599"/>
       <c r="B599"/>
       <c r="C599"/>
       <c r="D599"/>
-    </row>
-    <row r="600" spans="1:5">
+      <c r="E599"/>
+    </row>
+    <row r="600" spans="1:6">
       <c r="A600"/>
       <c r="B600"/>
       <c r="C600"/>
       <c r="D600"/>
-    </row>
-    <row r="601" spans="1:5">
+      <c r="E600"/>
+    </row>
+    <row r="601" spans="1:6">
       <c r="A601"/>
       <c r="B601"/>
       <c r="C601"/>
       <c r="D601"/>
-    </row>
-    <row r="602" spans="1:5">
+      <c r="E601"/>
+    </row>
+    <row r="602" spans="1:6">
       <c r="A602"/>
       <c r="B602"/>
       <c r="C602"/>
       <c r="D602"/>
-    </row>
-    <row r="603" spans="1:5">
+      <c r="E602"/>
+    </row>
+    <row r="603" spans="1:6">
       <c r="A603"/>
       <c r="B603"/>
       <c r="C603"/>
       <c r="D603"/>
-    </row>
-    <row r="604" spans="1:5">
+      <c r="E603"/>
+    </row>
+    <row r="604" spans="1:6">
       <c r="A604"/>
       <c r="B604"/>
       <c r="C604"/>
       <c r="D604"/>
-    </row>
-    <row r="605" spans="1:5">
+      <c r="E604"/>
+    </row>
+    <row r="605" spans="1:6">
       <c r="A605"/>
       <c r="B605"/>
       <c r="C605"/>
       <c r="D605"/>
-    </row>
-    <row r="606" spans="1:5">
+      <c r="E605"/>
+    </row>
+    <row r="606" spans="1:6">
       <c r="A606"/>
       <c r="B606"/>
       <c r="C606"/>
       <c r="D606"/>
-    </row>
-    <row r="607" spans="1:5">
+      <c r="E606"/>
+    </row>
+    <row r="607" spans="1:6">
       <c r="A607"/>
       <c r="B607"/>
       <c r="C607"/>
       <c r="D607"/>
-    </row>
-    <row r="608" spans="1:5">
+      <c r="E607"/>
+    </row>
+    <row r="608" spans="1:6">
       <c r="A608"/>
       <c r="B608"/>
       <c r="C608"/>
       <c r="D608"/>
-    </row>
-    <row r="609" spans="1:5">
+      <c r="E608"/>
+    </row>
+    <row r="609" spans="1:6">
       <c r="A609"/>
       <c r="B609"/>
       <c r="C609"/>
       <c r="D609"/>
-    </row>
-    <row r="610" spans="1:5">
+      <c r="E609"/>
+    </row>
+    <row r="610" spans="1:6">
       <c r="A610"/>
       <c r="B610"/>
       <c r="C610"/>
       <c r="D610"/>
-    </row>
-    <row r="611" spans="1:5">
+      <c r="E610"/>
+    </row>
+    <row r="611" spans="1:6">
       <c r="A611"/>
       <c r="B611"/>
       <c r="C611"/>
       <c r="D611"/>
-    </row>
-    <row r="612" spans="1:5">
+      <c r="E611"/>
+    </row>
+    <row r="612" spans="1:6">
       <c r="A612"/>
       <c r="B612"/>
       <c r="C612"/>
       <c r="D612"/>
-    </row>
-    <row r="613" spans="1:5">
+      <c r="E612"/>
+    </row>
+    <row r="613" spans="1:6">
       <c r="A613"/>
       <c r="B613"/>
       <c r="C613"/>
       <c r="D613"/>
-    </row>
-    <row r="614" spans="1:5">
+      <c r="E613"/>
+    </row>
+    <row r="614" spans="1:6">
       <c r="A614"/>
       <c r="B614"/>
       <c r="C614"/>
       <c r="D614"/>
-    </row>
-    <row r="615" spans="1:5">
+      <c r="E614"/>
+    </row>
+    <row r="615" spans="1:6">
       <c r="A615"/>
       <c r="B615"/>
       <c r="C615"/>
       <c r="D615"/>
-    </row>
-    <row r="616" spans="1:5">
+      <c r="E615"/>
+    </row>
+    <row r="616" spans="1:6">
       <c r="A616"/>
       <c r="B616"/>
       <c r="C616"/>
       <c r="D616"/>
-    </row>
-    <row r="617" spans="1:5">
+      <c r="E616"/>
+    </row>
+    <row r="617" spans="1:6">
       <c r="A617"/>
       <c r="B617"/>
       <c r="C617"/>
       <c r="D617"/>
-    </row>
-    <row r="618" spans="1:5">
+      <c r="E617"/>
+    </row>
+    <row r="618" spans="1:6">
       <c r="A618"/>
       <c r="B618"/>
       <c r="C618"/>
       <c r="D618"/>
-    </row>
-    <row r="619" spans="1:5">
+      <c r="E618"/>
+    </row>
+    <row r="619" spans="1:6">
       <c r="A619"/>
       <c r="B619"/>
       <c r="C619"/>
       <c r="D619"/>
-    </row>
-    <row r="620" spans="1:5">
+      <c r="E619"/>
+    </row>
+    <row r="620" spans="1:6">
       <c r="A620"/>
       <c r="B620"/>
       <c r="C620"/>
       <c r="D620"/>
-    </row>
-    <row r="621" spans="1:5">
+      <c r="E620"/>
+    </row>
+    <row r="621" spans="1:6">
       <c r="A621"/>
       <c r="B621"/>
       <c r="C621"/>
       <c r="D621"/>
-    </row>
-    <row r="622" spans="1:5">
+      <c r="E621"/>
+    </row>
+    <row r="622" spans="1:6">
       <c r="A622"/>
       <c r="B622"/>
       <c r="C622"/>
       <c r="D622"/>
-    </row>
-    <row r="623" spans="1:5">
+      <c r="E622"/>
+    </row>
+    <row r="623" spans="1:6">
       <c r="A623"/>
       <c r="B623"/>
       <c r="C623"/>
       <c r="D623"/>
-    </row>
-    <row r="624" spans="1:5">
+      <c r="E623"/>
+    </row>
+    <row r="624" spans="1:6">
       <c r="A624"/>
       <c r="B624"/>
       <c r="C624"/>
       <c r="D624"/>
-    </row>
-    <row r="625" spans="1:5">
+      <c r="E624"/>
+    </row>
+    <row r="625" spans="1:6">
       <c r="A625"/>
       <c r="B625"/>
       <c r="C625"/>
       <c r="D625"/>
-    </row>
-    <row r="626" spans="1:5">
+      <c r="E625"/>
+    </row>
+    <row r="626" spans="1:6">
       <c r="A626"/>
       <c r="B626"/>
       <c r="C626"/>
       <c r="D626"/>
-    </row>
-    <row r="627" spans="1:5">
+      <c r="E626"/>
+    </row>
+    <row r="627" spans="1:6">
       <c r="A627"/>
       <c r="B627"/>
       <c r="C627"/>
       <c r="D627"/>
-    </row>
-    <row r="628" spans="1:5">
+      <c r="E627"/>
+    </row>
+    <row r="628" spans="1:6">
       <c r="A628"/>
       <c r="B628"/>
       <c r="C628"/>
       <c r="D628"/>
-    </row>
-    <row r="629" spans="1:5">
+      <c r="E628"/>
+    </row>
+    <row r="629" spans="1:6">
       <c r="A629"/>
       <c r="B629"/>
       <c r="C629"/>
       <c r="D629"/>
-    </row>
-    <row r="630" spans="1:5">
+      <c r="E629"/>
+    </row>
+    <row r="630" spans="1:6">
       <c r="A630"/>
       <c r="B630"/>
       <c r="C630"/>
       <c r="D630"/>
-    </row>
-    <row r="631" spans="1:5">
+      <c r="E630"/>
+    </row>
+    <row r="631" spans="1:6">
       <c r="A631"/>
       <c r="B631"/>
       <c r="C631"/>
       <c r="D631"/>
-    </row>
-    <row r="632" spans="1:5">
+      <c r="E631"/>
+    </row>
+    <row r="632" spans="1:6">
       <c r="A632"/>
       <c r="B632"/>
       <c r="C632"/>
       <c r="D632"/>
-    </row>
-    <row r="633" spans="1:5">
+      <c r="E632"/>
+    </row>
+    <row r="633" spans="1:6">
       <c r="A633"/>
       <c r="B633"/>
       <c r="C633"/>
       <c r="D633"/>
-    </row>
-    <row r="634" spans="1:5">
+      <c r="E633"/>
+    </row>
+    <row r="634" spans="1:6">
       <c r="A634"/>
       <c r="B634"/>
       <c r="C634"/>
       <c r="D634"/>
-    </row>
-    <row r="635" spans="1:5">
+      <c r="E634"/>
+    </row>
+    <row r="635" spans="1:6">
       <c r="A635"/>
       <c r="B635"/>
       <c r="C635"/>
       <c r="D635"/>
-    </row>
-    <row r="636" spans="1:5">
+      <c r="E635"/>
+    </row>
+    <row r="636" spans="1:6">
       <c r="A636"/>
       <c r="B636"/>
       <c r="C636"/>
       <c r="D636"/>
-    </row>
-    <row r="637" spans="1:5">
+      <c r="E636"/>
+    </row>
+    <row r="637" spans="1:6">
       <c r="A637"/>
       <c r="B637"/>
       <c r="C637"/>
       <c r="D637"/>
-    </row>
-    <row r="638" spans="1:5">
+      <c r="E637"/>
+    </row>
+    <row r="638" spans="1:6">
       <c r="A638"/>
       <c r="B638"/>
       <c r="C638"/>
       <c r="D638"/>
-    </row>
-    <row r="639" spans="1:5">
+      <c r="E638"/>
+    </row>
+    <row r="639" spans="1:6">
       <c r="A639"/>
       <c r="B639"/>
       <c r="C639"/>
       <c r="D639"/>
-    </row>
-    <row r="640" spans="1:5">
+      <c r="E639"/>
+    </row>
+    <row r="640" spans="1:6">
       <c r="A640"/>
       <c r="B640"/>
       <c r="C640"/>
       <c r="D640"/>
-    </row>
-    <row r="641" spans="1:5">
+      <c r="E640"/>
+    </row>
+    <row r="641" spans="1:6">
       <c r="A641"/>
       <c r="B641"/>
       <c r="C641"/>
       <c r="D641"/>
-    </row>
-    <row r="642" spans="1:5">
+      <c r="E641"/>
+    </row>
+    <row r="642" spans="1:6">
       <c r="A642"/>
       <c r="B642"/>
       <c r="C642"/>
       <c r="D642"/>
-    </row>
-    <row r="643" spans="1:5">
+      <c r="E642"/>
+    </row>
+    <row r="643" spans="1:6">
       <c r="A643"/>
       <c r="B643"/>
       <c r="C643"/>
       <c r="D643"/>
-    </row>
-    <row r="644" spans="1:5">
+      <c r="E643"/>
+    </row>
+    <row r="644" spans="1:6">
       <c r="A644"/>
       <c r="B644"/>
       <c r="C644"/>
       <c r="D644"/>
-    </row>
-    <row r="645" spans="1:5">
+      <c r="E644"/>
+    </row>
+    <row r="645" spans="1:6">
       <c r="A645"/>
       <c r="B645"/>
       <c r="C645"/>
       <c r="D645"/>
-    </row>
-    <row r="646" spans="1:5">
+      <c r="E645"/>
+    </row>
+    <row r="646" spans="1:6">
       <c r="A646"/>
       <c r="B646"/>
       <c r="C646"/>
       <c r="D646"/>
-    </row>
-    <row r="647" spans="1:5">
+      <c r="E646"/>
+    </row>
+    <row r="647" spans="1:6">
       <c r="A647"/>
       <c r="B647"/>
       <c r="C647"/>
       <c r="D647"/>
-    </row>
-    <row r="648" spans="1:5">
+      <c r="E647"/>
+    </row>
+    <row r="648" spans="1:6">
       <c r="A648"/>
       <c r="B648"/>
       <c r="C648"/>
       <c r="D648"/>
-    </row>
-    <row r="649" spans="1:5">
+      <c r="E648"/>
+    </row>
+    <row r="649" spans="1:6">
       <c r="A649"/>
       <c r="B649"/>
       <c r="C649"/>
       <c r="D649"/>
-    </row>
-    <row r="650" spans="1:5">
+      <c r="E649"/>
+    </row>
+    <row r="650" spans="1:6">
       <c r="A650"/>
       <c r="B650"/>
       <c r="C650"/>
       <c r="D650"/>
-    </row>
-    <row r="651" spans="1:5">
+      <c r="E650"/>
+    </row>
+    <row r="651" spans="1:6">
       <c r="A651"/>
       <c r="B651"/>
       <c r="C651"/>
       <c r="D651"/>
-    </row>
-    <row r="652" spans="1:5">
+      <c r="E651"/>
+    </row>
+    <row r="652" spans="1:6">
       <c r="A652"/>
       <c r="B652"/>
       <c r="C652"/>
       <c r="D652"/>
-    </row>
-    <row r="653" spans="1:5">
+      <c r="E652"/>
+    </row>
+    <row r="653" spans="1:6">
       <c r="A653"/>
       <c r="B653"/>
       <c r="C653"/>
       <c r="D653"/>
-    </row>
-    <row r="654" spans="1:5">
+      <c r="E653"/>
+    </row>
+    <row r="654" spans="1:6">
       <c r="A654"/>
       <c r="B654"/>
       <c r="C654"/>
       <c r="D654"/>
-    </row>
-    <row r="655" spans="1:5">
+      <c r="E654"/>
+    </row>
+    <row r="655" spans="1:6">
       <c r="A655"/>
       <c r="B655"/>
       <c r="C655"/>
       <c r="D655"/>
-    </row>
-    <row r="656" spans="1:5">
+      <c r="E655"/>
+    </row>
+    <row r="656" spans="1:6">
       <c r="A656"/>
       <c r="B656"/>
       <c r="C656"/>
       <c r="D656"/>
-    </row>
-    <row r="657" spans="1:5">
+      <c r="E656"/>
+    </row>
+    <row r="657" spans="1:6">
       <c r="A657"/>
       <c r="B657"/>
       <c r="C657"/>
       <c r="D657"/>
-    </row>
-    <row r="658" spans="1:5">
+      <c r="E657"/>
+    </row>
+    <row r="658" spans="1:6">
       <c r="A658"/>
       <c r="B658"/>
       <c r="C658"/>
       <c r="D658"/>
-    </row>
-    <row r="659" spans="1:5">
+      <c r="E658"/>
+    </row>
+    <row r="659" spans="1:6">
       <c r="A659"/>
       <c r="B659"/>
       <c r="C659"/>
       <c r="D659"/>
-    </row>
-    <row r="660" spans="1:5">
+      <c r="E659"/>
+    </row>
+    <row r="660" spans="1:6">
       <c r="A660"/>
       <c r="B660"/>
       <c r="C660"/>
       <c r="D660"/>
-    </row>
-    <row r="661" spans="1:5">
+      <c r="E660"/>
+    </row>
+    <row r="661" spans="1:6">
       <c r="A661"/>
       <c r="B661"/>
       <c r="C661"/>
       <c r="D661"/>
-    </row>
-    <row r="662" spans="1:5">
+      <c r="E661"/>
+    </row>
+    <row r="662" spans="1:6">
       <c r="A662"/>
       <c r="B662"/>
       <c r="C662"/>
       <c r="D662"/>
-    </row>
-    <row r="663" spans="1:5">
+      <c r="E662"/>
+    </row>
+    <row r="663" spans="1:6">
       <c r="A663"/>
       <c r="B663"/>
       <c r="C663"/>
       <c r="D663"/>
-    </row>
-    <row r="664" spans="1:5">
+      <c r="E663"/>
+    </row>
+    <row r="664" spans="1:6">
       <c r="A664"/>
       <c r="B664"/>
       <c r="C664"/>
       <c r="D664"/>
-    </row>
-    <row r="665" spans="1:5">
+      <c r="E664"/>
+    </row>
+    <row r="665" spans="1:6">
       <c r="A665"/>
       <c r="B665"/>
       <c r="C665"/>
       <c r="D665"/>
-    </row>
-    <row r="666" spans="1:5">
+      <c r="E665"/>
+    </row>
+    <row r="666" spans="1:6">
       <c r="A666"/>
       <c r="B666"/>
       <c r="C666"/>
       <c r="D666"/>
-    </row>
-    <row r="667" spans="1:5">
+      <c r="E666"/>
+    </row>
+    <row r="667" spans="1:6">
       <c r="A667"/>
       <c r="B667"/>
       <c r="C667"/>
       <c r="D667"/>
-    </row>
-    <row r="668" spans="1:5">
+      <c r="E667"/>
+    </row>
+    <row r="668" spans="1:6">
       <c r="A668"/>
       <c r="B668"/>
       <c r="C668"/>
       <c r="D668"/>
-    </row>
-    <row r="669" spans="1:5">
+      <c r="E668"/>
+    </row>
+    <row r="669" spans="1:6">
       <c r="A669"/>
       <c r="B669"/>
       <c r="C669"/>
       <c r="D669"/>
-    </row>
-    <row r="670" spans="1:5">
+      <c r="E669"/>
+    </row>
+    <row r="670" spans="1:6">
       <c r="A670"/>
       <c r="B670"/>
       <c r="C670"/>
       <c r="D670"/>
-    </row>
-    <row r="671" spans="1:5">
+      <c r="E670"/>
+    </row>
+    <row r="671" spans="1:6">
       <c r="A671"/>
       <c r="B671"/>
       <c r="C671"/>
       <c r="D671"/>
-    </row>
-    <row r="672" spans="1:5">
+      <c r="E671"/>
+    </row>
+    <row r="672" spans="1:6">
       <c r="A672"/>
       <c r="B672"/>
       <c r="C672"/>
       <c r="D672"/>
-    </row>
-    <row r="673" spans="1:5">
+      <c r="E672"/>
+    </row>
+    <row r="673" spans="1:6">
       <c r="A673"/>
       <c r="B673"/>
       <c r="C673"/>
       <c r="D673"/>
-    </row>
-    <row r="674" spans="1:5">
+      <c r="E673"/>
+    </row>
+    <row r="674" spans="1:6">
       <c r="A674"/>
       <c r="B674"/>
       <c r="C674"/>
       <c r="D674"/>
-    </row>
-    <row r="675" spans="1:5">
+      <c r="E674"/>
+    </row>
+    <row r="675" spans="1:6">
       <c r="A675"/>
       <c r="B675"/>
       <c r="C675"/>
       <c r="D675"/>
-    </row>
-    <row r="676" spans="1:5">
+      <c r="E675"/>
+    </row>
+    <row r="676" spans="1:6">
       <c r="A676"/>
       <c r="B676"/>
       <c r="C676"/>
       <c r="D676"/>
-    </row>
-    <row r="677" spans="1:5">
+      <c r="E676"/>
+    </row>
+    <row r="677" spans="1:6">
       <c r="A677"/>
       <c r="B677"/>
       <c r="C677"/>
       <c r="D677"/>
-    </row>
-    <row r="678" spans="1:5">
+      <c r="E677"/>
+    </row>
+    <row r="678" spans="1:6">
       <c r="A678"/>
       <c r="B678"/>
       <c r="C678"/>
       <c r="D678"/>
-    </row>
-    <row r="679" spans="1:5">
+      <c r="E678"/>
+    </row>
+    <row r="679" spans="1:6">
       <c r="A679"/>
       <c r="B679"/>
       <c r="C679"/>
       <c r="D679"/>
-    </row>
-    <row r="680" spans="1:5">
+      <c r="E679"/>
+    </row>
+    <row r="680" spans="1:6">
       <c r="A680"/>
       <c r="B680"/>
       <c r="C680"/>
       <c r="D680"/>
-    </row>
-    <row r="681" spans="1:5">
+      <c r="E680"/>
+    </row>
+    <row r="681" spans="1:6">
       <c r="A681"/>
       <c r="B681"/>
       <c r="C681"/>
       <c r="D681"/>
-    </row>
-    <row r="682" spans="1:5">
+      <c r="E681"/>
+    </row>
+    <row r="682" spans="1:6">
       <c r="A682"/>
       <c r="B682"/>
       <c r="C682"/>
       <c r="D682"/>
-    </row>
-    <row r="683" spans="1:5">
+      <c r="E682"/>
+    </row>
+    <row r="683" spans="1:6">
       <c r="A683"/>
       <c r="B683"/>
       <c r="C683"/>
       <c r="D683"/>
-    </row>
-    <row r="684" spans="1:5">
+      <c r="E683"/>
+    </row>
+    <row r="684" spans="1:6">
       <c r="A684"/>
       <c r="B684"/>
       <c r="C684"/>
       <c r="D684"/>
-    </row>
-    <row r="685" spans="1:5">
+      <c r="E684"/>
+    </row>
+    <row r="685" spans="1:6">
       <c r="A685"/>
       <c r="B685"/>
       <c r="C685"/>
       <c r="D685"/>
-    </row>
-    <row r="686" spans="1:5">
+      <c r="E685"/>
+    </row>
+    <row r="686" spans="1:6">
       <c r="A686"/>
       <c r="B686"/>
       <c r="C686"/>
       <c r="D686"/>
-    </row>
-    <row r="687" spans="1:5">
+      <c r="E686"/>
+    </row>
+    <row r="687" spans="1:6">
       <c r="A687"/>
       <c r="B687"/>
       <c r="C687"/>
       <c r="D687"/>
-    </row>
-    <row r="688" spans="1:5">
+      <c r="E687"/>
+    </row>
+    <row r="688" spans="1:6">
       <c r="A688"/>
       <c r="B688"/>
       <c r="C688"/>
       <c r="D688"/>
-    </row>
-    <row r="689" spans="1:5">
+      <c r="E688"/>
+    </row>
+    <row r="689" spans="1:6">
       <c r="A689"/>
       <c r="B689"/>
       <c r="C689"/>
       <c r="D689"/>
-    </row>
-    <row r="690" spans="1:5">
+      <c r="E689"/>
+    </row>
+    <row r="690" spans="1:6">
       <c r="A690"/>
       <c r="B690"/>
       <c r="C690"/>
       <c r="D690"/>
-    </row>
-    <row r="691" spans="1:5">
+      <c r="E690"/>
+    </row>
+    <row r="691" spans="1:6">
       <c r="A691"/>
       <c r="B691"/>
       <c r="C691"/>
       <c r="D691"/>
-    </row>
-    <row r="692" spans="1:5">
+      <c r="E691"/>
+    </row>
+    <row r="692" spans="1:6">
       <c r="A692"/>
       <c r="B692"/>
       <c r="C692"/>
       <c r="D692"/>
-    </row>
-    <row r="693" spans="1:5">
+      <c r="E692"/>
+    </row>
+    <row r="693" spans="1:6">
       <c r="A693"/>
       <c r="B693"/>
       <c r="C693"/>
       <c r="D693"/>
-    </row>
-    <row r="694" spans="1:5">
+      <c r="E693"/>
+    </row>
+    <row r="694" spans="1:6">
       <c r="A694"/>
       <c r="B694"/>
       <c r="C694"/>
       <c r="D694"/>
-    </row>
-    <row r="695" spans="1:5">
+      <c r="E694"/>
+    </row>
+    <row r="695" spans="1:6">
       <c r="A695"/>
       <c r="B695"/>
       <c r="C695"/>
       <c r="D695"/>
-    </row>
-    <row r="696" spans="1:5">
+      <c r="E695"/>
+    </row>
+    <row r="696" spans="1:6">
       <c r="A696"/>
       <c r="B696"/>
       <c r="C696"/>
       <c r="D696"/>
-    </row>
-    <row r="697" spans="1:5">
+      <c r="E696"/>
+    </row>
+    <row r="697" spans="1:6">
       <c r="A697"/>
       <c r="B697"/>
       <c r="C697"/>
       <c r="D697"/>
-    </row>
-    <row r="698" spans="1:5">
+      <c r="E697"/>
+    </row>
+    <row r="698" spans="1:6">
       <c r="A698"/>
       <c r="B698"/>
       <c r="C698"/>
       <c r="D698"/>
-    </row>
-    <row r="699" spans="1:5">
+      <c r="E698"/>
+    </row>
+    <row r="699" spans="1:6">
       <c r="A699"/>
       <c r="B699"/>
       <c r="C699"/>
       <c r="D699"/>
-    </row>
-    <row r="700" spans="1:5">
+      <c r="E699"/>
+    </row>
+    <row r="700" spans="1:6">
       <c r="A700"/>
       <c r="B700"/>
       <c r="C700"/>
       <c r="D700"/>
-    </row>
-    <row r="701" spans="1:5">
+      <c r="E700"/>
+    </row>
+    <row r="701" spans="1:6">
       <c r="A701"/>
       <c r="B701"/>
       <c r="C701"/>
       <c r="D701"/>
-    </row>
-    <row r="702" spans="1:5">
+      <c r="E701"/>
+    </row>
+    <row r="702" spans="1:6">
       <c r="A702"/>
       <c r="B702"/>
       <c r="C702"/>
       <c r="D702"/>
-    </row>
-    <row r="703" spans="1:5">
+      <c r="E702"/>
+    </row>
+    <row r="703" spans="1:6">
       <c r="A703"/>
       <c r="B703"/>
       <c r="C703"/>
       <c r="D703"/>
-    </row>
-    <row r="704" spans="1:5">
+      <c r="E703"/>
+    </row>
+    <row r="704" spans="1:6">
       <c r="A704"/>
       <c r="B704"/>
       <c r="C704"/>
       <c r="D704"/>
-    </row>
-    <row r="705" spans="1:5">
+      <c r="E704"/>
+    </row>
+    <row r="705" spans="1:6">
       <c r="A705"/>
       <c r="B705"/>
       <c r="C705"/>
       <c r="D705"/>
-    </row>
-    <row r="706" spans="1:5">
+      <c r="E705"/>
+    </row>
+    <row r="706" spans="1:6">
       <c r="A706"/>
       <c r="B706"/>
       <c r="C706"/>
       <c r="D706"/>
-    </row>
-    <row r="707" spans="1:5">
+      <c r="E706"/>
+    </row>
+    <row r="707" spans="1:6">
       <c r="A707"/>
       <c r="B707"/>
       <c r="C707"/>
       <c r="D707"/>
-    </row>
-    <row r="708" spans="1:5">
+      <c r="E707"/>
+    </row>
+    <row r="708" spans="1:6">
       <c r="A708"/>
       <c r="B708"/>
       <c r="C708"/>
       <c r="D708"/>
-    </row>
-    <row r="709" spans="1:5">
+      <c r="E708"/>
+    </row>
+    <row r="709" spans="1:6">
       <c r="A709"/>
       <c r="B709"/>
       <c r="C709"/>
       <c r="D709"/>
-    </row>
-    <row r="710" spans="1:5">
+      <c r="E709"/>
+    </row>
+    <row r="710" spans="1:6">
       <c r="A710"/>
       <c r="B710"/>
       <c r="C710"/>
       <c r="D710"/>
-    </row>
-    <row r="711" spans="1:5">
+      <c r="E710"/>
+    </row>
+    <row r="711" spans="1:6">
       <c r="A711"/>
       <c r="B711"/>
       <c r="C711"/>
       <c r="D711"/>
-    </row>
-    <row r="712" spans="1:5">
+      <c r="E711"/>
+    </row>
+    <row r="712" spans="1:6">
       <c r="A712"/>
       <c r="B712"/>
       <c r="C712"/>
       <c r="D712"/>
-    </row>
-    <row r="713" spans="1:5">
+      <c r="E712"/>
+    </row>
+    <row r="713" spans="1:6">
       <c r="A713"/>
       <c r="B713"/>
       <c r="C713"/>
       <c r="D713"/>
-    </row>
-    <row r="714" spans="1:5">
+      <c r="E713"/>
+    </row>
+    <row r="714" spans="1:6">
       <c r="A714"/>
       <c r="B714"/>
       <c r="C714"/>
       <c r="D714"/>
-    </row>
-    <row r="715" spans="1:5">
+      <c r="E714"/>
+    </row>
+    <row r="715" spans="1:6">
       <c r="A715"/>
       <c r="B715"/>
       <c r="C715"/>
       <c r="D715"/>
-    </row>
-    <row r="716" spans="1:5">
+      <c r="E715"/>
+    </row>
+    <row r="716" spans="1:6">
       <c r="A716"/>
       <c r="B716"/>
       <c r="C716"/>
       <c r="D716"/>
-    </row>
-    <row r="717" spans="1:5">
+      <c r="E716"/>
+    </row>
+    <row r="717" spans="1:6">
       <c r="A717"/>
       <c r="B717"/>
       <c r="C717"/>
       <c r="D717"/>
-    </row>
-    <row r="718" spans="1:5">
+      <c r="E717"/>
+    </row>
+    <row r="718" spans="1:6">
       <c r="A718"/>
       <c r="B718"/>
       <c r="C718"/>
       <c r="D718"/>
-    </row>
-    <row r="719" spans="1:5">
+      <c r="E718"/>
+    </row>
+    <row r="719" spans="1:6">
       <c r="A719"/>
       <c r="B719"/>
       <c r="C719"/>
       <c r="D719"/>
-    </row>
-    <row r="720" spans="1:5">
+      <c r="E719"/>
+    </row>
+    <row r="720" spans="1:6">
       <c r="A720"/>
       <c r="B720"/>
       <c r="C720"/>
       <c r="D720"/>
-    </row>
-    <row r="721" spans="1:5">
+      <c r="E720"/>
+    </row>
+    <row r="721" spans="1:6">
       <c r="A721"/>
       <c r="B721"/>
       <c r="C721"/>
       <c r="D721"/>
-    </row>
-    <row r="722" spans="1:5">
+      <c r="E721"/>
+    </row>
+    <row r="722" spans="1:6">
       <c r="A722"/>
       <c r="B722"/>
       <c r="C722"/>
       <c r="D722"/>
-    </row>
-    <row r="723" spans="1:5">
+      <c r="E722"/>
+    </row>
+    <row r="723" spans="1:6">
       <c r="A723"/>
       <c r="B723"/>
       <c r="C723"/>
       <c r="D723"/>
-    </row>
-    <row r="724" spans="1:5">
+      <c r="E723"/>
+    </row>
+    <row r="724" spans="1:6">
       <c r="A724"/>
       <c r="B724"/>
       <c r="C724"/>
       <c r="D724"/>
-    </row>
-    <row r="725" spans="1:5">
+      <c r="E724"/>
+    </row>
+    <row r="725" spans="1:6">
       <c r="A725"/>
       <c r="B725"/>
       <c r="C725"/>
       <c r="D725"/>
-    </row>
-    <row r="726" spans="1:5">
+      <c r="E725"/>
+    </row>
+    <row r="726" spans="1:6">
       <c r="A726"/>
       <c r="B726"/>
       <c r="C726"/>
       <c r="D726"/>
-    </row>
-    <row r="727" spans="1:5">
+      <c r="E726"/>
+    </row>
+    <row r="727" spans="1:6">
       <c r="A727"/>
       <c r="B727"/>
       <c r="C727"/>
       <c r="D727"/>
-    </row>
-    <row r="728" spans="1:5">
+      <c r="E727"/>
+    </row>
+    <row r="728" spans="1:6">
       <c r="A728"/>
       <c r="B728"/>
       <c r="C728"/>
       <c r="D728"/>
-    </row>
-    <row r="729" spans="1:5">
+      <c r="E728"/>
+    </row>
+    <row r="729" spans="1:6">
       <c r="A729"/>
       <c r="B729"/>
       <c r="C729"/>
       <c r="D729"/>
-    </row>
-    <row r="730" spans="1:5">
+      <c r="E729"/>
+    </row>
+    <row r="730" spans="1:6">
       <c r="A730"/>
       <c r="B730"/>
       <c r="C730"/>
       <c r="D730"/>
-    </row>
-    <row r="731" spans="1:5">
+      <c r="E730"/>
+    </row>
+    <row r="731" spans="1:6">
       <c r="A731"/>
       <c r="B731"/>
       <c r="C731"/>
       <c r="D731"/>
-    </row>
-    <row r="732" spans="1:5">
+      <c r="E731"/>
+    </row>
+    <row r="732" spans="1:6">
       <c r="A732"/>
       <c r="B732"/>
       <c r="C732"/>
       <c r="D732"/>
-    </row>
-    <row r="733" spans="1:5">
+      <c r="E732"/>
+    </row>
+    <row r="733" spans="1:6">
       <c r="A733"/>
       <c r="B733"/>
       <c r="C733"/>
       <c r="D733"/>
-    </row>
-    <row r="734" spans="1:5">
+      <c r="E733"/>
+    </row>
+    <row r="734" spans="1:6">
       <c r="A734"/>
       <c r="B734"/>
       <c r="C734"/>
       <c r="D734"/>
-    </row>
-    <row r="735" spans="1:5">
+      <c r="E734"/>
+    </row>
+    <row r="735" spans="1:6">
       <c r="A735"/>
       <c r="B735"/>
       <c r="C735"/>
       <c r="D735"/>
-    </row>
-    <row r="736" spans="1:5">
+      <c r="E735"/>
+    </row>
+    <row r="736" spans="1:6">
       <c r="A736"/>
       <c r="B736"/>
       <c r="C736"/>
       <c r="D736"/>
-    </row>
-    <row r="737" spans="1:5">
+      <c r="E736"/>
+    </row>
+    <row r="737" spans="1:6">
       <c r="A737"/>
       <c r="B737"/>
       <c r="C737"/>
       <c r="D737"/>
-    </row>
-    <row r="738" spans="1:5">
+      <c r="E737"/>
+    </row>
+    <row r="738" spans="1:6">
       <c r="A738"/>
       <c r="B738"/>
       <c r="C738"/>
       <c r="D738"/>
-    </row>
-    <row r="739" spans="1:5">
+      <c r="E738"/>
+    </row>
+    <row r="739" spans="1:6">
       <c r="A739"/>
       <c r="B739"/>
       <c r="C739"/>
       <c r="D739"/>
-    </row>
-    <row r="740" spans="1:5">
+      <c r="E739"/>
+    </row>
+    <row r="740" spans="1:6">
       <c r="A740"/>
       <c r="B740"/>
       <c r="C740"/>
       <c r="D740"/>
-    </row>
-    <row r="741" spans="1:5">
+      <c r="E740"/>
+    </row>
+    <row r="741" spans="1:6">
       <c r="A741"/>
       <c r="B741"/>
       <c r="C741"/>
       <c r="D741"/>
-    </row>
-    <row r="742" spans="1:5">
+      <c r="E741"/>
+    </row>
+    <row r="742" spans="1:6">
       <c r="A742"/>
       <c r="B742"/>
       <c r="C742"/>
       <c r="D742"/>
-    </row>
-    <row r="743" spans="1:5">
+      <c r="E742"/>
+    </row>
+    <row r="743" spans="1:6">
       <c r="A743"/>
       <c r="B743"/>
       <c r="C743"/>
       <c r="D743"/>
-    </row>
-    <row r="744" spans="1:5">
+      <c r="E743"/>
+    </row>
+    <row r="744" spans="1:6">
       <c r="A744"/>
       <c r="B744"/>
       <c r="C744"/>
       <c r="D744"/>
-    </row>
-    <row r="745" spans="1:5">
+      <c r="E744"/>
+    </row>
+    <row r="745" spans="1:6">
       <c r="A745"/>
       <c r="B745"/>
       <c r="C745"/>
       <c r="D745"/>
-    </row>
-    <row r="746" spans="1:5">
+      <c r="E745"/>
+    </row>
+    <row r="746" spans="1:6">
       <c r="A746"/>
       <c r="B746"/>
       <c r="C746"/>
       <c r="D746"/>
-    </row>
-    <row r="747" spans="1:5">
+      <c r="E746"/>
+    </row>
+    <row r="747" spans="1:6">
       <c r="A747"/>
       <c r="B747"/>
       <c r="C747"/>
       <c r="D747"/>
-    </row>
-    <row r="748" spans="1:5">
+      <c r="E747"/>
+    </row>
+    <row r="748" spans="1:6">
       <c r="A748"/>
       <c r="B748"/>
       <c r="C748"/>
       <c r="D748"/>
-    </row>
-    <row r="749" spans="1:5">
+      <c r="E748"/>
+    </row>
+    <row r="749" spans="1:6">
       <c r="A749"/>
       <c r="B749"/>
       <c r="C749"/>
       <c r="D749"/>
-    </row>
-    <row r="750" spans="1:5">
+      <c r="E749"/>
+    </row>
+    <row r="750" spans="1:6">
       <c r="A750"/>
       <c r="B750"/>
       <c r="C750"/>
       <c r="D750"/>
-    </row>
-    <row r="751" spans="1:5">
+      <c r="E750"/>
+    </row>
+    <row r="751" spans="1:6">
       <c r="A751"/>
       <c r="B751"/>
       <c r="C751"/>
       <c r="D751"/>
-    </row>
-    <row r="752" spans="1:5">
+      <c r="E751"/>
+    </row>
+    <row r="752" spans="1:6">
       <c r="A752"/>
       <c r="B752"/>
       <c r="C752"/>
       <c r="D752"/>
-    </row>
-    <row r="753" spans="1:5">
+      <c r="E752"/>
+    </row>
+    <row r="753" spans="1:6">
       <c r="A753"/>
       <c r="B753"/>
       <c r="C753"/>
       <c r="D753"/>
-    </row>
-    <row r="754" spans="1:5">
+      <c r="E753"/>
+    </row>
+    <row r="754" spans="1:6">
       <c r="A754"/>
       <c r="B754"/>
       <c r="C754"/>
       <c r="D754"/>
-    </row>
-    <row r="755" spans="1:5">
+      <c r="E754"/>
+    </row>
+    <row r="755" spans="1:6">
       <c r="A755"/>
       <c r="B755"/>
       <c r="C755"/>
       <c r="D755"/>
-    </row>
-    <row r="756" spans="1:5">
+      <c r="E755"/>
+    </row>
+    <row r="756" spans="1:6">
       <c r="A756"/>
       <c r="B756"/>
       <c r="C756"/>
       <c r="D756"/>
-    </row>
-    <row r="757" spans="1:5">
+      <c r="E756"/>
+    </row>
+    <row r="757" spans="1:6">
       <c r="A757"/>
       <c r="B757"/>
       <c r="C757"/>
       <c r="D757"/>
-    </row>
-    <row r="758" spans="1:5">
+      <c r="E757"/>
+    </row>
+    <row r="758" spans="1:6">
       <c r="A758"/>
       <c r="B758"/>
       <c r="C758"/>
       <c r="D758"/>
-    </row>
-    <row r="759" spans="1:5">
+      <c r="E758"/>
+    </row>
+    <row r="759" spans="1:6">
       <c r="A759"/>
       <c r="B759"/>
       <c r="C759"/>
       <c r="D759"/>
-    </row>
-    <row r="760" spans="1:5">
+      <c r="E759"/>
+    </row>
+    <row r="760" spans="1:6">
       <c r="A760"/>
       <c r="B760"/>
       <c r="C760"/>
       <c r="D760"/>
-    </row>
-    <row r="761" spans="1:5">
+      <c r="E760"/>
+    </row>
+    <row r="761" spans="1:6">
       <c r="A761"/>
       <c r="B761"/>
       <c r="C761"/>
       <c r="D761"/>
-    </row>
-    <row r="762" spans="1:5">
+      <c r="E761"/>
+    </row>
+    <row r="762" spans="1:6">
       <c r="A762"/>
       <c r="B762"/>
       <c r="C762"/>
       <c r="D762"/>
-    </row>
-    <row r="763" spans="1:5">
+      <c r="E762"/>
+    </row>
+    <row r="763" spans="1:6">
       <c r="A763"/>
       <c r="B763"/>
       <c r="C763"/>
       <c r="D763"/>
-    </row>
-    <row r="764" spans="1:5">
+      <c r="E763"/>
+    </row>
+    <row r="764" spans="1:6">
       <c r="A764"/>
       <c r="B764"/>
       <c r="C764"/>
       <c r="D764"/>
-    </row>
-    <row r="765" spans="1:5">
+      <c r="E764"/>
+    </row>
+    <row r="765" spans="1:6">
       <c r="A765"/>
       <c r="B765"/>
       <c r="C765"/>
       <c r="D765"/>
-    </row>
-    <row r="766" spans="1:5">
+      <c r="E765"/>
+    </row>
+    <row r="766" spans="1:6">
       <c r="A766"/>
       <c r="B766"/>
       <c r="C766"/>
       <c r="D766"/>
-    </row>
-    <row r="767" spans="1:5">
+      <c r="E766"/>
+    </row>
+    <row r="767" spans="1:6">
       <c r="A767"/>
       <c r="B767"/>
       <c r="C767"/>
       <c r="D767"/>
-    </row>
-    <row r="768" spans="1:5">
+      <c r="E767"/>
+    </row>
+    <row r="768" spans="1:6">
       <c r="A768"/>
       <c r="B768"/>
       <c r="C768"/>
       <c r="D768"/>
-    </row>
-    <row r="769" spans="1:5">
+      <c r="E768"/>
+    </row>
+    <row r="769" spans="1:6">
       <c r="A769"/>
       <c r="B769"/>
       <c r="C769"/>
       <c r="D769"/>
-    </row>
-    <row r="770" spans="1:5">
+      <c r="E769"/>
+    </row>
+    <row r="770" spans="1:6">
       <c r="A770"/>
       <c r="B770"/>
       <c r="C770"/>
       <c r="D770"/>
-    </row>
-    <row r="771" spans="1:5">
+      <c r="E770"/>
+    </row>
+    <row r="771" spans="1:6">
       <c r="A771"/>
       <c r="B771"/>
       <c r="C771"/>
       <c r="D771"/>
-    </row>
-    <row r="772" spans="1:5">
+      <c r="E771"/>
+    </row>
+    <row r="772" spans="1:6">
       <c r="A772"/>
       <c r="B772"/>
       <c r="C772"/>
       <c r="D772"/>
-    </row>
-    <row r="773" spans="1:5">
+      <c r="E772"/>
+    </row>
+    <row r="773" spans="1:6">
       <c r="A773"/>
       <c r="B773"/>
       <c r="C773"/>
       <c r="D773"/>
-    </row>
-    <row r="774" spans="1:5">
+      <c r="E773"/>
+    </row>
+    <row r="774" spans="1:6">
       <c r="A774"/>
       <c r="B774"/>
       <c r="C774"/>
       <c r="D774"/>
-    </row>
-    <row r="775" spans="1:5">
+      <c r="E774"/>
+    </row>
+    <row r="775" spans="1:6">
       <c r="A775"/>
       <c r="B775"/>
       <c r="C775"/>
       <c r="D775"/>
-    </row>
-    <row r="776" spans="1:5">
+      <c r="E775"/>
+    </row>
+    <row r="776" spans="1:6">
       <c r="A776"/>
       <c r="B776"/>
       <c r="C776"/>
       <c r="D776"/>
-    </row>
-    <row r="777" spans="1:5">
+      <c r="E776"/>
+    </row>
+    <row r="777" spans="1:6">
       <c r="A777"/>
       <c r="B777"/>
       <c r="C777"/>
       <c r="D777"/>
-    </row>
-    <row r="778" spans="1:5">
+      <c r="E777"/>
+    </row>
+    <row r="778" spans="1:6">
       <c r="A778"/>
       <c r="B778"/>
       <c r="C778"/>
       <c r="D778"/>
-    </row>
-    <row r="779" spans="1:5">
+      <c r="E778"/>
+    </row>
+    <row r="779" spans="1:6">
       <c r="A779"/>
       <c r="B779"/>
       <c r="C779"/>
       <c r="D779"/>
-    </row>
-    <row r="780" spans="1:5">
+      <c r="E779"/>
+    </row>
+    <row r="780" spans="1:6">
       <c r="A780"/>
       <c r="B780"/>
       <c r="C780"/>
       <c r="D780"/>
-    </row>
-    <row r="781" spans="1:5">
+      <c r="E780"/>
+    </row>
+    <row r="781" spans="1:6">
       <c r="A781"/>
       <c r="B781"/>
       <c r="C781"/>
       <c r="D781"/>
-    </row>
-    <row r="782" spans="1:5">
+      <c r="E781"/>
+    </row>
+    <row r="782" spans="1:6">
       <c r="A782"/>
       <c r="B782"/>
       <c r="C782"/>
       <c r="D782"/>
-    </row>
-    <row r="783" spans="1:5">
+      <c r="E782"/>
+    </row>
+    <row r="783" spans="1:6">
       <c r="A783"/>
       <c r="B783"/>
       <c r="C783"/>
       <c r="D783"/>
-    </row>
-    <row r="784" spans="1:5">
+      <c r="E783"/>
+    </row>
+    <row r="784" spans="1:6">
       <c r="A784"/>
       <c r="B784"/>
       <c r="C784"/>
       <c r="D784"/>
-    </row>
-    <row r="785" spans="1:5">
+      <c r="E784"/>
+    </row>
+    <row r="785" spans="1:6">
       <c r="A785"/>
       <c r="B785"/>
       <c r="C785"/>
       <c r="D785"/>
-    </row>
-    <row r="786" spans="1:5">
+      <c r="E785"/>
+    </row>
+    <row r="786" spans="1:6">
       <c r="A786"/>
       <c r="B786"/>
       <c r="C786"/>
       <c r="D786"/>
-    </row>
-    <row r="787" spans="1:5">
+      <c r="E786"/>
+    </row>
+    <row r="787" spans="1:6">
       <c r="A787"/>
       <c r="B787"/>
       <c r="C787"/>
       <c r="D787"/>
-    </row>
-    <row r="788" spans="1:5">
+      <c r="E787"/>
+    </row>
+    <row r="788" spans="1:6">
       <c r="A788"/>
       <c r="B788"/>
       <c r="C788"/>
       <c r="D788"/>
-    </row>
-    <row r="789" spans="1:5">
+      <c r="E788"/>
+    </row>
+    <row r="789" spans="1:6">
       <c r="A789"/>
       <c r="B789"/>
       <c r="C789"/>
       <c r="D789"/>
-    </row>
-    <row r="790" spans="1:5">
+      <c r="E789"/>
+    </row>
+    <row r="790" spans="1:6">
       <c r="A790"/>
       <c r="B790"/>
       <c r="C790"/>
       <c r="D790"/>
-    </row>
-    <row r="791" spans="1:5">
+      <c r="E790"/>
+    </row>
+    <row r="791" spans="1:6">
       <c r="A791"/>
       <c r="B791"/>
       <c r="C791"/>
       <c r="D791"/>
-    </row>
-    <row r="792" spans="1:5">
+      <c r="E791"/>
+    </row>
+    <row r="792" spans="1:6">
       <c r="A792"/>
       <c r="B792"/>
       <c r="C792"/>
       <c r="D792"/>
-    </row>
-    <row r="793" spans="1:5">
+      <c r="E792"/>
+    </row>
+    <row r="793" spans="1:6">
       <c r="A793"/>
       <c r="B793"/>
       <c r="C793"/>
       <c r="D793"/>
-    </row>
-    <row r="794" spans="1:5">
+      <c r="E793"/>
+    </row>
+    <row r="794" spans="1:6">
       <c r="A794"/>
       <c r="B794"/>
       <c r="C794"/>
       <c r="D794"/>
-    </row>
-    <row r="795" spans="1:5">
+      <c r="E794"/>
+    </row>
+    <row r="795" spans="1:6">
       <c r="A795"/>
       <c r="B795"/>
       <c r="C795"/>
       <c r="D795"/>
-    </row>
-    <row r="796" spans="1:5">
+      <c r="E795"/>
+    </row>
+    <row r="796" spans="1:6">
       <c r="A796"/>
       <c r="B796"/>
       <c r="C796"/>
       <c r="D796"/>
-    </row>
-    <row r="797" spans="1:5">
+      <c r="E796"/>
+    </row>
+    <row r="797" spans="1:6">
       <c r="A797"/>
       <c r="B797"/>
       <c r="C797"/>
       <c r="D797"/>
-    </row>
-    <row r="798" spans="1:5">
+      <c r="E797"/>
+    </row>
+    <row r="798" spans="1:6">
       <c r="A798"/>
       <c r="B798"/>
       <c r="C798"/>
       <c r="D798"/>
-    </row>
-    <row r="799" spans="1:5">
+      <c r="E798"/>
+    </row>
+    <row r="799" spans="1:6">
       <c r="A799"/>
       <c r="B799"/>
       <c r="C799"/>
       <c r="D799"/>
-    </row>
-    <row r="800" spans="1:5">
+      <c r="E799"/>
+    </row>
+    <row r="800" spans="1:6">
       <c r="A800"/>
       <c r="B800"/>
       <c r="C800"/>
       <c r="D800"/>
-    </row>
-    <row r="801" spans="1:5">
+      <c r="E800"/>
+    </row>
+    <row r="801" spans="1:6">
       <c r="A801"/>
       <c r="B801"/>
       <c r="C801"/>
       <c r="D801"/>
-    </row>
-    <row r="802" spans="1:5">
+      <c r="E801"/>
+    </row>
+    <row r="802" spans="1:6">
       <c r="A802"/>
       <c r="B802"/>
       <c r="C802"/>
       <c r="D802"/>
-    </row>
-    <row r="803" spans="1:5">
+      <c r="E802"/>
+    </row>
+    <row r="803" spans="1:6">
       <c r="A803"/>
       <c r="B803"/>
       <c r="C803"/>
       <c r="D803"/>
-    </row>
-    <row r="804" spans="1:5">
+      <c r="E803"/>
+    </row>
+    <row r="804" spans="1:6">
       <c r="A804"/>
       <c r="B804"/>
       <c r="C804"/>
       <c r="D804"/>
-    </row>
-    <row r="805" spans="1:5">
+      <c r="E804"/>
+    </row>
+    <row r="805" spans="1:6">
       <c r="A805"/>
       <c r="B805"/>
       <c r="C805"/>
       <c r="D805"/>
-    </row>
-    <row r="806" spans="1:5">
+      <c r="E805"/>
+    </row>
+    <row r="806" spans="1:6">
       <c r="A806"/>
       <c r="B806"/>
       <c r="C806"/>
       <c r="D806"/>
-    </row>
-    <row r="807" spans="1:5">
+      <c r="E806"/>
+    </row>
+    <row r="807" spans="1:6">
       <c r="A807"/>
       <c r="B807"/>
       <c r="C807"/>
       <c r="D807"/>
-    </row>
-    <row r="808" spans="1:5">
+      <c r="E807"/>
+    </row>
+    <row r="808" spans="1:6">
       <c r="A808"/>
       <c r="B808"/>
       <c r="C808"/>
       <c r="D808"/>
-    </row>
-    <row r="809" spans="1:5">
+      <c r="E808"/>
+    </row>
+    <row r="809" spans="1:6">
       <c r="A809"/>
       <c r="B809"/>
       <c r="C809"/>
       <c r="D809"/>
-    </row>
-    <row r="810" spans="1:5">
+      <c r="E809"/>
+    </row>
+    <row r="810" spans="1:6">
       <c r="A810"/>
       <c r="B810"/>
       <c r="C810"/>
       <c r="D810"/>
-    </row>
-    <row r="811" spans="1:5">
+      <c r="E810"/>
+    </row>
+    <row r="811" spans="1:6">
       <c r="A811"/>
       <c r="B811"/>
       <c r="C811"/>
       <c r="D811"/>
-    </row>
-    <row r="812" spans="1:5">
+      <c r="E811"/>
+    </row>
+    <row r="812" spans="1:6">
       <c r="A812"/>
       <c r="B812"/>
       <c r="C812"/>
       <c r="D812"/>
-    </row>
-    <row r="813" spans="1:5">
+      <c r="E812"/>
+    </row>
+    <row r="813" spans="1:6">
       <c r="A813"/>
       <c r="B813"/>
       <c r="C813"/>
       <c r="D813"/>
-    </row>
-    <row r="814" spans="1:5">
+      <c r="E813"/>
+    </row>
+    <row r="814" spans="1:6">
       <c r="A814"/>
       <c r="B814"/>
       <c r="C814"/>
       <c r="D814"/>
-    </row>
-    <row r="815" spans="1:5">
+      <c r="E814"/>
+    </row>
+    <row r="815" spans="1:6">
       <c r="A815"/>
       <c r="B815"/>
       <c r="C815"/>
       <c r="D815"/>
-    </row>
-    <row r="816" spans="1:5">
+      <c r="E815"/>
+    </row>
+    <row r="816" spans="1:6">
       <c r="A816"/>
       <c r="B816"/>
       <c r="C816"/>
       <c r="D816"/>
-    </row>
-    <row r="817" spans="1:5">
+      <c r="E816"/>
+    </row>
+    <row r="817" spans="1:6">
       <c r="A817"/>
       <c r="B817"/>
       <c r="C817"/>
       <c r="D817"/>
-    </row>
-    <row r="818" spans="1:5">
+      <c r="E817"/>
+    </row>
+    <row r="818" spans="1:6">
       <c r="A818"/>
       <c r="B818"/>
       <c r="C818"/>
       <c r="D818"/>
-    </row>
-    <row r="819" spans="1:5">
+      <c r="E818"/>
+    </row>
+    <row r="819" spans="1:6">
       <c r="A819"/>
       <c r="B819"/>
       <c r="C819"/>
       <c r="D819"/>
-    </row>
-    <row r="820" spans="1:5">
+      <c r="E819"/>
+    </row>
+    <row r="820" spans="1:6">
       <c r="A820"/>
       <c r="B820"/>
       <c r="C820"/>
       <c r="D820"/>
-    </row>
-    <row r="821" spans="1:5">
+      <c r="E820"/>
+    </row>
+    <row r="821" spans="1:6">
       <c r="A821"/>
       <c r="B821"/>
       <c r="C821"/>
       <c r="D821"/>
-    </row>
-    <row r="822" spans="1:5">
+      <c r="E821"/>
+    </row>
+    <row r="822" spans="1:6">
       <c r="A822"/>
       <c r="B822"/>
       <c r="C822"/>
       <c r="D822"/>
-    </row>
-    <row r="823" spans="1:5">
+      <c r="E822"/>
+    </row>
+    <row r="823" spans="1:6">
       <c r="A823"/>
       <c r="B823"/>
       <c r="C823"/>
       <c r="D823"/>
-    </row>
-    <row r="824" spans="1:5">
+      <c r="E823"/>
+    </row>
+    <row r="824" spans="1:6">
       <c r="A824"/>
       <c r="B824"/>
       <c r="C824"/>
       <c r="D824"/>
-    </row>
-    <row r="825" spans="1:5">
+      <c r="E824"/>
+    </row>
+    <row r="825" spans="1:6">
       <c r="A825"/>
       <c r="B825"/>
       <c r="C825"/>
       <c r="D825"/>
-    </row>
-    <row r="826" spans="1:5">
+      <c r="E825"/>
+    </row>
+    <row r="826" spans="1:6">
       <c r="A826"/>
       <c r="B826"/>
       <c r="C826"/>
       <c r="D826"/>
-    </row>
-    <row r="827" spans="1:5">
+      <c r="E826"/>
+    </row>
+    <row r="827" spans="1:6">
       <c r="A827"/>
       <c r="B827"/>
       <c r="C827"/>
       <c r="D827"/>
-    </row>
-    <row r="828" spans="1:5">
+      <c r="E827"/>
+    </row>
+    <row r="828" spans="1:6">
       <c r="A828"/>
       <c r="B828"/>
       <c r="C828"/>
       <c r="D828"/>
-    </row>
-    <row r="829" spans="1:5">
+      <c r="E828"/>
+    </row>
+    <row r="829" spans="1:6">
       <c r="A829"/>
       <c r="B829"/>
       <c r="C829"/>
       <c r="D829"/>
-    </row>
-    <row r="830" spans="1:5">
+      <c r="E829"/>
+    </row>
+    <row r="830" spans="1:6">
       <c r="A830"/>
       <c r="B830"/>
       <c r="C830"/>
       <c r="D830"/>
-    </row>
-    <row r="831" spans="1:5">
+      <c r="E830"/>
+    </row>
+    <row r="831" spans="1:6">
       <c r="A831"/>
       <c r="B831"/>
       <c r="C831"/>
       <c r="D831"/>
-    </row>
-    <row r="832" spans="1:5">
+      <c r="E831"/>
+    </row>
+    <row r="832" spans="1:6">
       <c r="A832"/>
       <c r="B832"/>
       <c r="C832"/>
       <c r="D832"/>
-    </row>
-    <row r="833" spans="1:5">
+      <c r="E832"/>
+    </row>
+    <row r="833" spans="1:6">
       <c r="A833"/>
       <c r="B833"/>
       <c r="C833"/>
       <c r="D833"/>
-    </row>
-    <row r="834" spans="1:5">
+      <c r="E833"/>
+    </row>
+    <row r="834" spans="1:6">
       <c r="A834"/>
       <c r="B834"/>
       <c r="C834"/>
       <c r="D834"/>
-    </row>
-    <row r="835" spans="1:5">
+      <c r="E834"/>
+    </row>
+    <row r="835" spans="1:6">
       <c r="A835"/>
       <c r="B835"/>
       <c r="C835"/>
       <c r="D835"/>
-    </row>
-    <row r="836" spans="1:5">
+      <c r="E835"/>
+    </row>
+    <row r="836" spans="1:6">
       <c r="A836"/>
       <c r="B836"/>
       <c r="C836"/>
       <c r="D836"/>
-    </row>
-    <row r="837" spans="1:5">
+      <c r="E836"/>
+    </row>
+    <row r="837" spans="1:6">
       <c r="A837"/>
       <c r="B837"/>
       <c r="C837"/>
       <c r="D837"/>
-    </row>
-    <row r="838" spans="1:5">
+      <c r="E837"/>
+    </row>
+    <row r="838" spans="1:6">
       <c r="A838"/>
       <c r="B838"/>
       <c r="C838"/>
       <c r="D838"/>
-    </row>
-    <row r="839" spans="1:5">
+      <c r="E838"/>
+    </row>
+    <row r="839" spans="1:6">
       <c r="A839"/>
       <c r="B839"/>
       <c r="C839"/>
       <c r="D839"/>
-    </row>
-    <row r="840" spans="1:5">
+      <c r="E839"/>
+    </row>
+    <row r="840" spans="1:6">
       <c r="A840"/>
       <c r="B840"/>
       <c r="C840"/>
       <c r="D840"/>
-    </row>
-    <row r="841" spans="1:5">
+      <c r="E840"/>
+    </row>
+    <row r="841" spans="1:6">
       <c r="A841"/>
       <c r="B841"/>
       <c r="C841"/>
       <c r="D841"/>
-    </row>
-    <row r="842" spans="1:5">
+      <c r="E841"/>
+    </row>
+    <row r="842" spans="1:6">
       <c r="A842"/>
       <c r="B842"/>
       <c r="C842"/>
       <c r="D842"/>
-    </row>
-    <row r="843" spans="1:5">
+      <c r="E842"/>
+    </row>
+    <row r="843" spans="1:6">
       <c r="A843"/>
       <c r="B843"/>
       <c r="C843"/>
       <c r="D843"/>
-    </row>
-    <row r="844" spans="1:5">
+      <c r="E843"/>
+    </row>
+    <row r="844" spans="1:6">
       <c r="A844"/>
       <c r="B844"/>
       <c r="C844"/>
       <c r="D844"/>
-    </row>
-    <row r="845" spans="1:5">
+      <c r="E844"/>
+    </row>
+    <row r="845" spans="1:6">
       <c r="A845"/>
       <c r="B845"/>
       <c r="C845"/>
       <c r="D845"/>
-    </row>
-    <row r="846" spans="1:5">
+      <c r="E845"/>
+    </row>
+    <row r="846" spans="1:6">
       <c r="A846"/>
       <c r="B846"/>
       <c r="C846"/>
       <c r="D846"/>
-    </row>
-    <row r="847" spans="1:5">
+      <c r="E846"/>
+    </row>
+    <row r="847" spans="1:6">
       <c r="A847"/>
       <c r="B847"/>
       <c r="C847"/>
       <c r="D847"/>
-    </row>
-    <row r="848" spans="1:5">
+      <c r="E847"/>
+    </row>
+    <row r="848" spans="1:6">
       <c r="A848"/>
       <c r="B848"/>
       <c r="C848"/>
       <c r="D848"/>
-    </row>
-    <row r="849" spans="1:5">
+      <c r="E848"/>
+    </row>
+    <row r="849" spans="1:6">
       <c r="A849"/>
       <c r="B849"/>
       <c r="C849"/>
       <c r="D849"/>
-    </row>
-    <row r="850" spans="1:5">
+      <c r="E849"/>
+    </row>
+    <row r="850" spans="1:6">
       <c r="A850"/>
       <c r="B850"/>
       <c r="C850"/>
       <c r="D850"/>
-    </row>
-    <row r="851" spans="1:5">
+      <c r="E850"/>
+    </row>
+    <row r="851" spans="1:6">
       <c r="A851"/>
       <c r="B851"/>
       <c r="C851"/>
       <c r="D851"/>
-    </row>
-    <row r="852" spans="1:5">
+      <c r="E851"/>
+    </row>
+    <row r="852" spans="1:6">
       <c r="A852"/>
       <c r="B852"/>
       <c r="C852"/>
       <c r="D852"/>
-    </row>
-    <row r="853" spans="1:5">
+      <c r="E852"/>
+    </row>
+    <row r="853" spans="1:6">
       <c r="A853"/>
       <c r="B853"/>
       <c r="C853"/>
       <c r="D853"/>
-    </row>
-    <row r="854" spans="1:5">
+      <c r="E853"/>
+    </row>
+    <row r="854" spans="1:6">
       <c r="A854"/>
       <c r="B854"/>
       <c r="C854"/>
       <c r="D854"/>
-    </row>
-    <row r="855" spans="1:5">
+      <c r="E854"/>
+    </row>
+    <row r="855" spans="1:6">
       <c r="A855"/>
       <c r="B855"/>
       <c r="C855"/>
       <c r="D855"/>
-    </row>
-    <row r="856" spans="1:5">
+      <c r="E855"/>
+    </row>
+    <row r="856" spans="1:6">
       <c r="A856"/>
       <c r="B856"/>
       <c r="C856"/>
       <c r="D856"/>
-    </row>
-    <row r="857" spans="1:5">
+      <c r="E856"/>
+    </row>
+    <row r="857" spans="1:6">
       <c r="A857"/>
       <c r="B857"/>
       <c r="C857"/>
       <c r="D857"/>
-    </row>
-    <row r="858" spans="1:5">
+      <c r="E857"/>
+    </row>
+    <row r="858" spans="1:6">
       <c r="A858"/>
       <c r="B858"/>
       <c r="C858"/>
       <c r="D858"/>
-    </row>
-    <row r="859" spans="1:5">
+      <c r="E858"/>
+    </row>
+    <row r="859" spans="1:6">
       <c r="A859"/>
       <c r="B859"/>
       <c r="C859"/>
       <c r="D859"/>
-    </row>
-    <row r="860" spans="1:5">
+      <c r="E859"/>
+    </row>
+    <row r="860" spans="1:6">
       <c r="A860"/>
       <c r="B860"/>
       <c r="C860"/>
       <c r="D860"/>
-    </row>
-    <row r="861" spans="1:5">
+      <c r="E860"/>
+    </row>
+    <row r="861" spans="1:6">
       <c r="A861"/>
       <c r="B861"/>
       <c r="C861"/>
       <c r="D861"/>
-    </row>
-    <row r="862" spans="1:5">
+      <c r="E861"/>
+    </row>
+    <row r="862" spans="1:6">
       <c r="A862"/>
       <c r="B862"/>
       <c r="C862"/>
       <c r="D862"/>
-    </row>
-    <row r="863" spans="1:5">
+      <c r="E862"/>
+    </row>
+    <row r="863" spans="1:6">
       <c r="A863"/>
       <c r="B863"/>
       <c r="C863"/>
       <c r="D863"/>
-    </row>
-    <row r="864" spans="1:5">
+      <c r="E863"/>
+    </row>
+    <row r="864" spans="1:6">
       <c r="A864"/>
       <c r="B864"/>
       <c r="C864"/>
       <c r="D864"/>
-    </row>
-    <row r="865" spans="1:5">
+      <c r="E864"/>
+    </row>
+    <row r="865" spans="1:6">
       <c r="A865"/>
       <c r="B865"/>
       <c r="C865"/>
       <c r="D865"/>
-    </row>
-    <row r="866" spans="1:5">
+      <c r="E865"/>
+    </row>
+    <row r="866" spans="1:6">
       <c r="A866"/>
       <c r="B866"/>
       <c r="C866"/>
       <c r="D866"/>
-    </row>
-    <row r="867" spans="1:5">
+      <c r="E866"/>
+    </row>
+    <row r="867" spans="1:6">
       <c r="A867"/>
       <c r="B867"/>
       <c r="C867"/>
       <c r="D867"/>
-    </row>
-    <row r="868" spans="1:5">
+      <c r="E867"/>
+    </row>
+    <row r="868" spans="1:6">
       <c r="A868"/>
       <c r="B868"/>
       <c r="C868"/>
       <c r="D868"/>
-    </row>
-    <row r="869" spans="1:5">
+      <c r="E868"/>
+    </row>
+    <row r="869" spans="1:6">
       <c r="A869"/>
       <c r="B869"/>
       <c r="C869"/>
       <c r="D869"/>
-    </row>
-    <row r="870" spans="1:5">
+      <c r="E869"/>
+    </row>
+    <row r="870" spans="1:6">
       <c r="A870"/>
       <c r="B870"/>
       <c r="C870"/>
       <c r="D870"/>
-    </row>
-    <row r="871" spans="1:5">
+      <c r="E870"/>
+    </row>
+    <row r="871" spans="1:6">
       <c r="A871"/>
       <c r="B871"/>
       <c r="C871"/>
       <c r="D871"/>
-    </row>
-    <row r="872" spans="1:5">
+      <c r="E871"/>
+    </row>
+    <row r="872" spans="1:6">
       <c r="A872"/>
       <c r="B872"/>
       <c r="C872"/>
       <c r="D872"/>
-    </row>
-    <row r="873" spans="1:5">
+      <c r="E872"/>
+    </row>
+    <row r="873" spans="1:6">
       <c r="A873"/>
       <c r="B873"/>
       <c r="C873"/>
       <c r="D873"/>
-    </row>
-    <row r="874" spans="1:5">
+      <c r="E873"/>
+    </row>
+    <row r="874" spans="1:6">
       <c r="A874"/>
       <c r="B874"/>
       <c r="C874"/>
       <c r="D874"/>
-    </row>
-    <row r="875" spans="1:5">
+      <c r="E874"/>
+    </row>
+    <row r="875" spans="1:6">
       <c r="A875"/>
       <c r="B875"/>
       <c r="C875"/>
       <c r="D875"/>
-    </row>
-    <row r="876" spans="1:5">
+      <c r="E875"/>
+    </row>
+    <row r="876" spans="1:6">
       <c r="A876"/>
       <c r="B876"/>
       <c r="C876"/>
       <c r="D876"/>
-    </row>
-    <row r="877" spans="1:5">
+      <c r="E876"/>
+    </row>
+    <row r="877" spans="1:6">
       <c r="A877"/>
       <c r="B877"/>
       <c r="C877"/>
       <c r="D877"/>
-    </row>
-    <row r="878" spans="1:5">
+      <c r="E877"/>
+    </row>
+    <row r="878" spans="1:6">
       <c r="A878"/>
       <c r="B878"/>
       <c r="C878"/>
       <c r="D878"/>
-    </row>
-    <row r="879" spans="1:5">
+      <c r="E878"/>
+    </row>
+    <row r="879" spans="1:6">
       <c r="A879"/>
       <c r="B879"/>
       <c r="C879"/>
       <c r="D879"/>
-    </row>
-    <row r="880" spans="1:5">
+      <c r="E879"/>
+    </row>
+    <row r="880" spans="1:6">
       <c r="A880"/>
       <c r="B880"/>
       <c r="C880"/>
       <c r="D880"/>
-    </row>
-    <row r="881" spans="1:5">
+      <c r="E880"/>
+    </row>
+    <row r="881" spans="1:6">
       <c r="A881"/>
       <c r="B881"/>
       <c r="C881"/>
       <c r="D881"/>
-    </row>
-    <row r="882" spans="1:5">
+      <c r="E881"/>
+    </row>
+    <row r="882" spans="1:6">
       <c r="A882"/>
       <c r="B882"/>
       <c r="C882"/>
       <c r="D882"/>
-    </row>
-    <row r="883" spans="1:5">
+      <c r="E882"/>
+    </row>
+    <row r="883" spans="1:6">
       <c r="A883"/>
       <c r="B883"/>
       <c r="C883"/>
       <c r="D883"/>
-    </row>
-    <row r="884" spans="1:5">
+      <c r="E883"/>
+    </row>
+    <row r="884" spans="1:6">
       <c r="A884"/>
       <c r="B884"/>
       <c r="C884"/>
       <c r="D884"/>
-    </row>
-    <row r="885" spans="1:5">
+      <c r="E884"/>
+    </row>
+    <row r="885" spans="1:6">
       <c r="A885"/>
       <c r="B885"/>
       <c r="C885"/>
       <c r="D885"/>
-    </row>
-    <row r="886" spans="1:5">
+      <c r="E885"/>
+    </row>
+    <row r="886" spans="1:6">
       <c r="A886"/>
       <c r="B886"/>
       <c r="C886"/>
       <c r="D886"/>
-    </row>
-    <row r="887" spans="1:5">
+      <c r="E886"/>
+    </row>
+    <row r="887" spans="1:6">
       <c r="A887"/>
       <c r="B887"/>
       <c r="C887"/>
       <c r="D887"/>
-    </row>
-    <row r="888" spans="1:5">
+      <c r="E887"/>
+    </row>
+    <row r="888" spans="1:6">
       <c r="A888"/>
       <c r="B888"/>
       <c r="C888"/>
       <c r="D888"/>
-    </row>
-    <row r="889" spans="1:5">
+      <c r="E888"/>
+    </row>
+    <row r="889" spans="1:6">
       <c r="A889"/>
       <c r="B889"/>
       <c r="C889"/>
       <c r="D889"/>
-    </row>
-    <row r="890" spans="1:5">
+      <c r="E889"/>
+    </row>
+    <row r="890" spans="1:6">
       <c r="A890"/>
       <c r="B890"/>
       <c r="C890"/>
       <c r="D890"/>
-    </row>
-    <row r="891" spans="1:5">
+      <c r="E890"/>
+    </row>
+    <row r="891" spans="1:6">
       <c r="A891"/>
       <c r="B891"/>
       <c r="C891"/>
       <c r="D891"/>
-    </row>
-    <row r="892" spans="1:5">
+      <c r="E891"/>
+    </row>
+    <row r="892" spans="1:6">
       <c r="A892"/>
       <c r="B892"/>
       <c r="C892"/>
       <c r="D892"/>
-    </row>
-    <row r="893" spans="1:5">
+      <c r="E892"/>
+    </row>
+    <row r="893" spans="1:6">
       <c r="A893"/>
       <c r="B893"/>
       <c r="C893"/>
       <c r="D893"/>
-    </row>
-    <row r="894" spans="1:5">
+      <c r="E893"/>
+    </row>
+    <row r="894" spans="1:6">
       <c r="A894"/>
       <c r="B894"/>
       <c r="C894"/>
       <c r="D894"/>
-    </row>
-    <row r="895" spans="1:5">
+      <c r="E894"/>
+    </row>
+    <row r="895" spans="1:6">
       <c r="A895"/>
       <c r="B895"/>
       <c r="C895"/>
       <c r="D895"/>
-    </row>
-    <row r="896" spans="1:5">
+      <c r="E895"/>
+    </row>
+    <row r="896" spans="1:6">
       <c r="A896"/>
       <c r="B896"/>
       <c r="C896"/>
       <c r="D896"/>
-    </row>
-    <row r="897" spans="1:5">
+      <c r="E896"/>
+    </row>
+    <row r="897" spans="1:6">
       <c r="A897"/>
       <c r="B897"/>
       <c r="C897"/>
       <c r="D897"/>
-    </row>
-    <row r="898" spans="1:5">
+      <c r="E897"/>
+    </row>
+    <row r="898" spans="1:6">
       <c r="A898"/>
       <c r="B898"/>
       <c r="C898"/>
       <c r="D898"/>
-    </row>
-    <row r="899" spans="1:5">
+      <c r="E898"/>
+    </row>
+    <row r="899" spans="1:6">
       <c r="A899"/>
       <c r="B899"/>
       <c r="C899"/>
       <c r="D899"/>
-    </row>
-    <row r="900" spans="1:5">
+      <c r="E899"/>
+    </row>
+    <row r="900" spans="1:6">
       <c r="A900"/>
       <c r="B900"/>
       <c r="C900"/>
       <c r="D900"/>
-    </row>
-    <row r="901" spans="1:5">
+      <c r="E900"/>
+    </row>
+    <row r="901" spans="1:6">
       <c r="A901"/>
       <c r="B901"/>
       <c r="C901"/>
       <c r="D901"/>
-    </row>
-    <row r="902" spans="1:5">
+      <c r="E901"/>
+    </row>
+    <row r="902" spans="1:6">
       <c r="A902"/>
       <c r="B902"/>
       <c r="C902"/>
       <c r="D902"/>
-    </row>
-    <row r="903" spans="1:5">
+      <c r="E902"/>
+    </row>
+    <row r="903" spans="1:6">
       <c r="A903"/>
       <c r="B903"/>
       <c r="C903"/>
       <c r="D903"/>
-    </row>
-    <row r="904" spans="1:5">
+      <c r="E903"/>
+    </row>
+    <row r="904" spans="1:6">
       <c r="A904"/>
       <c r="B904"/>
       <c r="C904"/>
       <c r="D904"/>
-    </row>
-    <row r="905" spans="1:5">
+      <c r="E904"/>
+    </row>
+    <row r="905" spans="1:6">
       <c r="A905"/>
       <c r="B905"/>
       <c r="C905"/>
       <c r="D905"/>
-    </row>
-    <row r="906" spans="1:5">
+      <c r="E905"/>
+    </row>
+    <row r="906" spans="1:6">
       <c r="A906"/>
       <c r="B906"/>
       <c r="C906"/>
       <c r="D906"/>
-    </row>
-    <row r="907" spans="1:5">
+      <c r="E906"/>
+    </row>
+    <row r="907" spans="1:6">
       <c r="A907"/>
       <c r="B907"/>
       <c r="C907"/>
       <c r="D907"/>
-    </row>
-    <row r="908" spans="1:5">
+      <c r="E907"/>
+    </row>
+    <row r="908" spans="1:6">
       <c r="A908"/>
       <c r="B908"/>
       <c r="C908"/>
       <c r="D908"/>
-    </row>
-    <row r="909" spans="1:5">
+      <c r="E908"/>
+    </row>
+    <row r="909" spans="1:6">
       <c r="A909"/>
       <c r="B909"/>
       <c r="C909"/>
       <c r="D909"/>
-    </row>
-    <row r="910" spans="1:5">
+      <c r="E909"/>
+    </row>
+    <row r="910" spans="1:6">
       <c r="A910"/>
       <c r="B910"/>
       <c r="C910"/>
       <c r="D910"/>
-    </row>
-    <row r="911" spans="1:5">
+      <c r="E910"/>
+    </row>
+    <row r="911" spans="1:6">
       <c r="A911"/>
       <c r="B911"/>
       <c r="C911"/>
       <c r="D911"/>
-    </row>
-    <row r="912" spans="1:5">
+      <c r="E911"/>
+    </row>
+    <row r="912" spans="1:6">
       <c r="A912"/>
       <c r="B912"/>
       <c r="C912"/>
       <c r="D912"/>
-    </row>
-    <row r="913" spans="1:5">
+      <c r="E912"/>
+    </row>
+    <row r="913" spans="1:6">
       <c r="A913"/>
       <c r="B913"/>
       <c r="C913"/>
       <c r="D913"/>
-    </row>
-    <row r="914" spans="1:5">
+      <c r="E913"/>
+    </row>
+    <row r="914" spans="1:6">
       <c r="A914"/>
       <c r="B914"/>
       <c r="C914"/>
       <c r="D914"/>
-    </row>
-    <row r="915" spans="1:5">
+      <c r="E914"/>
+    </row>
+    <row r="915" spans="1:6">
       <c r="A915"/>
       <c r="B915"/>
       <c r="C915"/>
       <c r="D915"/>
-    </row>
-    <row r="916" spans="1:5">
+      <c r="E915"/>
+    </row>
+    <row r="916" spans="1:6">
       <c r="A916"/>
       <c r="B916"/>
       <c r="C916"/>
       <c r="D916"/>
-    </row>
-    <row r="917" spans="1:5">
+      <c r="E916"/>
+    </row>
+    <row r="917" spans="1:6">
       <c r="A917"/>
       <c r="B917"/>
       <c r="C917"/>
       <c r="D917"/>
-    </row>
-    <row r="918" spans="1:5">
+      <c r="E917"/>
+    </row>
+    <row r="918" spans="1:6">
       <c r="A918"/>
       <c r="B918"/>
       <c r="C918"/>
       <c r="D918"/>
-    </row>
-    <row r="919" spans="1:5">
+      <c r="E918"/>
+    </row>
+    <row r="919" spans="1:6">
       <c r="A919"/>
       <c r="B919"/>
       <c r="C919"/>
       <c r="D919"/>
-    </row>
-    <row r="920" spans="1:5">
+      <c r="E919"/>
+    </row>
+    <row r="920" spans="1:6">
       <c r="A920"/>
       <c r="B920"/>
       <c r="C920"/>
       <c r="D920"/>
-    </row>
-    <row r="921" spans="1:5">
+      <c r="E920"/>
+    </row>
+    <row r="921" spans="1:6">
       <c r="A921"/>
       <c r="B921"/>
       <c r="C921"/>
       <c r="D921"/>
-    </row>
-    <row r="922" spans="1:5">
+      <c r="E921"/>
+    </row>
+    <row r="922" spans="1:6">
       <c r="A922"/>
       <c r="B922"/>
       <c r="C922"/>
       <c r="D922"/>
-    </row>
-    <row r="923" spans="1:5">
+      <c r="E922"/>
+    </row>
+    <row r="923" spans="1:6">
       <c r="A923"/>
       <c r="B923"/>
       <c r="C923"/>
       <c r="D923"/>
-    </row>
-    <row r="924" spans="1:5">
+      <c r="E923"/>
+    </row>
+    <row r="924" spans="1:6">
       <c r="A924"/>
       <c r="B924"/>
       <c r="C924"/>
       <c r="D924"/>
-    </row>
-    <row r="925" spans="1:5">
+      <c r="E924"/>
+    </row>
+    <row r="925" spans="1:6">
       <c r="A925"/>
       <c r="B925"/>
       <c r="C925"/>
       <c r="D925"/>
-    </row>
-    <row r="926" spans="1:5">
+      <c r="E925"/>
+    </row>
+    <row r="926" spans="1:6">
       <c r="A926"/>
       <c r="B926"/>
       <c r="C926"/>
       <c r="D926"/>
-    </row>
-    <row r="927" spans="1:5">
+      <c r="E926"/>
+    </row>
+    <row r="927" spans="1:6">
       <c r="A927"/>
       <c r="B927"/>
       <c r="C927"/>
       <c r="D927"/>
-    </row>
-    <row r="928" spans="1:5">
+      <c r="E927"/>
+    </row>
+    <row r="928" spans="1:6">
       <c r="A928"/>
       <c r="B928"/>
       <c r="C928"/>
       <c r="D928"/>
-    </row>
-    <row r="929" spans="1:5">
+      <c r="E928"/>
+    </row>
+    <row r="929" spans="1:6">
       <c r="A929"/>
       <c r="B929"/>
       <c r="C929"/>
       <c r="D929"/>
-    </row>
-    <row r="930" spans="1:5">
+      <c r="E929"/>
+    </row>
+    <row r="930" spans="1:6">
       <c r="A930"/>
       <c r="B930"/>
       <c r="C930"/>
       <c r="D930"/>
-    </row>
-    <row r="931" spans="1:5">
+      <c r="E930"/>
+    </row>
+    <row r="931" spans="1:6">
       <c r="A931"/>
       <c r="B931"/>
       <c r="C931"/>
       <c r="D931"/>
-    </row>
-    <row r="932" spans="1:5">
+      <c r="E931"/>
+    </row>
+    <row r="932" spans="1:6">
       <c r="A932"/>
       <c r="B932"/>
       <c r="C932"/>
       <c r="D932"/>
-    </row>
-    <row r="933" spans="1:5">
+      <c r="E932"/>
+    </row>
+    <row r="933" spans="1:6">
       <c r="A933"/>
       <c r="B933"/>
       <c r="C933"/>
       <c r="D933"/>
-    </row>
-    <row r="934" spans="1:5">
+      <c r="E933"/>
+    </row>
+    <row r="934" spans="1:6">
       <c r="A934"/>
       <c r="B934"/>
       <c r="C934"/>
       <c r="D934"/>
-    </row>
-    <row r="935" spans="1:5">
+      <c r="E934"/>
+    </row>
+    <row r="935" spans="1:6">
       <c r="A935"/>
       <c r="B935"/>
       <c r="C935"/>
       <c r="D935"/>
-    </row>
-    <row r="936" spans="1:5">
+      <c r="E935"/>
+    </row>
+    <row r="936" spans="1:6">
       <c r="A936"/>
       <c r="B936"/>
       <c r="C936"/>
       <c r="D936"/>
-    </row>
-    <row r="937" spans="1:5">
+      <c r="E936"/>
+    </row>
+    <row r="937" spans="1:6">
       <c r="A937"/>
       <c r="B937"/>
       <c r="C937"/>
       <c r="D937"/>
-    </row>
-    <row r="938" spans="1:5">
+      <c r="E937"/>
+    </row>
+    <row r="938" spans="1:6">
       <c r="A938"/>
       <c r="B938"/>
       <c r="C938"/>
       <c r="D938"/>
-    </row>
-    <row r="939" spans="1:5">
+      <c r="E938"/>
+    </row>
+    <row r="939" spans="1:6">
       <c r="A939"/>
       <c r="B939"/>
       <c r="C939"/>
       <c r="D939"/>
-    </row>
-    <row r="940" spans="1:5">
+      <c r="E939"/>
+    </row>
+    <row r="940" spans="1:6">
       <c r="A940"/>
       <c r="B940"/>
       <c r="C940"/>
       <c r="D940"/>
-    </row>
-    <row r="941" spans="1:5">
+      <c r="E940"/>
+    </row>
+    <row r="941" spans="1:6">
       <c r="A941"/>
       <c r="B941"/>
       <c r="C941"/>
       <c r="D941"/>
-    </row>
-    <row r="942" spans="1:5">
+      <c r="E941"/>
+    </row>
+    <row r="942" spans="1:6">
       <c r="A942"/>
       <c r="B942"/>
       <c r="C942"/>
       <c r="D942"/>
-    </row>
-    <row r="943" spans="1:5">
+      <c r="E942"/>
+    </row>
+    <row r="943" spans="1:6">
       <c r="A943"/>
       <c r="B943"/>
       <c r="C943"/>
       <c r="D943"/>
-    </row>
-    <row r="944" spans="1:5">
+      <c r="E943"/>
+    </row>
+    <row r="944" spans="1:6">
       <c r="A944"/>
       <c r="B944"/>
       <c r="C944"/>
       <c r="D944"/>
-    </row>
-    <row r="945" spans="1:5">
+      <c r="E944"/>
+    </row>
+    <row r="945" spans="1:6">
       <c r="A945"/>
       <c r="B945"/>
       <c r="C945"/>
       <c r="D945"/>
-    </row>
-    <row r="946" spans="1:5">
+      <c r="E945"/>
+    </row>
+    <row r="946" spans="1:6">
       <c r="A946"/>
       <c r="B946"/>
       <c r="C946"/>
       <c r="D946"/>
-    </row>
-    <row r="947" spans="1:5">
+      <c r="E946"/>
+    </row>
+    <row r="947" spans="1:6">
       <c r="A947"/>
       <c r="B947"/>
       <c r="C947"/>
       <c r="D947"/>
-    </row>
-    <row r="948" spans="1:5">
+      <c r="E947"/>
+    </row>
+    <row r="948" spans="1:6">
       <c r="A948"/>
       <c r="B948"/>
       <c r="C948"/>
       <c r="D948"/>
-    </row>
-    <row r="949" spans="1:5">
+      <c r="E948"/>
+    </row>
+    <row r="949" spans="1:6">
       <c r="A949"/>
       <c r="B949"/>
       <c r="C949"/>
       <c r="D949"/>
-    </row>
-    <row r="950" spans="1:5">
+      <c r="E949"/>
+    </row>
+    <row r="950" spans="1:6">
       <c r="A950"/>
       <c r="B950"/>
       <c r="C950"/>
       <c r="D950"/>
-    </row>
-    <row r="951" spans="1:5">
+      <c r="E950"/>
+    </row>
+    <row r="951" spans="1:6">
       <c r="A951"/>
       <c r="B951"/>
       <c r="C951"/>
       <c r="D951"/>
-    </row>
-    <row r="952" spans="1:5">
+      <c r="E951"/>
+    </row>
+    <row r="952" spans="1:6">
       <c r="A952"/>
       <c r="B952"/>
       <c r="C952"/>
       <c r="D952"/>
-    </row>
-    <row r="953" spans="1:5">
+      <c r="E952"/>
+    </row>
+    <row r="953" spans="1:6">
       <c r="A953"/>
       <c r="B953"/>
       <c r="C953"/>
       <c r="D953"/>
-    </row>
-    <row r="954" spans="1:5">
+      <c r="E953"/>
+    </row>
+    <row r="954" spans="1:6">
       <c r="A954"/>
       <c r="B954"/>
       <c r="C954"/>
       <c r="D954"/>
-    </row>
-    <row r="955" spans="1:5">
+      <c r="E954"/>
+    </row>
+    <row r="955" spans="1:6">
       <c r="A955"/>
       <c r="B955"/>
       <c r="C955"/>
       <c r="D955"/>
-    </row>
-    <row r="956" spans="1:5">
+      <c r="E955"/>
+    </row>
+    <row r="956" spans="1:6">
       <c r="A956"/>
       <c r="B956"/>
       <c r="C956"/>
       <c r="D956"/>
-    </row>
-    <row r="957" spans="1:5">
+      <c r="E956"/>
+    </row>
+    <row r="957" spans="1:6">
       <c r="A957"/>
       <c r="B957"/>
       <c r="C957"/>
       <c r="D957"/>
-    </row>
-    <row r="958" spans="1:5">
+      <c r="E957"/>
+    </row>
+    <row r="958" spans="1:6">
       <c r="A958"/>
       <c r="B958"/>
       <c r="C958"/>
       <c r="D958"/>
-    </row>
-    <row r="959" spans="1:5">
+      <c r="E958"/>
+    </row>
+    <row r="959" spans="1:6">
       <c r="A959"/>
       <c r="B959"/>
       <c r="C959"/>
       <c r="D959"/>
-    </row>
-    <row r="960" spans="1:5">
+      <c r="E959"/>
+    </row>
+    <row r="960" spans="1:6">
       <c r="A960"/>
       <c r="B960"/>
       <c r="C960"/>
       <c r="D960"/>
-    </row>
-    <row r="961" spans="1:5">
+      <c r="E960"/>
+    </row>
+    <row r="961" spans="1:6">
       <c r="A961"/>
       <c r="B961"/>
       <c r="C961"/>
       <c r="D961"/>
-    </row>
-    <row r="962" spans="1:5">
+      <c r="E961"/>
+    </row>
+    <row r="962" spans="1:6">
       <c r="A962"/>
       <c r="B962"/>
       <c r="C962"/>
       <c r="D962"/>
-    </row>
-    <row r="963" spans="1:5">
+      <c r="E962"/>
+    </row>
+    <row r="963" spans="1:6">
       <c r="A963"/>
       <c r="B963"/>
       <c r="C963"/>
       <c r="D963"/>
-    </row>
-    <row r="964" spans="1:5">
+      <c r="E963"/>
+    </row>
+    <row r="964" spans="1:6">
       <c r="A964"/>
       <c r="B964"/>
       <c r="C964"/>
       <c r="D964"/>
-    </row>
-    <row r="965" spans="1:5">
+      <c r="E964"/>
+    </row>
+    <row r="965" spans="1:6">
       <c r="A965"/>
       <c r="B965"/>
       <c r="C965"/>
       <c r="D965"/>
-    </row>
-    <row r="966" spans="1:5">
+      <c r="E965"/>
+    </row>
+    <row r="966" spans="1:6">
       <c r="A966"/>
       <c r="B966"/>
       <c r="C966"/>
       <c r="D966"/>
-    </row>
-    <row r="967" spans="1:5">
+      <c r="E966"/>
+    </row>
+    <row r="967" spans="1:6">
       <c r="A967"/>
       <c r="B967"/>
       <c r="C967"/>
       <c r="D967"/>
-    </row>
-    <row r="968" spans="1:5">
+      <c r="E967"/>
+    </row>
+    <row r="968" spans="1:6">
       <c r="A968"/>
       <c r="B968"/>
       <c r="C968"/>
       <c r="D968"/>
-    </row>
-    <row r="969" spans="1:5">
+      <c r="E968"/>
+    </row>
+    <row r="969" spans="1:6">
       <c r="A969"/>
       <c r="B969"/>
       <c r="C969"/>
       <c r="D969"/>
-    </row>
-    <row r="970" spans="1:5">
+      <c r="E969"/>
+    </row>
+    <row r="970" spans="1:6">
       <c r="A970"/>
       <c r="B970"/>
       <c r="C970"/>
       <c r="D970"/>
-    </row>
-    <row r="971" spans="1:5">
+      <c r="E970"/>
+    </row>
+    <row r="971" spans="1:6">
       <c r="A971"/>
       <c r="B971"/>
       <c r="C971"/>
       <c r="D971"/>
-    </row>
-    <row r="972" spans="1:5">
+      <c r="E971"/>
+    </row>
+    <row r="972" spans="1:6">
       <c r="A972"/>
       <c r="B972"/>
       <c r="C972"/>
       <c r="D972"/>
-    </row>
-    <row r="973" spans="1:5">
+      <c r="E972"/>
+    </row>
+    <row r="973" spans="1:6">
       <c r="A973"/>
       <c r="B973"/>
       <c r="C973"/>
       <c r="D973"/>
-    </row>
-    <row r="974" spans="1:5">
+      <c r="E973"/>
+    </row>
+    <row r="974" spans="1:6">
       <c r="A974"/>
       <c r="B974"/>
       <c r="C974"/>
       <c r="D974"/>
-    </row>
-    <row r="975" spans="1:5">
+      <c r="E974"/>
+    </row>
+    <row r="975" spans="1:6">
       <c r="A975"/>
       <c r="B975"/>
       <c r="C975"/>
       <c r="D975"/>
-    </row>
-    <row r="976" spans="1:5">
+      <c r="E975"/>
+    </row>
+    <row r="976" spans="1:6">
       <c r="A976"/>
       <c r="B976"/>
       <c r="C976"/>
       <c r="D976"/>
-    </row>
-    <row r="977" spans="1:5">
+      <c r="E976"/>
+    </row>
+    <row r="977" spans="1:6">
       <c r="A977"/>
       <c r="B977"/>
       <c r="C977"/>
       <c r="D977"/>
-    </row>
-    <row r="978" spans="1:5">
+      <c r="E977"/>
+    </row>
+    <row r="978" spans="1:6">
       <c r="A978"/>
       <c r="B978"/>
       <c r="C978"/>
       <c r="D978"/>
-    </row>
-    <row r="979" spans="1:5">
+      <c r="E978"/>
+    </row>
+    <row r="979" spans="1:6">
       <c r="A979"/>
       <c r="B979"/>
       <c r="C979"/>
       <c r="D979"/>
-    </row>
-    <row r="980" spans="1:5">
+      <c r="E979"/>
+    </row>
+    <row r="980" spans="1:6">
       <c r="A980"/>
       <c r="B980"/>
       <c r="C980"/>
       <c r="D980"/>
-    </row>
-    <row r="981" spans="1:5">
+      <c r="E980"/>
+    </row>
+    <row r="981" spans="1:6">
       <c r="A981"/>
       <c r="B981"/>
       <c r="C981"/>
       <c r="D981"/>
-    </row>
-    <row r="982" spans="1:5">
+      <c r="E981"/>
+    </row>
+    <row r="982" spans="1:6">
       <c r="A982"/>
       <c r="B982"/>
       <c r="C982"/>
       <c r="D982"/>
-    </row>
-    <row r="983" spans="1:5">
+      <c r="E982"/>
+    </row>
+    <row r="983" spans="1:6">
       <c r="A983"/>
       <c r="B983"/>
       <c r="C983"/>
       <c r="D983"/>
-    </row>
-    <row r="984" spans="1:5">
+      <c r="E983"/>
+    </row>
+    <row r="984" spans="1:6">
       <c r="A984"/>
       <c r="B984"/>
       <c r="C984"/>
       <c r="D984"/>
-    </row>
-    <row r="985" spans="1:5">
+      <c r="E984"/>
+    </row>
+    <row r="985" spans="1:6">
       <c r="A985"/>
       <c r="B985"/>
       <c r="C985"/>
       <c r="D985"/>
-    </row>
-    <row r="986" spans="1:5">
+      <c r="E985"/>
+    </row>
+    <row r="986" spans="1:6">
       <c r="A986"/>
       <c r="B986"/>
       <c r="C986"/>
       <c r="D986"/>
-    </row>
-    <row r="987" spans="1:5">
+      <c r="E986"/>
+    </row>
+    <row r="987" spans="1:6">
       <c r="A987"/>
       <c r="B987"/>
       <c r="C987"/>
       <c r="D987"/>
-    </row>
-    <row r="988" spans="1:5">
+      <c r="E987"/>
+    </row>
+    <row r="988" spans="1:6">
       <c r="A988"/>
       <c r="B988"/>
       <c r="C988"/>
       <c r="D988"/>
-    </row>
-    <row r="989" spans="1:5">
+      <c r="E988"/>
+    </row>
+    <row r="989" spans="1:6">
       <c r="A989"/>
       <c r="B989"/>
       <c r="C989"/>
       <c r="D989"/>
-    </row>
-    <row r="990" spans="1:5">
+      <c r="E989"/>
+    </row>
+    <row r="990" spans="1:6">
       <c r="A990"/>
       <c r="B990"/>
       <c r="C990"/>
       <c r="D990"/>
-    </row>
-    <row r="991" spans="1:5">
+      <c r="E990"/>
+    </row>
+    <row r="991" spans="1:6">
       <c r="A991"/>
       <c r="B991"/>
       <c r="C991"/>
       <c r="D991"/>
-    </row>
-    <row r="992" spans="1:5">
+      <c r="E991"/>
+    </row>
+    <row r="992" spans="1:6">
       <c r="A992"/>
       <c r="B992"/>
       <c r="C992"/>
       <c r="D992"/>
-    </row>
-    <row r="993" spans="1:5">
+      <c r="E992"/>
+    </row>
+    <row r="993" spans="1:6">
       <c r="A993"/>
       <c r="B993"/>
       <c r="C993"/>
       <c r="D993"/>
-    </row>
-    <row r="994" spans="1:5">
+      <c r="E993"/>
+    </row>
+    <row r="994" spans="1:6">
       <c r="A994"/>
       <c r="B994"/>
       <c r="C994"/>
       <c r="D994"/>
-    </row>
-    <row r="995" spans="1:5">
+      <c r="E994"/>
+    </row>
+    <row r="995" spans="1:6">
       <c r="A995"/>
       <c r="B995"/>
       <c r="C995"/>
       <c r="D995"/>
-    </row>
-    <row r="996" spans="1:5">
+      <c r="E995"/>
+    </row>
+    <row r="996" spans="1:6">
       <c r="A996"/>
       <c r="B996"/>
       <c r="C996"/>
       <c r="D996"/>
-    </row>
-    <row r="997" spans="1:5">
+      <c r="E996"/>
+    </row>
+    <row r="997" spans="1:6">
       <c r="A997"/>
       <c r="B997"/>
       <c r="C997"/>
       <c r="D997"/>
-    </row>
-    <row r="998" spans="1:5">
+      <c r="E997"/>
+    </row>
+    <row r="998" spans="1:6">
       <c r="A998"/>
       <c r="B998"/>
       <c r="C998"/>
       <c r="D998"/>
-    </row>
-    <row r="999" spans="1:5">
+      <c r="E998"/>
+    </row>
+    <row r="999" spans="1:6">
       <c r="A999"/>
       <c r="B999"/>
       <c r="C999"/>
       <c r="D999"/>
-    </row>
-    <row r="1000" spans="1:5">
+      <c r="E999"/>
+    </row>
+    <row r="1000" spans="1:6">
       <c r="A1000"/>
       <c r="B1000"/>
       <c r="C1000"/>
       <c r="D1000"/>
+      <c r="E1000"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="A2:A1000">
       <formula1>=YearList</formula1>
     </dataValidation>
@@ -6498,6 +7510,9 @@
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="D2:D1000">
       <formula1>=EntityList</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Pilihan tidak valid" error="Nilai yang dimasukkan tidak ada dalam daftar." promptTitle="Pilih dari daftar" prompt="Silakan pilih salah satu nilai dari dropdown." sqref="E2:E1000">
+      <formula1>=EndUserList</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -6520,127 +7535,130 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1">
         <v>2024</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
+      <c r="E1" t="s">
+        <v>9</v>
       </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2027</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2028</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
